--- a/Hoadon/HDVao/10/HDDienTuMayTinhTien.xlsx
+++ b/Hoadon/HDVao/10/HDDienTuMayTinhTien.xlsx
@@ -450,6 +450,154 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" s="4" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>C25MVT</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>213473</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>10/10/2025</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>0302249586-009</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>CHI NHÁNH CÔNG TY TNHH MM MEGA MARKET (VIỆT NAM) TẠI TỈNH BÀ RỊA - VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>Đường 2 tháng 9 (Quốc lộ 51B), Khu phố 1, Phường Phước Thắng, Thành phố Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="I9" s="7" t="inlineStr">
+        <is>
+          <t>3502245376</t>
+        </is>
+      </c>
+      <c r="J9" s="6" t="inlineStr">
+        <is>
+          <t>CONG TY CO PHAN DAU TU XAY DUNG THUONG MAI
+DICH VU KY THUAT H &amp; V</t>
+        </is>
+      </c>
+      <c r="K9" s="6"/>
+      <c r="L9" s="13" t="n">
+        <v>828183.0</v>
+      </c>
+      <c r="M9" s="13" t="n">
+        <v>82818.0</v>
+      </c>
+      <c r="N9" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O9" s="13" t="n">
+        <v>911001.0</v>
+      </c>
+      <c r="P9" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q9" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>C25MVT</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>213475</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>10/10/2025</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>0302249586-009</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>CHI NHÁNH CÔNG TY TNHH MM MEGA MARKET (VIỆT NAM) TẠI TỈNH BÀ RỊA - VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>Đường 2 tháng 9 (Quốc lộ 51B), Khu phố 1, Phường Phước Thắng, Thành phố Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="I10" s="7" t="inlineStr">
+        <is>
+          <t>3502245376</t>
+        </is>
+      </c>
+      <c r="J10" s="6" t="inlineStr">
+        <is>
+          <t>CONG TY CO PHAN DAU TU XAY DUNG THUONG MAI
+DICH VU KY THUAT H &amp; V</t>
+        </is>
+      </c>
+      <c r="K10" s="6"/>
+      <c r="L10" s="13" t="n">
+        <v>2527250.0</v>
+      </c>
+      <c r="M10" s="13" t="n">
+        <v>126361.0</v>
+      </c>
+      <c r="N10" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O10" s="13" t="n">
+        <v>2653611.0</v>
+      </c>
+      <c r="P10" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q10" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A3:Q3"/>

--- a/Hoadon/HDVao/10/HDDienTuMayTinhTien.xlsx
+++ b/Hoadon/HDVao/10/HDDienTuMayTinhTien.xlsx
@@ -598,6 +598,153 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" s="4" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>C25MVT</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>215275</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>12/10/2025</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>0302249586-009</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>CHI NHÁNH CÔNG TY TNHH MM MEGA MARKET (VIỆT NAM) TẠI TỈNH BÀ RỊA - VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>Đường 2 tháng 9 (Quốc lộ 51B), Khu phố 1, Phường Phước Thắng, Thành phố Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="I11" s="7" t="inlineStr">
+        <is>
+          <t>3502245376</t>
+        </is>
+      </c>
+      <c r="J11" s="6" t="inlineStr">
+        <is>
+          <t>CONG TY CO PHAN DAU TU XAY DUNG THUONG MAI
+DICH VU KY THUAT H &amp; V</t>
+        </is>
+      </c>
+      <c r="K11" s="6"/>
+      <c r="L11" s="13" t="n">
+        <v>1330552.0</v>
+      </c>
+      <c r="M11" s="13" t="n">
+        <v>106444.0</v>
+      </c>
+      <c r="N11" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O11" s="13" t="n">
+        <v>1436996.0</v>
+      </c>
+      <c r="P11" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q11" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>C25MHN</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>2176</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>11/10/2025</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>3502546101</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI - DỊCH VỤ GAS HOÀNG NAM</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>C5-2/1 TT Đô Thị Chí Linh, Phường Rạch Dừa, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I12" s="7" t="inlineStr">
+        <is>
+          <t>3502245376</t>
+        </is>
+      </c>
+      <c r="J12" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
+        </is>
+      </c>
+      <c r="K12" s="6"/>
+      <c r="L12" s="13" t="n">
+        <v>551852.0</v>
+      </c>
+      <c r="M12" s="13" t="n">
+        <v>44148.0</v>
+      </c>
+      <c r="N12" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O12" s="13" t="n">
+        <v>596000.0</v>
+      </c>
+      <c r="P12" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q12" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A3:Q3"/>

--- a/Hoadon/HDVao/10/HDDienTuMayTinhTien.xlsx
+++ b/Hoadon/HDVao/10/HDDienTuMayTinhTien.xlsx
@@ -313,57 +313,56 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>C25MVT</t>
+          <t>C25MHM</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>208364</t>
+          <t>1056119</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>03/10/2025</t>
+          <t>14/10/2025</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>0302249586-009</t>
+          <t>0110269067-014</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>CHI NHÁNH CÔNG TY TNHH MM MEGA MARKET (VIỆT NAM) TẠI TỈNH BÀ RỊA - VŨNG TÀU</t>
+          <t>CHI NHÁNH BÀ RỊA - VŨNG TÀU – CÔNG TY CỔ PHẦN DI CHUYỂN XANH VÀ THÔNG MINH GSM</t>
         </is>
       </c>
       <c r="H7" s="6" t="inlineStr">
         <is>
-          <t>Đường 2 tháng 9 (Quốc lộ 51B), Khu phố 1, Phường Phước Thắng, Thành phố Hồ Chí Minh</t>
+          <t>1169/7 Đường 30/4, Phường Phước Thắng, TP Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I7" s="7" t="inlineStr">
         <is>
-          <t>3502245376</t>
+          <t>3502217971</t>
         </is>
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
-          <t>CONG TY CO PHAN DAU TU XAY DUNG THUONG MAI
-DICH VU KY THUAT H &amp; V</t>
+          <t>CTY TNHH ĐẠI LÝ TÀU BIỂN VŨNG TÀU</t>
         </is>
       </c>
       <c r="K7" s="6"/>
       <c r="L7" s="13" t="n">
-        <v>1707183.0</v>
+        <v>34259.0</v>
       </c>
       <c r="M7" s="13" t="n">
-        <v>170718.0</v>
+        <v>2741.0</v>
       </c>
       <c r="N7" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O7" s="13" t="n">
-        <v>1877901.0</v>
+        <v>37000.0</v>
       </c>
       <c r="P7" s="6" t="inlineStr">
         <is>
@@ -387,57 +386,56 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>C25MVT</t>
+          <t>C25MHM</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>208367</t>
+          <t>1057544</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>03/10/2025</t>
+          <t>14/10/2025</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>0302249586-009</t>
+          <t>0110269067-014</t>
         </is>
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>CHI NHÁNH CÔNG TY TNHH MM MEGA MARKET (VIỆT NAM) TẠI TỈNH BÀ RỊA - VŨNG TÀU</t>
+          <t>CHI NHÁNH BÀ RỊA - VŨNG TÀU – CÔNG TY CỔ PHẦN DI CHUYỂN XANH VÀ THÔNG MINH GSM</t>
         </is>
       </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
-          <t>Đường 2 tháng 9 (Quốc lộ 51B), Khu phố 1, Phường Phước Thắng, Thành phố Hồ Chí Minh</t>
+          <t>1169/7 Đường 30/4, Phường Phước Thắng, TP Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I8" s="7" t="inlineStr">
         <is>
-          <t>3502245376</t>
+          <t>3502217971</t>
         </is>
       </c>
       <c r="J8" s="6" t="inlineStr">
         <is>
-          <t>CONG TY CO PHAN DAU TU XAY DUNG THUONG MAI
-DICH VU KY THUAT H &amp; V</t>
+          <t>CTY TNHH ĐẠI LÝ TÀU BIỂN VŨNG TÀU</t>
         </is>
       </c>
       <c r="K8" s="6"/>
       <c r="L8" s="13" t="n">
-        <v>1184229.0</v>
+        <v>34259.0</v>
       </c>
       <c r="M8" s="13" t="n">
-        <v>92481.0</v>
+        <v>2741.0</v>
       </c>
       <c r="N8" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O8" s="13" t="n">
-        <v>1276710.0</v>
+        <v>37000.0</v>
       </c>
       <c r="P8" s="6" t="inlineStr">
         <is>
@@ -461,57 +459,54 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>C25MVT</t>
+          <t>C25MMD</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>213473</t>
+          <t>17366</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>10/10/2025</t>
+          <t>11/10/2025</t>
         </is>
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>0302249586-009</t>
+          <t>3500354108</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>CHI NHÁNH CÔNG TY TNHH MM MEGA MARKET (VIỆT NAM) TẠI TỈNH BÀ RỊA - VŨNG TÀU</t>
+          <t>DOANH NGHIỆP TƯ NHÂN XĂNG DẦU LONG PHƯỚC</t>
         </is>
       </c>
       <c r="H9" s="6" t="inlineStr">
         <is>
-          <t>Đường 2 tháng 9 (Quốc lộ 51B), Khu phố 1, Phường Phước Thắng, Thành phố Hồ Chí Minh</t>
+          <t>Số 3 Trần Phú, Phường Vũng Tàu, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I9" s="7" t="inlineStr">
         <is>
-          <t>3502245376</t>
+          <t>3502217971</t>
         </is>
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
-          <t>CONG TY CO PHAN DAU TU XAY DUNG THUONG MAI
-DICH VU KY THUAT H &amp; V</t>
+          <t>Công Ty TNHH Đại Lý Tàu Biển Vũng Tàu</t>
         </is>
       </c>
       <c r="K9" s="6"/>
       <c r="L9" s="13" t="n">
-        <v>828183.0</v>
+        <v>450204.0</v>
       </c>
       <c r="M9" s="13" t="n">
-        <v>82818.0</v>
-      </c>
-      <c r="N9" s="13" t="n">
-        <v>0.0</v>
-      </c>
+        <v>36016.0</v>
+      </c>
+      <c r="N9" s="13"/>
       <c r="O9" s="13" t="n">
-        <v>911001.0</v>
+        <v>486220.0</v>
       </c>
       <c r="P9" s="6" t="inlineStr">
         <is>
@@ -535,57 +530,54 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>C25MVT</t>
+          <t>C25MMD</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>213475</t>
+          <t>17367</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>10/10/2025</t>
+          <t>11/10/2025</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>0302249586-009</t>
+          <t>3500354108</t>
         </is>
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>CHI NHÁNH CÔNG TY TNHH MM MEGA MARKET (VIỆT NAM) TẠI TỈNH BÀ RỊA - VŨNG TÀU</t>
+          <t>DOANH NGHIỆP TƯ NHÂN XĂNG DẦU LONG PHƯỚC</t>
         </is>
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>Đường 2 tháng 9 (Quốc lộ 51B), Khu phố 1, Phường Phước Thắng, Thành phố Hồ Chí Minh</t>
+          <t>Số 3 Trần Phú, Phường Vũng Tàu, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I10" s="7" t="inlineStr">
         <is>
-          <t>3502245376</t>
+          <t>3502217971</t>
         </is>
       </c>
       <c r="J10" s="6" t="inlineStr">
         <is>
-          <t>CONG TY CO PHAN DAU TU XAY DUNG THUONG MAI
-DICH VU KY THUAT H &amp; V</t>
+          <t>Công Ty TNHH Đại Lý Tàu Biển Vũng Tàu</t>
         </is>
       </c>
       <c r="K10" s="6"/>
       <c r="L10" s="13" t="n">
-        <v>2527250.0</v>
+        <v>70000.0</v>
       </c>
       <c r="M10" s="13" t="n">
-        <v>126361.0</v>
-      </c>
-      <c r="N10" s="13" t="n">
-        <v>0.0</v>
-      </c>
+        <v>7000.0</v>
+      </c>
+      <c r="N10" s="13"/>
       <c r="O10" s="13" t="n">
-        <v>2653611.0</v>
+        <v>77000.0</v>
       </c>
       <c r="P10" s="6" t="inlineStr">
         <is>
@@ -593,153 +585,6 @@
         </is>
       </c>
       <c r="Q10" s="6" t="inlineStr">
-        <is>
-          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="n">
-        <v>5.0</v>
-      </c>
-      <c r="B11" s="7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>C25MVT</t>
-        </is>
-      </c>
-      <c r="D11" s="7" t="inlineStr">
-        <is>
-          <t>215275</t>
-        </is>
-      </c>
-      <c r="E11" s="7" t="inlineStr">
-        <is>
-          <t>12/10/2025</t>
-        </is>
-      </c>
-      <c r="F11" s="7" t="inlineStr">
-        <is>
-          <t>0302249586-009</t>
-        </is>
-      </c>
-      <c r="G11" s="6" t="inlineStr">
-        <is>
-          <t>CHI NHÁNH CÔNG TY TNHH MM MEGA MARKET (VIỆT NAM) TẠI TỈNH BÀ RỊA - VŨNG TÀU</t>
-        </is>
-      </c>
-      <c r="H11" s="6" t="inlineStr">
-        <is>
-          <t>Đường 2 tháng 9 (Quốc lộ 51B), Khu phố 1, Phường Phước Thắng, Thành phố Hồ Chí Minh</t>
-        </is>
-      </c>
-      <c r="I11" s="7" t="inlineStr">
-        <is>
-          <t>3502245376</t>
-        </is>
-      </c>
-      <c r="J11" s="6" t="inlineStr">
-        <is>
-          <t>CONG TY CO PHAN DAU TU XAY DUNG THUONG MAI
-DICH VU KY THUAT H &amp; V</t>
-        </is>
-      </c>
-      <c r="K11" s="6"/>
-      <c r="L11" s="13" t="n">
-        <v>1330552.0</v>
-      </c>
-      <c r="M11" s="13" t="n">
-        <v>106444.0</v>
-      </c>
-      <c r="N11" s="13" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="O11" s="13" t="n">
-        <v>1436996.0</v>
-      </c>
-      <c r="P11" s="6" t="inlineStr">
-        <is>
-          <t>Hóa đơn mới</t>
-        </is>
-      </c>
-      <c r="Q11" s="6" t="inlineStr">
-        <is>
-          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="n">
-        <v>6.0</v>
-      </c>
-      <c r="B12" s="7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>C25MHN</t>
-        </is>
-      </c>
-      <c r="D12" s="7" t="inlineStr">
-        <is>
-          <t>2176</t>
-        </is>
-      </c>
-      <c r="E12" s="7" t="inlineStr">
-        <is>
-          <t>11/10/2025</t>
-        </is>
-      </c>
-      <c r="F12" s="7" t="inlineStr">
-        <is>
-          <t>3502546101</t>
-        </is>
-      </c>
-      <c r="G12" s="6" t="inlineStr">
-        <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI - DỊCH VỤ GAS HOÀNG NAM</t>
-        </is>
-      </c>
-      <c r="H12" s="6" t="inlineStr">
-        <is>
-          <t>C5-2/1 TT Đô Thị Chí Linh, Phường Rạch Dừa, Thành phố Hồ Chí Minh, Việt Nam</t>
-        </is>
-      </c>
-      <c r="I12" s="7" t="inlineStr">
-        <is>
-          <t>3502245376</t>
-        </is>
-      </c>
-      <c r="J12" s="6" t="inlineStr">
-        <is>
-          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
-        </is>
-      </c>
-      <c r="K12" s="6"/>
-      <c r="L12" s="13" t="n">
-        <v>551852.0</v>
-      </c>
-      <c r="M12" s="13" t="n">
-        <v>44148.0</v>
-      </c>
-      <c r="N12" s="13" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="O12" s="13" t="n">
-        <v>596000.0</v>
-      </c>
-      <c r="P12" s="6" t="inlineStr">
-        <is>
-          <t>Hóa đơn mới</t>
-        </is>
-      </c>
-      <c r="Q12" s="6" t="inlineStr">
         <is>
           <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
         </is>

--- a/Hoadon/HDVao/10/HDDienTuMayTinhTien.xlsx
+++ b/Hoadon/HDVao/10/HDDienTuMayTinhTien.xlsx
@@ -313,56 +313,57 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>C25MHM</t>
+          <t>C25MVT</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>1056119</t>
+          <t>208364</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>14/10/2025</t>
+          <t>03/10/2025</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>0110269067-014</t>
+          <t>0302249586-009</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>CHI NHÁNH BÀ RỊA - VŨNG TÀU – CÔNG TY CỔ PHẦN DI CHUYỂN XANH VÀ THÔNG MINH GSM</t>
+          <t>CHI NHÁNH CÔNG TY TNHH MM MEGA MARKET (VIỆT NAM) TẠI TỈNH BÀ RỊA - VŨNG TÀU</t>
         </is>
       </c>
       <c r="H7" s="6" t="inlineStr">
         <is>
-          <t>1169/7 Đường 30/4, Phường Phước Thắng, TP Hồ Chí Minh, Việt Nam</t>
+          <t>Đường 2 tháng 9 (Quốc lộ 51B), Khu phố 1, Phường Phước Thắng, Thành phố Hồ Chí Minh</t>
         </is>
       </c>
       <c r="I7" s="7" t="inlineStr">
         <is>
-          <t>3502217971</t>
+          <t>3502245376</t>
         </is>
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
-          <t>CTY TNHH ĐẠI LÝ TÀU BIỂN VŨNG TÀU</t>
+          <t>CONG TY CO PHAN DAU TU XAY DUNG THUONG MAI
+DICH VU KY THUAT H &amp; V</t>
         </is>
       </c>
       <c r="K7" s="6"/>
       <c r="L7" s="13" t="n">
-        <v>34259.0</v>
+        <v>1707183.0</v>
       </c>
       <c r="M7" s="13" t="n">
-        <v>2741.0</v>
+        <v>170718.0</v>
       </c>
       <c r="N7" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O7" s="13" t="n">
-        <v>37000.0</v>
+        <v>1877901.0</v>
       </c>
       <c r="P7" s="6" t="inlineStr">
         <is>
@@ -386,56 +387,57 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>C25MHM</t>
+          <t>C25MVT</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>1057544</t>
+          <t>208367</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>14/10/2025</t>
+          <t>03/10/2025</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>0110269067-014</t>
+          <t>0302249586-009</t>
         </is>
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>CHI NHÁNH BÀ RỊA - VŨNG TÀU – CÔNG TY CỔ PHẦN DI CHUYỂN XANH VÀ THÔNG MINH GSM</t>
+          <t>CHI NHÁNH CÔNG TY TNHH MM MEGA MARKET (VIỆT NAM) TẠI TỈNH BÀ RỊA - VŨNG TÀU</t>
         </is>
       </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
-          <t>1169/7 Đường 30/4, Phường Phước Thắng, TP Hồ Chí Minh, Việt Nam</t>
+          <t>Đường 2 tháng 9 (Quốc lộ 51B), Khu phố 1, Phường Phước Thắng, Thành phố Hồ Chí Minh</t>
         </is>
       </c>
       <c r="I8" s="7" t="inlineStr">
         <is>
-          <t>3502217971</t>
+          <t>3502245376</t>
         </is>
       </c>
       <c r="J8" s="6" t="inlineStr">
         <is>
-          <t>CTY TNHH ĐẠI LÝ TÀU BIỂN VŨNG TÀU</t>
+          <t>CONG TY CO PHAN DAU TU XAY DUNG THUONG MAI
+DICH VU KY THUAT H &amp; V</t>
         </is>
       </c>
       <c r="K8" s="6"/>
       <c r="L8" s="13" t="n">
-        <v>34259.0</v>
+        <v>1184229.0</v>
       </c>
       <c r="M8" s="13" t="n">
-        <v>2741.0</v>
+        <v>92481.0</v>
       </c>
       <c r="N8" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O8" s="13" t="n">
-        <v>37000.0</v>
+        <v>1276710.0</v>
       </c>
       <c r="P8" s="6" t="inlineStr">
         <is>
@@ -459,54 +461,57 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>C25MMD</t>
+          <t>C25MVT</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>17366</t>
+          <t>213473</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>11/10/2025</t>
+          <t>10/10/2025</t>
         </is>
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>3500354108</t>
+          <t>0302249586-009</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>DOANH NGHIỆP TƯ NHÂN XĂNG DẦU LONG PHƯỚC</t>
+          <t>CHI NHÁNH CÔNG TY TNHH MM MEGA MARKET (VIỆT NAM) TẠI TỈNH BÀ RỊA - VŨNG TÀU</t>
         </is>
       </c>
       <c r="H9" s="6" t="inlineStr">
         <is>
-          <t>Số 3 Trần Phú, Phường Vũng Tàu, Thành Phố Hồ Chí Minh, Việt Nam</t>
+          <t>Đường 2 tháng 9 (Quốc lộ 51B), Khu phố 1, Phường Phước Thắng, Thành phố Hồ Chí Minh</t>
         </is>
       </c>
       <c r="I9" s="7" t="inlineStr">
         <is>
-          <t>3502217971</t>
+          <t>3502245376</t>
         </is>
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
-          <t>Công Ty TNHH Đại Lý Tàu Biển Vũng Tàu</t>
+          <t>CONG TY CO PHAN DAU TU XAY DUNG THUONG MAI
+DICH VU KY THUAT H &amp; V</t>
         </is>
       </c>
       <c r="K9" s="6"/>
       <c r="L9" s="13" t="n">
-        <v>450204.0</v>
+        <v>828183.0</v>
       </c>
       <c r="M9" s="13" t="n">
-        <v>36016.0</v>
-      </c>
-      <c r="N9" s="13"/>
+        <v>82818.0</v>
+      </c>
+      <c r="N9" s="13" t="n">
+        <v>0.0</v>
+      </c>
       <c r="O9" s="13" t="n">
-        <v>486220.0</v>
+        <v>911001.0</v>
       </c>
       <c r="P9" s="6" t="inlineStr">
         <is>
@@ -530,54 +535,57 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>C25MMD</t>
+          <t>C25MVT</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>17367</t>
+          <t>213475</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>11/10/2025</t>
+          <t>10/10/2025</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>3500354108</t>
+          <t>0302249586-009</t>
         </is>
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>DOANH NGHIỆP TƯ NHÂN XĂNG DẦU LONG PHƯỚC</t>
+          <t>CHI NHÁNH CÔNG TY TNHH MM MEGA MARKET (VIỆT NAM) TẠI TỈNH BÀ RỊA - VŨNG TÀU</t>
         </is>
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>Số 3 Trần Phú, Phường Vũng Tàu, Thành Phố Hồ Chí Minh, Việt Nam</t>
+          <t>Đường 2 tháng 9 (Quốc lộ 51B), Khu phố 1, Phường Phước Thắng, Thành phố Hồ Chí Minh</t>
         </is>
       </c>
       <c r="I10" s="7" t="inlineStr">
         <is>
-          <t>3502217971</t>
+          <t>3502245376</t>
         </is>
       </c>
       <c r="J10" s="6" t="inlineStr">
         <is>
-          <t>Công Ty TNHH Đại Lý Tàu Biển Vũng Tàu</t>
+          <t>CONG TY CO PHAN DAU TU XAY DUNG THUONG MAI
+DICH VU KY THUAT H &amp; V</t>
         </is>
       </c>
       <c r="K10" s="6"/>
       <c r="L10" s="13" t="n">
-        <v>70000.0</v>
+        <v>2527250.0</v>
       </c>
       <c r="M10" s="13" t="n">
-        <v>7000.0</v>
-      </c>
-      <c r="N10" s="13"/>
+        <v>126361.0</v>
+      </c>
+      <c r="N10" s="13" t="n">
+        <v>0.0</v>
+      </c>
       <c r="O10" s="13" t="n">
-        <v>77000.0</v>
+        <v>2653611.0</v>
       </c>
       <c r="P10" s="6" t="inlineStr">
         <is>
@@ -585,6 +593,226 @@
         </is>
       </c>
       <c r="Q10" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>C25MVT</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>215275</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>12/10/2025</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>0302249586-009</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>CHI NHÁNH CÔNG TY TNHH MM MEGA MARKET (VIỆT NAM) TẠI TỈNH BÀ RỊA - VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>Đường 2 tháng 9 (Quốc lộ 51B), Khu phố 1, Phường Phước Thắng, Thành phố Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="I11" s="7" t="inlineStr">
+        <is>
+          <t>3502245376</t>
+        </is>
+      </c>
+      <c r="J11" s="6" t="inlineStr">
+        <is>
+          <t>CONG TY CO PHAN DAU TU XAY DUNG THUONG MAI
+DICH VU KY THUAT H &amp; V</t>
+        </is>
+      </c>
+      <c r="K11" s="6"/>
+      <c r="L11" s="13" t="n">
+        <v>1330552.0</v>
+      </c>
+      <c r="M11" s="13" t="n">
+        <v>106444.0</v>
+      </c>
+      <c r="N11" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O11" s="13" t="n">
+        <v>1436996.0</v>
+      </c>
+      <c r="P11" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q11" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>C25MSF</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>11154</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>15/10/2025</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>3502469464</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH PHÚ SỸ FOOD</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>Số 149 , Đường Ngô Đức Kế, Phường Tam Thắng,Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I12" s="7" t="inlineStr">
+        <is>
+          <t>3502245376</t>
+        </is>
+      </c>
+      <c r="J12" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
+        </is>
+      </c>
+      <c r="K12" s="6"/>
+      <c r="L12" s="13" t="n">
+        <v>1514286.0</v>
+      </c>
+      <c r="M12" s="13" t="n">
+        <v>75714.0</v>
+      </c>
+      <c r="N12" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O12" s="13" t="n">
+        <v>1590000.0</v>
+      </c>
+      <c r="P12" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q12" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="n">
+        <v>7.0</v>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>C25MHN</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>2176</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>11/10/2025</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>3502546101</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI - DỊCH VỤ GAS HOÀNG NAM</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>C5-2/1 TT Đô Thị Chí Linh, Phường Rạch Dừa, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I13" s="7" t="inlineStr">
+        <is>
+          <t>3502245376</t>
+        </is>
+      </c>
+      <c r="J13" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
+        </is>
+      </c>
+      <c r="K13" s="6"/>
+      <c r="L13" s="13" t="n">
+        <v>551852.0</v>
+      </c>
+      <c r="M13" s="13" t="n">
+        <v>44148.0</v>
+      </c>
+      <c r="N13" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O13" s="13" t="n">
+        <v>596000.0</v>
+      </c>
+      <c r="P13" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q13" s="6" t="inlineStr">
         <is>
           <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
         </is>

--- a/Hoadon/HDVao/10/HDDienTuMayTinhTien.xlsx
+++ b/Hoadon/HDVao/10/HDDienTuMayTinhTien.xlsx
@@ -308,62 +308,57 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>C25MVT</t>
+          <t>C25MVC</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>208364</t>
+          <t>134</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>03/10/2025</t>
+          <t>14/10/2025</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>0302249586-009</t>
+          <t>026078008681</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>CHI NHÁNH CÔNG TY TNHH MM MEGA MARKET (VIỆT NAM) TẠI TỈNH BÀ RỊA - VŨNG TÀU</t>
+          <t>Hộ Kinh Doanh Trần Văn Cường (Phường 8)</t>
         </is>
       </c>
       <c r="H7" s="6" t="inlineStr">
         <is>
-          <t>Đường 2 tháng 9 (Quốc lộ 51B), Khu phố 1, Phường Phước Thắng, Thành phố Hồ Chí Minh</t>
+          <t>209 đường Bình Giã, Phường Tam Thắng, Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I7" s="7" t="inlineStr">
         <is>
-          <t>3502245376</t>
+          <t>3502469834</t>
         </is>
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
-          <t>CONG TY CO PHAN DAU TU XAY DUNG THUONG MAI
-DICH VU KY THUAT H &amp; V</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
         </is>
       </c>
       <c r="K7" s="6"/>
-      <c r="L7" s="13" t="n">
-        <v>1707183.0</v>
-      </c>
-      <c r="M7" s="13" t="n">
-        <v>170718.0</v>
-      </c>
+      <c r="L7" s="13"/>
+      <c r="M7" s="13"/>
       <c r="N7" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O7" s="13" t="n">
-        <v>1877901.0</v>
+        <v>2.039E7</v>
       </c>
       <c r="P7" s="6" t="inlineStr">
         <is>
@@ -382,62 +377,57 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>C25MVT</t>
+          <t>C25MVC</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>208367</t>
+          <t>137</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>03/10/2025</t>
+          <t>15/10/2025</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>0302249586-009</t>
+          <t>026078008681</t>
         </is>
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>CHI NHÁNH CÔNG TY TNHH MM MEGA MARKET (VIỆT NAM) TẠI TỈNH BÀ RỊA - VŨNG TÀU</t>
+          <t>Hộ Kinh Doanh Trần Văn Cường (Phường 8)</t>
         </is>
       </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
-          <t>Đường 2 tháng 9 (Quốc lộ 51B), Khu phố 1, Phường Phước Thắng, Thành phố Hồ Chí Minh</t>
+          <t>209 đường Bình Giã, Phường Tam Thắng, Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I8" s="7" t="inlineStr">
         <is>
-          <t>3502245376</t>
+          <t>3502469834</t>
         </is>
       </c>
       <c r="J8" s="6" t="inlineStr">
         <is>
-          <t>CONG TY CO PHAN DAU TU XAY DUNG THUONG MAI
-DICH VU KY THUAT H &amp; V</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
         </is>
       </c>
       <c r="K8" s="6"/>
-      <c r="L8" s="13" t="n">
-        <v>1184229.0</v>
-      </c>
-      <c r="M8" s="13" t="n">
-        <v>92481.0</v>
-      </c>
+      <c r="L8" s="13"/>
+      <c r="M8" s="13"/>
       <c r="N8" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O8" s="13" t="n">
-        <v>1276710.0</v>
+        <v>5982500.0</v>
       </c>
       <c r="P8" s="6" t="inlineStr">
         <is>
@@ -456,62 +446,57 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>C25MVT</t>
+          <t>C25MTL</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>213473</t>
+          <t>10602</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>10/10/2025</t>
+          <t>04/10/2025</t>
         </is>
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>0302249586-009</t>
+          <t>037165003053</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>CHI NHÁNH CÔNG TY TNHH MM MEGA MARKET (VIỆT NAM) TẠI TỈNH BÀ RỊA - VŨNG TÀU</t>
+          <t>HỘ KINH DOANH CỬA HÀNG THÀNH LẬP 1</t>
         </is>
       </c>
       <c r="H9" s="6" t="inlineStr">
         <is>
-          <t>Đường 2 tháng 9 (Quốc lộ 51B), Khu phố 1, Phường Phước Thắng, Thành phố Hồ Chí Minh</t>
+          <t>15A Kha Vạn Cân, Phường Tam Thắng, Thành phố Hồ Chí Minh, Việt Nam.</t>
         </is>
       </c>
       <c r="I9" s="7" t="inlineStr">
         <is>
-          <t>3502245376</t>
+          <t>3502469834</t>
         </is>
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
-          <t>CONG TY CO PHAN DAU TU XAY DUNG THUONG MAI
-DICH VU KY THUAT H &amp; V</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
         </is>
       </c>
       <c r="K9" s="6"/>
-      <c r="L9" s="13" t="n">
-        <v>828183.0</v>
-      </c>
-      <c r="M9" s="13" t="n">
-        <v>82818.0</v>
-      </c>
+      <c r="L9" s="13"/>
+      <c r="M9" s="13"/>
       <c r="N9" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O9" s="13" t="n">
-        <v>911001.0</v>
+        <v>1200000.0</v>
       </c>
       <c r="P9" s="6" t="inlineStr">
         <is>
@@ -530,62 +515,57 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>C25MVT</t>
+          <t>C25MTL</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>213475</t>
+          <t>10603</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>10/10/2025</t>
+          <t>04/10/2025</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>0302249586-009</t>
+          <t>037165003053</t>
         </is>
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>CHI NHÁNH CÔNG TY TNHH MM MEGA MARKET (VIỆT NAM) TẠI TỈNH BÀ RỊA - VŨNG TÀU</t>
+          <t>HỘ KINH DOANH CỬA HÀNG THÀNH LẬP 1</t>
         </is>
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>Đường 2 tháng 9 (Quốc lộ 51B), Khu phố 1, Phường Phước Thắng, Thành phố Hồ Chí Minh</t>
+          <t>15A Kha Vạn Cân, Phường Tam Thắng, Thành phố Hồ Chí Minh, Việt Nam.</t>
         </is>
       </c>
       <c r="I10" s="7" t="inlineStr">
         <is>
-          <t>3502245376</t>
+          <t>3502469834</t>
         </is>
       </c>
       <c r="J10" s="6" t="inlineStr">
         <is>
-          <t>CONG TY CO PHAN DAU TU XAY DUNG THUONG MAI
-DICH VU KY THUAT H &amp; V</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
         </is>
       </c>
       <c r="K10" s="6"/>
-      <c r="L10" s="13" t="n">
-        <v>2527250.0</v>
-      </c>
-      <c r="M10" s="13" t="n">
-        <v>126361.0</v>
-      </c>
+      <c r="L10" s="13"/>
+      <c r="M10" s="13"/>
       <c r="N10" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O10" s="13" t="n">
-        <v>2653611.0</v>
+        <v>2364000.0</v>
       </c>
       <c r="P10" s="6" t="inlineStr">
         <is>
@@ -604,62 +584,57 @@
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>C25MVT</t>
+          <t>C25MTL</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>215275</t>
+          <t>10798</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t>12/10/2025</t>
+          <t>18/10/2025</t>
         </is>
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>0302249586-009</t>
+          <t>037165003053</t>
         </is>
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>CHI NHÁNH CÔNG TY TNHH MM MEGA MARKET (VIỆT NAM) TẠI TỈNH BÀ RỊA - VŨNG TÀU</t>
+          <t>HỘ KINH DOANH CỬA HÀNG THÀNH LẬP 1</t>
         </is>
       </c>
       <c r="H11" s="6" t="inlineStr">
         <is>
-          <t>Đường 2 tháng 9 (Quốc lộ 51B), Khu phố 1, Phường Phước Thắng, Thành phố Hồ Chí Minh</t>
+          <t>15A Kha Vạn Cân, Phường Tam Thắng, Thành phố Hồ Chí Minh, Việt Nam.</t>
         </is>
       </c>
       <c r="I11" s="7" t="inlineStr">
         <is>
-          <t>3502245376</t>
+          <t>3502469834</t>
         </is>
       </c>
       <c r="J11" s="6" t="inlineStr">
         <is>
-          <t>CONG TY CO PHAN DAU TU XAY DUNG THUONG MAI
-DICH VU KY THUAT H &amp; V</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
         </is>
       </c>
       <c r="K11" s="6"/>
-      <c r="L11" s="13" t="n">
-        <v>1330552.0</v>
-      </c>
-      <c r="M11" s="13" t="n">
-        <v>106444.0</v>
-      </c>
+      <c r="L11" s="13"/>
+      <c r="M11" s="13"/>
       <c r="N11" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O11" s="13" t="n">
-        <v>1436996.0</v>
+        <v>1200000.0</v>
       </c>
       <c r="P11" s="6" t="inlineStr">
         <is>
@@ -678,61 +653,57 @@
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>C25MSF</t>
+          <t>C25MTL</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>11154</t>
+          <t>10799</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>15/10/2025</t>
+          <t>18/10/2025</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>3502469464</t>
+          <t>037165003053</t>
         </is>
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH PHÚ SỸ FOOD</t>
+          <t>HỘ KINH DOANH CỬA HÀNG THÀNH LẬP 1</t>
         </is>
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>Số 149 , Đường Ngô Đức Kế, Phường Tam Thắng,Thành Phố Hồ Chí Minh, Việt Nam</t>
+          <t>15A Kha Vạn Cân, Phường Tam Thắng, Thành phố Hồ Chí Minh, Việt Nam.</t>
         </is>
       </c>
       <c r="I12" s="7" t="inlineStr">
         <is>
-          <t>3502245376</t>
+          <t>3502469834</t>
         </is>
       </c>
       <c r="J12" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
         </is>
       </c>
       <c r="K12" s="6"/>
-      <c r="L12" s="13" t="n">
-        <v>1514286.0</v>
-      </c>
-      <c r="M12" s="13" t="n">
-        <v>75714.0</v>
-      </c>
+      <c r="L12" s="13"/>
+      <c r="M12" s="13"/>
       <c r="N12" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O12" s="13" t="n">
-        <v>1590000.0</v>
+        <v>786000.0</v>
       </c>
       <c r="P12" s="6" t="inlineStr">
         <is>
@@ -751,61 +722,57 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>C25MHN</t>
+          <t>C25MYY</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>2176</t>
+          <t>2367</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>11/10/2025</t>
+          <t>18/10/2025</t>
         </is>
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
-          <t>3502546101</t>
+          <t>037184012312</t>
         </is>
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI - DỊCH VỤ GAS HOÀNG NAM</t>
+          <t>HỘ KINH DOANH PHẠM HẢI QUỲNH ANH</t>
         </is>
       </c>
       <c r="H13" s="6" t="inlineStr">
         <is>
-          <t>C5-2/1 TT Đô Thị Chí Linh, Phường Rạch Dừa, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 45B đường Đoàn Thị Điểm, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam.</t>
         </is>
       </c>
       <c r="I13" s="7" t="inlineStr">
         <is>
-          <t>3502245376</t>
+          <t>3502469834</t>
         </is>
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
         </is>
       </c>
       <c r="K13" s="6"/>
-      <c r="L13" s="13" t="n">
-        <v>551852.0</v>
-      </c>
-      <c r="M13" s="13" t="n">
-        <v>44148.0</v>
-      </c>
+      <c r="L13" s="13"/>
+      <c r="M13" s="13"/>
       <c r="N13" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O13" s="13" t="n">
-        <v>596000.0</v>
+        <v>4950000.0</v>
       </c>
       <c r="P13" s="6" t="inlineStr">
         <is>
@@ -813,6 +780,213 @@
         </is>
       </c>
       <c r="Q13" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="n">
+        <v>8.0</v>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>C25MTH</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>13/10/2025</t>
+        </is>
+      </c>
+      <c r="F14" s="7" t="inlineStr">
+        <is>
+          <t>077094004359</t>
+        </is>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>HỘ KINH DOANH HẢI SẢN TƯ HÀ</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>10 Hoàng Hoa Thám, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I14" s="7" t="inlineStr">
+        <is>
+          <t>3502469834</t>
+        </is>
+      </c>
+      <c r="J14" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K14" s="6"/>
+      <c r="L14" s="13"/>
+      <c r="M14" s="13"/>
+      <c r="N14" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O14" s="13" t="n">
+        <v>4365000.0</v>
+      </c>
+      <c r="P14" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q14" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="n">
+        <v>9.0</v>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>C25MND</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>15/10/2025</t>
+        </is>
+      </c>
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t>095194004728</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>HỘ KINH DOANH NGUYỄN THỊ NGỌC DIỆP</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>Lô 92 Khu chợ đêm Quốc lộ 56, Phường Bà Rịa, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I15" s="7" t="inlineStr">
+        <is>
+          <t>3502469834</t>
+        </is>
+      </c>
+      <c r="J15" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K15" s="6"/>
+      <c r="L15" s="13"/>
+      <c r="M15" s="13"/>
+      <c r="N15" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O15" s="13" t="n">
+        <v>3420000.0</v>
+      </c>
+      <c r="P15" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q15" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="n">
+        <v>10.0</v>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>C25MND</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>17/10/2025</t>
+        </is>
+      </c>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>095194004728</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>HỘ KINH DOANH NGUYỄN THỊ NGỌC DIỆP</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>Lô 92 Khu chợ đêm Quốc lộ 56, Phường Bà Rịa, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I16" s="7" t="inlineStr">
+        <is>
+          <t>3502469834</t>
+        </is>
+      </c>
+      <c r="J16" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K16" s="6"/>
+      <c r="L16" s="13"/>
+      <c r="M16" s="13"/>
+      <c r="N16" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O16" s="13" t="n">
+        <v>3060000.0</v>
+      </c>
+      <c r="P16" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q16" s="6" t="inlineStr">
         <is>
           <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
         </is>

--- a/Hoadon/HDVao/10/HDDienTuMayTinhTien.xlsx
+++ b/Hoadon/HDVao/10/HDDienTuMayTinhTien.xlsx
@@ -308,57 +308,62 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>C25MVC</t>
+          <t>C25MVT</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>208364</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>14/10/2025</t>
+          <t>03/10/2025</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>026078008681</t>
+          <t>0302249586-009</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>Hộ Kinh Doanh Trần Văn Cường (Phường 8)</t>
+          <t>CHI NHÁNH CÔNG TY TNHH MM MEGA MARKET (VIỆT NAM) TẠI TỈNH BÀ RỊA - VŨNG TÀU</t>
         </is>
       </c>
       <c r="H7" s="6" t="inlineStr">
         <is>
-          <t>209 đường Bình Giã, Phường Tam Thắng, Hồ Chí Minh, Việt Nam</t>
+          <t>Đường 2 tháng 9 (Quốc lộ 51B), Khu phố 1, Phường Phước Thắng, Thành phố Hồ Chí Minh</t>
         </is>
       </c>
       <c r="I7" s="7" t="inlineStr">
         <is>
-          <t>3502469834</t>
+          <t>3502245376</t>
         </is>
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+          <t>CONG TY CO PHAN DAU TU XAY DUNG THUONG MAI
+DICH VU KY THUAT H &amp; V</t>
         </is>
       </c>
       <c r="K7" s="6"/>
-      <c r="L7" s="13"/>
-      <c r="M7" s="13"/>
+      <c r="L7" s="13" t="n">
+        <v>1707183.0</v>
+      </c>
+      <c r="M7" s="13" t="n">
+        <v>170718.0</v>
+      </c>
       <c r="N7" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O7" s="13" t="n">
-        <v>2.039E7</v>
+        <v>1877901.0</v>
       </c>
       <c r="P7" s="6" t="inlineStr">
         <is>
@@ -377,57 +382,62 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>C25MVC</t>
+          <t>C25MVT</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>208367</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>15/10/2025</t>
+          <t>03/10/2025</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>026078008681</t>
+          <t>0302249586-009</t>
         </is>
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>Hộ Kinh Doanh Trần Văn Cường (Phường 8)</t>
+          <t>CHI NHÁNH CÔNG TY TNHH MM MEGA MARKET (VIỆT NAM) TẠI TỈNH BÀ RỊA - VŨNG TÀU</t>
         </is>
       </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
-          <t>209 đường Bình Giã, Phường Tam Thắng, Hồ Chí Minh, Việt Nam</t>
+          <t>Đường 2 tháng 9 (Quốc lộ 51B), Khu phố 1, Phường Phước Thắng, Thành phố Hồ Chí Minh</t>
         </is>
       </c>
       <c r="I8" s="7" t="inlineStr">
         <is>
-          <t>3502469834</t>
+          <t>3502245376</t>
         </is>
       </c>
       <c r="J8" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+          <t>CONG TY CO PHAN DAU TU XAY DUNG THUONG MAI
+DICH VU KY THUAT H &amp; V</t>
         </is>
       </c>
       <c r="K8" s="6"/>
-      <c r="L8" s="13"/>
-      <c r="M8" s="13"/>
+      <c r="L8" s="13" t="n">
+        <v>1184229.0</v>
+      </c>
+      <c r="M8" s="13" t="n">
+        <v>92481.0</v>
+      </c>
       <c r="N8" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O8" s="13" t="n">
-        <v>5982500.0</v>
+        <v>1276710.0</v>
       </c>
       <c r="P8" s="6" t="inlineStr">
         <is>
@@ -446,57 +456,62 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>C25MTL</t>
+          <t>C25MVT</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>10602</t>
+          <t>213473</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>04/10/2025</t>
+          <t>10/10/2025</t>
         </is>
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>037165003053</t>
+          <t>0302249586-009</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>HỘ KINH DOANH CỬA HÀNG THÀNH LẬP 1</t>
+          <t>CHI NHÁNH CÔNG TY TNHH MM MEGA MARKET (VIỆT NAM) TẠI TỈNH BÀ RỊA - VŨNG TÀU</t>
         </is>
       </c>
       <c r="H9" s="6" t="inlineStr">
         <is>
-          <t>15A Kha Vạn Cân, Phường Tam Thắng, Thành phố Hồ Chí Minh, Việt Nam.</t>
+          <t>Đường 2 tháng 9 (Quốc lộ 51B), Khu phố 1, Phường Phước Thắng, Thành phố Hồ Chí Minh</t>
         </is>
       </c>
       <c r="I9" s="7" t="inlineStr">
         <is>
-          <t>3502469834</t>
+          <t>3502245376</t>
         </is>
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+          <t>CONG TY CO PHAN DAU TU XAY DUNG THUONG MAI
+DICH VU KY THUAT H &amp; V</t>
         </is>
       </c>
       <c r="K9" s="6"/>
-      <c r="L9" s="13"/>
-      <c r="M9" s="13"/>
+      <c r="L9" s="13" t="n">
+        <v>828183.0</v>
+      </c>
+      <c r="M9" s="13" t="n">
+        <v>82818.0</v>
+      </c>
       <c r="N9" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O9" s="13" t="n">
-        <v>1200000.0</v>
+        <v>911001.0</v>
       </c>
       <c r="P9" s="6" t="inlineStr">
         <is>
@@ -515,57 +530,62 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>C25MTL</t>
+          <t>C25MVT</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>10603</t>
+          <t>213475</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>04/10/2025</t>
+          <t>10/10/2025</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>037165003053</t>
+          <t>0302249586-009</t>
         </is>
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>HỘ KINH DOANH CỬA HÀNG THÀNH LẬP 1</t>
+          <t>CHI NHÁNH CÔNG TY TNHH MM MEGA MARKET (VIỆT NAM) TẠI TỈNH BÀ RỊA - VŨNG TÀU</t>
         </is>
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>15A Kha Vạn Cân, Phường Tam Thắng, Thành phố Hồ Chí Minh, Việt Nam.</t>
+          <t>Đường 2 tháng 9 (Quốc lộ 51B), Khu phố 1, Phường Phước Thắng, Thành phố Hồ Chí Minh</t>
         </is>
       </c>
       <c r="I10" s="7" t="inlineStr">
         <is>
-          <t>3502469834</t>
+          <t>3502245376</t>
         </is>
       </c>
       <c r="J10" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+          <t>CONG TY CO PHAN DAU TU XAY DUNG THUONG MAI
+DICH VU KY THUAT H &amp; V</t>
         </is>
       </c>
       <c r="K10" s="6"/>
-      <c r="L10" s="13"/>
-      <c r="M10" s="13"/>
+      <c r="L10" s="13" t="n">
+        <v>2527250.0</v>
+      </c>
+      <c r="M10" s="13" t="n">
+        <v>126361.0</v>
+      </c>
       <c r="N10" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O10" s="13" t="n">
-        <v>2364000.0</v>
+        <v>2653611.0</v>
       </c>
       <c r="P10" s="6" t="inlineStr">
         <is>
@@ -584,57 +604,62 @@
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>C25MTL</t>
+          <t>C25MVT</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>10798</t>
+          <t>215275</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t>18/10/2025</t>
+          <t>12/10/2025</t>
         </is>
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>037165003053</t>
+          <t>0302249586-009</t>
         </is>
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>HỘ KINH DOANH CỬA HÀNG THÀNH LẬP 1</t>
+          <t>CHI NHÁNH CÔNG TY TNHH MM MEGA MARKET (VIỆT NAM) TẠI TỈNH BÀ RỊA - VŨNG TÀU</t>
         </is>
       </c>
       <c r="H11" s="6" t="inlineStr">
         <is>
-          <t>15A Kha Vạn Cân, Phường Tam Thắng, Thành phố Hồ Chí Minh, Việt Nam.</t>
+          <t>Đường 2 tháng 9 (Quốc lộ 51B), Khu phố 1, Phường Phước Thắng, Thành phố Hồ Chí Minh</t>
         </is>
       </c>
       <c r="I11" s="7" t="inlineStr">
         <is>
-          <t>3502469834</t>
+          <t>3502245376</t>
         </is>
       </c>
       <c r="J11" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+          <t>CONG TY CO PHAN DAU TU XAY DUNG THUONG MAI
+DICH VU KY THUAT H &amp; V</t>
         </is>
       </c>
       <c r="K11" s="6"/>
-      <c r="L11" s="13"/>
-      <c r="M11" s="13"/>
+      <c r="L11" s="13" t="n">
+        <v>1330552.0</v>
+      </c>
+      <c r="M11" s="13" t="n">
+        <v>106444.0</v>
+      </c>
       <c r="N11" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O11" s="13" t="n">
-        <v>1200000.0</v>
+        <v>1436996.0</v>
       </c>
       <c r="P11" s="6" t="inlineStr">
         <is>
@@ -653,57 +678,62 @@
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>C25MTL</t>
+          <t>C25MVT</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>10799</t>
+          <t>225524</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>18/10/2025</t>
+          <t>26/10/2025</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>037165003053</t>
+          <t>0302249586-009</t>
         </is>
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>HỘ KINH DOANH CỬA HÀNG THÀNH LẬP 1</t>
+          <t>CHI NHÁNH CÔNG TY TNHH MM MEGA MARKET (VIỆT NAM) TẠI TỈNH BÀ RỊA - VŨNG TÀU</t>
         </is>
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>15A Kha Vạn Cân, Phường Tam Thắng, Thành phố Hồ Chí Minh, Việt Nam.</t>
+          <t>Đường 2 tháng 9 (Quốc lộ 51B), Khu phố 1, Phường Phước Thắng, Thành phố Hồ Chí Minh</t>
         </is>
       </c>
       <c r="I12" s="7" t="inlineStr">
         <is>
-          <t>3502469834</t>
+          <t>3502245376</t>
         </is>
       </c>
       <c r="J12" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+          <t>CONG TY CO PHAN DAU TU XAY DUNG THUONG MAI
+DICH VU KY THUAT H &amp; V</t>
         </is>
       </c>
       <c r="K12" s="6"/>
-      <c r="L12" s="13"/>
-      <c r="M12" s="13"/>
+      <c r="L12" s="13" t="n">
+        <v>856359.0</v>
+      </c>
+      <c r="M12" s="13" t="n">
+        <v>72945.0</v>
+      </c>
       <c r="N12" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O12" s="13" t="n">
-        <v>786000.0</v>
+        <v>929304.0</v>
       </c>
       <c r="P12" s="6" t="inlineStr">
         <is>
@@ -722,57 +752,61 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>C25MYY</t>
+          <t>C25MSF</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>2367</t>
+          <t>11154</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>18/10/2025</t>
+          <t>15/10/2025</t>
         </is>
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
-          <t>037184012312</t>
+          <t>3502469464</t>
         </is>
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>HỘ KINH DOANH PHẠM HẢI QUỲNH ANH</t>
+          <t>CÔNG TY TNHH PHÚ SỸ FOOD</t>
         </is>
       </c>
       <c r="H13" s="6" t="inlineStr">
         <is>
-          <t>Số 45B đường Đoàn Thị Điểm, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam.</t>
+          <t>Số 149 , Đường Ngô Đức Kế, Phường Tam Thắng,Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I13" s="7" t="inlineStr">
         <is>
-          <t>3502469834</t>
+          <t>3502245376</t>
         </is>
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
         </is>
       </c>
       <c r="K13" s="6"/>
-      <c r="L13" s="13"/>
-      <c r="M13" s="13"/>
+      <c r="L13" s="13" t="n">
+        <v>1514286.0</v>
+      </c>
+      <c r="M13" s="13" t="n">
+        <v>75714.0</v>
+      </c>
       <c r="N13" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O13" s="13" t="n">
-        <v>4950000.0</v>
+        <v>1590000.0</v>
       </c>
       <c r="P13" s="6" t="inlineStr">
         <is>
@@ -791,57 +825,61 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>C25MTH</t>
+          <t>C25MHN</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>2176</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>13/10/2025</t>
+          <t>11/10/2025</t>
         </is>
       </c>
       <c r="F14" s="7" t="inlineStr">
         <is>
-          <t>077094004359</t>
+          <t>3502546101</t>
         </is>
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>HỘ KINH DOANH HẢI SẢN TƯ HÀ</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI - DỊCH VỤ GAS HOÀNG NAM</t>
         </is>
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
-          <t>10 Hoàng Hoa Thám, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>C5-2/1 TT Đô Thị Chí Linh, Phường Rạch Dừa, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I14" s="7" t="inlineStr">
         <is>
-          <t>3502469834</t>
+          <t>3502245376</t>
         </is>
       </c>
       <c r="J14" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
         </is>
       </c>
       <c r="K14" s="6"/>
-      <c r="L14" s="13"/>
-      <c r="M14" s="13"/>
+      <c r="L14" s="13" t="n">
+        <v>551852.0</v>
+      </c>
+      <c r="M14" s="13" t="n">
+        <v>44148.0</v>
+      </c>
       <c r="N14" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O14" s="13" t="n">
-        <v>4365000.0</v>
+        <v>596000.0</v>
       </c>
       <c r="P14" s="6" t="inlineStr">
         <is>
@@ -849,144 +887,6 @@
         </is>
       </c>
       <c r="Q14" s="6" t="inlineStr">
-        <is>
-          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="n">
-        <v>9.0</v>
-      </c>
-      <c r="B15" s="7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>C25MND</t>
-        </is>
-      </c>
-      <c r="D15" s="7" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="E15" s="7" t="inlineStr">
-        <is>
-          <t>15/10/2025</t>
-        </is>
-      </c>
-      <c r="F15" s="7" t="inlineStr">
-        <is>
-          <t>095194004728</t>
-        </is>
-      </c>
-      <c r="G15" s="6" t="inlineStr">
-        <is>
-          <t>HỘ KINH DOANH NGUYỄN THỊ NGỌC DIỆP</t>
-        </is>
-      </c>
-      <c r="H15" s="6" t="inlineStr">
-        <is>
-          <t>Lô 92 Khu chợ đêm Quốc lộ 56, Phường Bà Rịa, Thành Phố Hồ Chí Minh, Việt Nam</t>
-        </is>
-      </c>
-      <c r="I15" s="7" t="inlineStr">
-        <is>
-          <t>3502469834</t>
-        </is>
-      </c>
-      <c r="J15" s="6" t="inlineStr">
-        <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
-        </is>
-      </c>
-      <c r="K15" s="6"/>
-      <c r="L15" s="13"/>
-      <c r="M15" s="13"/>
-      <c r="N15" s="13" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="O15" s="13" t="n">
-        <v>3420000.0</v>
-      </c>
-      <c r="P15" s="6" t="inlineStr">
-        <is>
-          <t>Hóa đơn mới</t>
-        </is>
-      </c>
-      <c r="Q15" s="6" t="inlineStr">
-        <is>
-          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="n">
-        <v>10.0</v>
-      </c>
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t>C25MND</t>
-        </is>
-      </c>
-      <c r="D16" s="7" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="E16" s="7" t="inlineStr">
-        <is>
-          <t>17/10/2025</t>
-        </is>
-      </c>
-      <c r="F16" s="7" t="inlineStr">
-        <is>
-          <t>095194004728</t>
-        </is>
-      </c>
-      <c r="G16" s="6" t="inlineStr">
-        <is>
-          <t>HỘ KINH DOANH NGUYỄN THỊ NGỌC DIỆP</t>
-        </is>
-      </c>
-      <c r="H16" s="6" t="inlineStr">
-        <is>
-          <t>Lô 92 Khu chợ đêm Quốc lộ 56, Phường Bà Rịa, Thành Phố Hồ Chí Minh, Việt Nam</t>
-        </is>
-      </c>
-      <c r="I16" s="7" t="inlineStr">
-        <is>
-          <t>3502469834</t>
-        </is>
-      </c>
-      <c r="J16" s="6" t="inlineStr">
-        <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
-        </is>
-      </c>
-      <c r="K16" s="6"/>
-      <c r="L16" s="13"/>
-      <c r="M16" s="13"/>
-      <c r="N16" s="13" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="O16" s="13" t="n">
-        <v>3060000.0</v>
-      </c>
-      <c r="P16" s="6" t="inlineStr">
-        <is>
-          <t>Hóa đơn mới</t>
-        </is>
-      </c>
-      <c r="Q16" s="6" t="inlineStr">
         <is>
           <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
         </is>

--- a/Hoadon/HDVao/10/HDDienTuMayTinhTien.xlsx
+++ b/Hoadon/HDVao/10/HDDienTuMayTinhTien.xlsx
@@ -313,57 +313,54 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>C25MVT</t>
+          <t>C25MCV</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>208364</t>
+          <t>3413123</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>03/10/2025</t>
+          <t>24/10/2025</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>0302249586-009</t>
+          <t>0102721191-001</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>CHI NHÁNH CÔNG TY TNHH MM MEGA MARKET (VIỆT NAM) TẠI TỈNH BÀ RỊA - VŨNG TÀU</t>
+          <t>CÔNG TY CỔ PHẦN TẬP ĐOÀN GOLDEN GATE - CHI NHÁNH MIỀN NAM</t>
         </is>
       </c>
       <c r="H7" s="6" t="inlineStr">
         <is>
-          <t>Đường 2 tháng 9 (Quốc lộ 51B), Khu phố 1, Phường Phước Thắng, Thành phố Hồ Chí Minh</t>
+          <t>Tầng 7 TTTM Gigamall, Số 240-242 Phạm Văn Đồng, Phường Hiệp Bình, TP Hồ Chí Minh</t>
         </is>
       </c>
       <c r="I7" s="7" t="inlineStr">
         <is>
-          <t>3502245376</t>
+          <t>3500779171</t>
         </is>
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
-          <t>CONG TY CO PHAN DAU TU XAY DUNG THUONG MAI
-DICH VU KY THUAT H &amp; V</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ XÂY DỰNG ĐẠI THÀNH CÔNG</t>
         </is>
       </c>
       <c r="K7" s="6"/>
       <c r="L7" s="13" t="n">
-        <v>1707183.0</v>
+        <v>2052000.0</v>
       </c>
       <c r="M7" s="13" t="n">
-        <v>170718.0</v>
-      </c>
-      <c r="N7" s="13" t="n">
-        <v>0.0</v>
-      </c>
+        <v>164160.0</v>
+      </c>
+      <c r="N7" s="13"/>
       <c r="O7" s="13" t="n">
-        <v>1877901.0</v>
+        <v>2216160.0</v>
       </c>
       <c r="P7" s="6" t="inlineStr">
         <is>
@@ -382,62 +379,55 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>C25MVT</t>
+          <t>C25MKD</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>208367</t>
+          <t>428</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>03/10/2025</t>
+          <t>20/10/2025</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>0302249586-009</t>
+          <t>052094003601</t>
         </is>
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>CHI NHÁNH CÔNG TY TNHH MM MEGA MARKET (VIỆT NAM) TẠI TỈNH BÀ RỊA - VŨNG TÀU</t>
+          <t>HỘ KINH DOANH GOLD 79</t>
         </is>
       </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
-          <t>Đường 2 tháng 9 (Quốc lộ 51B), Khu phố 1, Phường Phước Thắng, Thành phố Hồ Chí Minh</t>
+          <t>Số 595, Đường Phạm Văn Đồng, Phường Bà Rịa, Thành Phố Hồ Chí Minh</t>
         </is>
       </c>
       <c r="I8" s="7" t="inlineStr">
         <is>
-          <t>3502245376</t>
+          <t>3500779171</t>
         </is>
       </c>
       <c r="J8" s="6" t="inlineStr">
         <is>
-          <t>CONG TY CO PHAN DAU TU XAY DUNG THUONG MAI
-DICH VU KY THUAT H &amp; V</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ XÂY DỰNG ĐẠI THÀNH CÔNG</t>
         </is>
       </c>
       <c r="K8" s="6"/>
-      <c r="L8" s="13" t="n">
-        <v>1184229.0</v>
-      </c>
-      <c r="M8" s="13" t="n">
-        <v>92481.0</v>
-      </c>
-      <c r="N8" s="13" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="L8" s="13"/>
+      <c r="M8" s="13"/>
+      <c r="N8" s="13"/>
       <c r="O8" s="13" t="n">
-        <v>1276710.0</v>
+        <v>2334000.0</v>
       </c>
       <c r="P8" s="6" t="inlineStr">
         <is>
@@ -461,57 +451,56 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>C25MVT</t>
+          <t>C25MKT</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>213473</t>
+          <t>87</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>10/10/2025</t>
+          <t>03/10/2025</t>
         </is>
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>0302249586-009</t>
+          <t>3502243040</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>CHI NHÁNH CÔNG TY TNHH MM MEGA MARKET (VIỆT NAM) TẠI TỈNH BÀ RỊA - VŨNG TÀU</t>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN NGỌC KIM THANH</t>
         </is>
       </c>
       <c r="H9" s="6" t="inlineStr">
         <is>
-          <t>Đường 2 tháng 9 (Quốc lộ 51B), Khu phố 1, Phường Phước Thắng, Thành phố Hồ Chí Minh</t>
+          <t>Khu phố Chu Hải, Phường Tân Hải, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I9" s="7" t="inlineStr">
         <is>
-          <t>3502245376</t>
+          <t>3500779171</t>
         </is>
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
-          <t>CONG TY CO PHAN DAU TU XAY DUNG THUONG MAI
-DICH VU KY THUAT H &amp; V</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ XÂY DỰNG ĐẠI THÀNH CÔNG</t>
         </is>
       </c>
       <c r="K9" s="6"/>
       <c r="L9" s="13" t="n">
-        <v>828183.0</v>
+        <v>2.47055E8</v>
       </c>
       <c r="M9" s="13" t="n">
-        <v>82818.0</v>
+        <v>1.97644E7</v>
       </c>
       <c r="N9" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O9" s="13" t="n">
-        <v>911001.0</v>
+        <v>2.668194E8</v>
       </c>
       <c r="P9" s="6" t="inlineStr">
         <is>
@@ -519,374 +508,6 @@
         </is>
       </c>
       <c r="Q9" s="6" t="inlineStr">
-        <is>
-          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="n">
-        <v>4.0</v>
-      </c>
-      <c r="B10" s="7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>C25MVT</t>
-        </is>
-      </c>
-      <c r="D10" s="7" t="inlineStr">
-        <is>
-          <t>213475</t>
-        </is>
-      </c>
-      <c r="E10" s="7" t="inlineStr">
-        <is>
-          <t>10/10/2025</t>
-        </is>
-      </c>
-      <c r="F10" s="7" t="inlineStr">
-        <is>
-          <t>0302249586-009</t>
-        </is>
-      </c>
-      <c r="G10" s="6" t="inlineStr">
-        <is>
-          <t>CHI NHÁNH CÔNG TY TNHH MM MEGA MARKET (VIỆT NAM) TẠI TỈNH BÀ RỊA - VŨNG TÀU</t>
-        </is>
-      </c>
-      <c r="H10" s="6" t="inlineStr">
-        <is>
-          <t>Đường 2 tháng 9 (Quốc lộ 51B), Khu phố 1, Phường Phước Thắng, Thành phố Hồ Chí Minh</t>
-        </is>
-      </c>
-      <c r="I10" s="7" t="inlineStr">
-        <is>
-          <t>3502245376</t>
-        </is>
-      </c>
-      <c r="J10" s="6" t="inlineStr">
-        <is>
-          <t>CONG TY CO PHAN DAU TU XAY DUNG THUONG MAI
-DICH VU KY THUAT H &amp; V</t>
-        </is>
-      </c>
-      <c r="K10" s="6"/>
-      <c r="L10" s="13" t="n">
-        <v>2527250.0</v>
-      </c>
-      <c r="M10" s="13" t="n">
-        <v>126361.0</v>
-      </c>
-      <c r="N10" s="13" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="O10" s="13" t="n">
-        <v>2653611.0</v>
-      </c>
-      <c r="P10" s="6" t="inlineStr">
-        <is>
-          <t>Hóa đơn mới</t>
-        </is>
-      </c>
-      <c r="Q10" s="6" t="inlineStr">
-        <is>
-          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="n">
-        <v>5.0</v>
-      </c>
-      <c r="B11" s="7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>C25MVT</t>
-        </is>
-      </c>
-      <c r="D11" s="7" t="inlineStr">
-        <is>
-          <t>215275</t>
-        </is>
-      </c>
-      <c r="E11" s="7" t="inlineStr">
-        <is>
-          <t>12/10/2025</t>
-        </is>
-      </c>
-      <c r="F11" s="7" t="inlineStr">
-        <is>
-          <t>0302249586-009</t>
-        </is>
-      </c>
-      <c r="G11" s="6" t="inlineStr">
-        <is>
-          <t>CHI NHÁNH CÔNG TY TNHH MM MEGA MARKET (VIỆT NAM) TẠI TỈNH BÀ RỊA - VŨNG TÀU</t>
-        </is>
-      </c>
-      <c r="H11" s="6" t="inlineStr">
-        <is>
-          <t>Đường 2 tháng 9 (Quốc lộ 51B), Khu phố 1, Phường Phước Thắng, Thành phố Hồ Chí Minh</t>
-        </is>
-      </c>
-      <c r="I11" s="7" t="inlineStr">
-        <is>
-          <t>3502245376</t>
-        </is>
-      </c>
-      <c r="J11" s="6" t="inlineStr">
-        <is>
-          <t>CONG TY CO PHAN DAU TU XAY DUNG THUONG MAI
-DICH VU KY THUAT H &amp; V</t>
-        </is>
-      </c>
-      <c r="K11" s="6"/>
-      <c r="L11" s="13" t="n">
-        <v>1330552.0</v>
-      </c>
-      <c r="M11" s="13" t="n">
-        <v>106444.0</v>
-      </c>
-      <c r="N11" s="13" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="O11" s="13" t="n">
-        <v>1436996.0</v>
-      </c>
-      <c r="P11" s="6" t="inlineStr">
-        <is>
-          <t>Hóa đơn mới</t>
-        </is>
-      </c>
-      <c r="Q11" s="6" t="inlineStr">
-        <is>
-          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="n">
-        <v>6.0</v>
-      </c>
-      <c r="B12" s="7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>C25MVT</t>
-        </is>
-      </c>
-      <c r="D12" s="7" t="inlineStr">
-        <is>
-          <t>225524</t>
-        </is>
-      </c>
-      <c r="E12" s="7" t="inlineStr">
-        <is>
-          <t>26/10/2025</t>
-        </is>
-      </c>
-      <c r="F12" s="7" t="inlineStr">
-        <is>
-          <t>0302249586-009</t>
-        </is>
-      </c>
-      <c r="G12" s="6" t="inlineStr">
-        <is>
-          <t>CHI NHÁNH CÔNG TY TNHH MM MEGA MARKET (VIỆT NAM) TẠI TỈNH BÀ RỊA - VŨNG TÀU</t>
-        </is>
-      </c>
-      <c r="H12" s="6" t="inlineStr">
-        <is>
-          <t>Đường 2 tháng 9 (Quốc lộ 51B), Khu phố 1, Phường Phước Thắng, Thành phố Hồ Chí Minh</t>
-        </is>
-      </c>
-      <c r="I12" s="7" t="inlineStr">
-        <is>
-          <t>3502245376</t>
-        </is>
-      </c>
-      <c r="J12" s="6" t="inlineStr">
-        <is>
-          <t>CONG TY CO PHAN DAU TU XAY DUNG THUONG MAI
-DICH VU KY THUAT H &amp; V</t>
-        </is>
-      </c>
-      <c r="K12" s="6"/>
-      <c r="L12" s="13" t="n">
-        <v>856359.0</v>
-      </c>
-      <c r="M12" s="13" t="n">
-        <v>72945.0</v>
-      </c>
-      <c r="N12" s="13" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="O12" s="13" t="n">
-        <v>929304.0</v>
-      </c>
-      <c r="P12" s="6" t="inlineStr">
-        <is>
-          <t>Hóa đơn mới</t>
-        </is>
-      </c>
-      <c r="Q12" s="6" t="inlineStr">
-        <is>
-          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="n">
-        <v>7.0</v>
-      </c>
-      <c r="B13" s="7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>C25MSF</t>
-        </is>
-      </c>
-      <c r="D13" s="7" t="inlineStr">
-        <is>
-          <t>11154</t>
-        </is>
-      </c>
-      <c r="E13" s="7" t="inlineStr">
-        <is>
-          <t>15/10/2025</t>
-        </is>
-      </c>
-      <c r="F13" s="7" t="inlineStr">
-        <is>
-          <t>3502469464</t>
-        </is>
-      </c>
-      <c r="G13" s="6" t="inlineStr">
-        <is>
-          <t>CÔNG TY TNHH PHÚ SỸ FOOD</t>
-        </is>
-      </c>
-      <c r="H13" s="6" t="inlineStr">
-        <is>
-          <t>Số 149 , Đường Ngô Đức Kế, Phường Tam Thắng,Thành Phố Hồ Chí Minh, Việt Nam</t>
-        </is>
-      </c>
-      <c r="I13" s="7" t="inlineStr">
-        <is>
-          <t>3502245376</t>
-        </is>
-      </c>
-      <c r="J13" s="6" t="inlineStr">
-        <is>
-          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
-        </is>
-      </c>
-      <c r="K13" s="6"/>
-      <c r="L13" s="13" t="n">
-        <v>1514286.0</v>
-      </c>
-      <c r="M13" s="13" t="n">
-        <v>75714.0</v>
-      </c>
-      <c r="N13" s="13" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="O13" s="13" t="n">
-        <v>1590000.0</v>
-      </c>
-      <c r="P13" s="6" t="inlineStr">
-        <is>
-          <t>Hóa đơn mới</t>
-        </is>
-      </c>
-      <c r="Q13" s="6" t="inlineStr">
-        <is>
-          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="n">
-        <v>8.0</v>
-      </c>
-      <c r="B14" s="7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>C25MHN</t>
-        </is>
-      </c>
-      <c r="D14" s="7" t="inlineStr">
-        <is>
-          <t>2176</t>
-        </is>
-      </c>
-      <c r="E14" s="7" t="inlineStr">
-        <is>
-          <t>11/10/2025</t>
-        </is>
-      </c>
-      <c r="F14" s="7" t="inlineStr">
-        <is>
-          <t>3502546101</t>
-        </is>
-      </c>
-      <c r="G14" s="6" t="inlineStr">
-        <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI - DỊCH VỤ GAS HOÀNG NAM</t>
-        </is>
-      </c>
-      <c r="H14" s="6" t="inlineStr">
-        <is>
-          <t>C5-2/1 TT Đô Thị Chí Linh, Phường Rạch Dừa, Thành phố Hồ Chí Minh, Việt Nam</t>
-        </is>
-      </c>
-      <c r="I14" s="7" t="inlineStr">
-        <is>
-          <t>3502245376</t>
-        </is>
-      </c>
-      <c r="J14" s="6" t="inlineStr">
-        <is>
-          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
-        </is>
-      </c>
-      <c r="K14" s="6"/>
-      <c r="L14" s="13" t="n">
-        <v>551852.0</v>
-      </c>
-      <c r="M14" s="13" t="n">
-        <v>44148.0</v>
-      </c>
-      <c r="N14" s="13" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="O14" s="13" t="n">
-        <v>596000.0</v>
-      </c>
-      <c r="P14" s="6" t="inlineStr">
-        <is>
-          <t>Hóa đơn mới</t>
-        </is>
-      </c>
-      <c r="Q14" s="6" t="inlineStr">
         <is>
           <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
         </is>

--- a/Hoadon/HDVao/10/HDDienTuMayTinhTien.xlsx
+++ b/Hoadon/HDVao/10/HDDienTuMayTinhTien.xlsx
@@ -313,54 +313,56 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>C25MCV</t>
+          <t>C25MXD</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>3413123</t>
+          <t>206279</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>24/10/2025</t>
+          <t>02/10/2025</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>0102721191-001</t>
+          <t>3500816070</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN TẬP ĐOÀN GOLDEN GATE - CHI NHÁNH MIỀN NAM</t>
+          <t>CÔNG TY CỔ PHẦN DẦU KHÍ THÁI BÌNH DƯƠNG</t>
         </is>
       </c>
       <c r="H7" s="6" t="inlineStr">
         <is>
-          <t>Tầng 7 TTTM Gigamall, Số 240-242 Phạm Văn Đồng, Phường Hiệp Bình, TP Hồ Chí Minh</t>
+          <t>Số 104 Trần Phú, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I7" s="7" t="inlineStr">
         <is>
-          <t>3500779171</t>
+          <t>3502501171</t>
         </is>
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ XÂY DỰNG ĐẠI THÀNH CÔNG</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI PHÁT ĐẠT VŨNG TÀU</t>
         </is>
       </c>
       <c r="K7" s="6"/>
       <c r="L7" s="13" t="n">
-        <v>2052000.0</v>
+        <v>1381481.0</v>
       </c>
       <c r="M7" s="13" t="n">
-        <v>164160.0</v>
-      </c>
-      <c r="N7" s="13"/>
+        <v>110519.0</v>
+      </c>
+      <c r="N7" s="13" t="n">
+        <v>0.0</v>
+      </c>
       <c r="O7" s="13" t="n">
-        <v>2216160.0</v>
+        <v>1492000.0</v>
       </c>
       <c r="P7" s="6" t="inlineStr">
         <is>
@@ -379,55 +381,61 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>C25MKD</t>
+          <t>C25MXD</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>428</t>
+          <t>206281</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>20/10/2025</t>
+          <t>02/10/2025</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>052094003601</t>
+          <t>3500816070</t>
         </is>
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>HỘ KINH DOANH GOLD 79</t>
+          <t>CÔNG TY CỔ PHẦN DẦU KHÍ THÁI BÌNH DƯƠNG</t>
         </is>
       </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
-          <t>Số 595, Đường Phạm Văn Đồng, Phường Bà Rịa, Thành Phố Hồ Chí Minh</t>
+          <t>Số 104 Trần Phú, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I8" s="7" t="inlineStr">
         <is>
-          <t>3500779171</t>
+          <t>3502501171</t>
         </is>
       </c>
       <c r="J8" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ XÂY DỰNG ĐẠI THÀNH CÔNG</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI PHÁT ĐẠT VŨNG TÀU</t>
         </is>
       </c>
       <c r="K8" s="6"/>
-      <c r="L8" s="13"/>
-      <c r="M8" s="13"/>
-      <c r="N8" s="13"/>
+      <c r="L8" s="13" t="n">
+        <v>759815.0</v>
+      </c>
+      <c r="M8" s="13" t="n">
+        <v>60785.0</v>
+      </c>
+      <c r="N8" s="13" t="n">
+        <v>0.0</v>
+      </c>
       <c r="O8" s="13" t="n">
-        <v>2334000.0</v>
+        <v>820600.0</v>
       </c>
       <c r="P8" s="6" t="inlineStr">
         <is>
@@ -451,56 +459,56 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>C25MKT</t>
+          <t>C25MXD</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>209593</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>03/10/2025</t>
+          <t>06/10/2025</t>
         </is>
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>3502243040</t>
+          <t>3500816070</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN NGỌC KIM THANH</t>
+          <t>CÔNG TY CỔ PHẦN DẦU KHÍ THÁI BÌNH DƯƠNG</t>
         </is>
       </c>
       <c r="H9" s="6" t="inlineStr">
         <is>
-          <t>Khu phố Chu Hải, Phường Tân Hải, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 104 Trần Phú, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I9" s="7" t="inlineStr">
         <is>
-          <t>3500779171</t>
+          <t>3502501171</t>
         </is>
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ XÂY DỰNG ĐẠI THÀNH CÔNG</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI PHÁT ĐẠT VŨNG TÀU</t>
         </is>
       </c>
       <c r="K9" s="6"/>
       <c r="L9" s="13" t="n">
-        <v>2.47055E8</v>
+        <v>2995463.0</v>
       </c>
       <c r="M9" s="13" t="n">
-        <v>1.97644E7</v>
+        <v>239637.0</v>
       </c>
       <c r="N9" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O9" s="13" t="n">
-        <v>2.668194E8</v>
+        <v>3235100.0</v>
       </c>
       <c r="P9" s="6" t="inlineStr">
         <is>
@@ -508,6 +516,444 @@
         </is>
       </c>
       <c r="Q9" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>C25MXD</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>211718</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>09/10/2025</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>3500816070</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN DẦU KHÍ THÁI BÌNH DƯƠNG</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>Số 104 Trần Phú, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I10" s="7" t="inlineStr">
+        <is>
+          <t>3502501171</t>
+        </is>
+      </c>
+      <c r="J10" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI PHÁT ĐẠT VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K10" s="6"/>
+      <c r="L10" s="13" t="n">
+        <v>828157.0</v>
+      </c>
+      <c r="M10" s="13" t="n">
+        <v>66253.0</v>
+      </c>
+      <c r="N10" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O10" s="13" t="n">
+        <v>894410.0</v>
+      </c>
+      <c r="P10" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q10" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>C25MXD</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>215083</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>13/10/2025</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>3500816070</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN DẦU KHÍ THÁI BÌNH DƯƠNG</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>Số 104 Trần Phú, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I11" s="7" t="inlineStr">
+        <is>
+          <t>3502501171</t>
+        </is>
+      </c>
+      <c r="J11" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI PHÁT ĐẠT VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K11" s="6"/>
+      <c r="L11" s="13" t="n">
+        <v>1722222.0</v>
+      </c>
+      <c r="M11" s="13" t="n">
+        <v>137778.0</v>
+      </c>
+      <c r="N11" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O11" s="13" t="n">
+        <v>1860000.0</v>
+      </c>
+      <c r="P11" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q11" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>C25MXD</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>217225</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>16/10/2025</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>3500816070</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN DẦU KHÍ THÁI BÌNH DƯƠNG</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>Số 104 Trần Phú, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I12" s="7" t="inlineStr">
+        <is>
+          <t>3502501171</t>
+        </is>
+      </c>
+      <c r="J12" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI PHÁT ĐẠT VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K12" s="6"/>
+      <c r="L12" s="13" t="n">
+        <v>912778.0</v>
+      </c>
+      <c r="M12" s="13" t="n">
+        <v>73022.0</v>
+      </c>
+      <c r="N12" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O12" s="13" t="n">
+        <v>985800.0</v>
+      </c>
+      <c r="P12" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q12" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="n">
+        <v>7.0</v>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>C25MXD</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>220448</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>20/10/2025</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>3500816070</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN DẦU KHÍ THÁI BÌNH DƯƠNG</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>Số 104 Trần Phú, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I13" s="7" t="inlineStr">
+        <is>
+          <t>3502501171</t>
+        </is>
+      </c>
+      <c r="J13" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI PHÁT ĐẠT VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K13" s="6"/>
+      <c r="L13" s="13" t="n">
+        <v>2728889.0</v>
+      </c>
+      <c r="M13" s="13" t="n">
+        <v>218311.0</v>
+      </c>
+      <c r="N13" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O13" s="13" t="n">
+        <v>2947200.0</v>
+      </c>
+      <c r="P13" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q13" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="n">
+        <v>8.0</v>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>C25MXD</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>221185</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>21/10/2025</t>
+        </is>
+      </c>
+      <c r="F14" s="7" t="inlineStr">
+        <is>
+          <t>3500816070</t>
+        </is>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN DẦU KHÍ THÁI BÌNH DƯƠNG</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>Số 104 Trần Phú, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I14" s="7" t="inlineStr">
+        <is>
+          <t>3502501171</t>
+        </is>
+      </c>
+      <c r="J14" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI PHÁT ĐẠT VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K14" s="6"/>
+      <c r="L14" s="13" t="n">
+        <v>886889.0</v>
+      </c>
+      <c r="M14" s="13" t="n">
+        <v>70951.0</v>
+      </c>
+      <c r="N14" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O14" s="13" t="n">
+        <v>957840.0</v>
+      </c>
+      <c r="P14" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q14" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="n">
+        <v>9.0</v>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>C25MTL</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>4708</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>03/10/2025</t>
+        </is>
+      </c>
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t>3502236646</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ VẬN TẢI TIẾN LỢI</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>Số 20, tổ 1 , ấp Lò Vôi, Xã Long Hải, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I15" s="7" t="inlineStr">
+        <is>
+          <t>3502501171</t>
+        </is>
+      </c>
+      <c r="J15" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI PHÁT ĐẠT VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K15" s="6"/>
+      <c r="L15" s="13" t="n">
+        <v>2.555E7</v>
+      </c>
+      <c r="M15" s="13" t="n">
+        <v>2044000.0</v>
+      </c>
+      <c r="N15" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O15" s="13" t="n">
+        <v>2.7594E7</v>
+      </c>
+      <c r="P15" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q15" s="6" t="inlineStr">
         <is>
           <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
         </is>

--- a/Hoadon/HDVao/10/HDDienTuMayTinhTien.xlsx
+++ b/Hoadon/HDVao/10/HDDienTuMayTinhTien.xlsx
@@ -313,56 +313,56 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>C25MXD</t>
+          <t>C25MLT</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>206279</t>
+          <t>2668512</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>02/10/2025</t>
+          <t>01/10/2025</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>3500816070</t>
+          <t>3600445359</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN DẦU KHÍ THÁI BÌNH DƯƠNG</t>
+          <t>CÔNG TY CỔ PHẦN THƯƠNG MẠI LONG THÀNH</t>
         </is>
       </c>
       <c r="H7" s="6" t="inlineStr">
         <is>
-          <t>Số 104 Trần Phú, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 286, Đường Lê Duẩn, Ấp Văn Hải, Xã Long Thành, Tỉnh Đồng Nai</t>
         </is>
       </c>
       <c r="I7" s="7" t="inlineStr">
         <is>
-          <t>3502501171</t>
+          <t>3502267355</t>
         </is>
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI PHÁT ĐẠT VŨNG TÀU</t>
+          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
         </is>
       </c>
       <c r="K7" s="6"/>
       <c r="L7" s="13" t="n">
-        <v>1381481.0</v>
+        <v>925926.0</v>
       </c>
       <c r="M7" s="13" t="n">
-        <v>110519.0</v>
+        <v>74074.0</v>
       </c>
       <c r="N7" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O7" s="13" t="n">
-        <v>1492000.0</v>
+        <v>1000000.0</v>
       </c>
       <c r="P7" s="6" t="inlineStr">
         <is>
@@ -386,12 +386,12 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>C25MXD</t>
+          <t>C25MLT</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>206281</t>
+          <t>2675119</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
@@ -401,41 +401,41 @@
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>3500816070</t>
+          <t>3600445359</t>
         </is>
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN DẦU KHÍ THÁI BÌNH DƯƠNG</t>
+          <t>CÔNG TY CỔ PHẦN THƯƠNG MẠI LONG THÀNH</t>
         </is>
       </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
-          <t>Số 104 Trần Phú, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 286, Đường Lê Duẩn, Ấp Văn Hải, Xã Long Thành, Tỉnh Đồng Nai</t>
         </is>
       </c>
       <c r="I8" s="7" t="inlineStr">
         <is>
-          <t>3502501171</t>
+          <t>3502267355</t>
         </is>
       </c>
       <c r="J8" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI PHÁT ĐẠT VŨNG TÀU</t>
+          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
         </is>
       </c>
       <c r="K8" s="6"/>
       <c r="L8" s="13" t="n">
-        <v>759815.0</v>
+        <v>925926.0</v>
       </c>
       <c r="M8" s="13" t="n">
-        <v>60785.0</v>
+        <v>74074.0</v>
       </c>
       <c r="N8" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O8" s="13" t="n">
-        <v>820600.0</v>
+        <v>1000000.0</v>
       </c>
       <c r="P8" s="6" t="inlineStr">
         <is>
@@ -459,56 +459,56 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>C25MXD</t>
+          <t>C25MLT</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>209593</t>
+          <t>2675817</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>06/10/2025</t>
+          <t>02/10/2025</t>
         </is>
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>3500816070</t>
+          <t>3600445359</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN DẦU KHÍ THÁI BÌNH DƯƠNG</t>
+          <t>CÔNG TY CỔ PHẦN THƯƠNG MẠI LONG THÀNH</t>
         </is>
       </c>
       <c r="H9" s="6" t="inlineStr">
         <is>
-          <t>Số 104 Trần Phú, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 286, Đường Lê Duẩn, Ấp Văn Hải, Xã Long Thành, Tỉnh Đồng Nai</t>
         </is>
       </c>
       <c r="I9" s="7" t="inlineStr">
         <is>
-          <t>3502501171</t>
+          <t>3502267355</t>
         </is>
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI PHÁT ĐẠT VŨNG TÀU</t>
+          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
         </is>
       </c>
       <c r="K9" s="6"/>
       <c r="L9" s="13" t="n">
-        <v>2995463.0</v>
+        <v>926017.0</v>
       </c>
       <c r="M9" s="13" t="n">
-        <v>239637.0</v>
+        <v>74081.0</v>
       </c>
       <c r="N9" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O9" s="13" t="n">
-        <v>3235100.0</v>
+        <v>1000098.0</v>
       </c>
       <c r="P9" s="6" t="inlineStr">
         <is>
@@ -532,56 +532,56 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>C25MXD</t>
+          <t>C25MLT</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>211718</t>
+          <t>2689066</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>09/10/2025</t>
+          <t>03/10/2025</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>3500816070</t>
+          <t>3600445359</t>
         </is>
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN DẦU KHÍ THÁI BÌNH DƯƠNG</t>
+          <t>CÔNG TY CỔ PHẦN THƯƠNG MẠI LONG THÀNH</t>
         </is>
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>Số 104 Trần Phú, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 286, Đường Lê Duẩn, Ấp Văn Hải, Xã Long Thành, Tỉnh Đồng Nai</t>
         </is>
       </c>
       <c r="I10" s="7" t="inlineStr">
         <is>
-          <t>3502501171</t>
+          <t>3502267355</t>
         </is>
       </c>
       <c r="J10" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI PHÁT ĐẠT VŨNG TÀU</t>
+          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
         </is>
       </c>
       <c r="K10" s="6"/>
       <c r="L10" s="13" t="n">
-        <v>828157.0</v>
+        <v>879630.0</v>
       </c>
       <c r="M10" s="13" t="n">
-        <v>66253.0</v>
+        <v>70370.0</v>
       </c>
       <c r="N10" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O10" s="13" t="n">
-        <v>894410.0</v>
+        <v>950000.0</v>
       </c>
       <c r="P10" s="6" t="inlineStr">
         <is>
@@ -605,56 +605,56 @@
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>C25MXD</t>
+          <t>C25MLT</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>215083</t>
+          <t>2729417</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t>13/10/2025</t>
+          <t>07/10/2025</t>
         </is>
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>3500816070</t>
+          <t>3600445359</t>
         </is>
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN DẦU KHÍ THÁI BÌNH DƯƠNG</t>
+          <t>CÔNG TY CỔ PHẦN THƯƠNG MẠI LONG THÀNH</t>
         </is>
       </c>
       <c r="H11" s="6" t="inlineStr">
         <is>
-          <t>Số 104 Trần Phú, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 286, Đường Lê Duẩn, Ấp Văn Hải, Xã Long Thành, Tỉnh Đồng Nai</t>
         </is>
       </c>
       <c r="I11" s="7" t="inlineStr">
         <is>
-          <t>3502501171</t>
+          <t>3502267355</t>
         </is>
       </c>
       <c r="J11" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI PHÁT ĐẠT VŨNG TÀU</t>
+          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
         </is>
       </c>
       <c r="K11" s="6"/>
       <c r="L11" s="13" t="n">
-        <v>1722222.0</v>
+        <v>879630.0</v>
       </c>
       <c r="M11" s="13" t="n">
-        <v>137778.0</v>
+        <v>70370.0</v>
       </c>
       <c r="N11" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O11" s="13" t="n">
-        <v>1860000.0</v>
+        <v>950000.0</v>
       </c>
       <c r="P11" s="6" t="inlineStr">
         <is>
@@ -678,56 +678,56 @@
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>C25MXD</t>
+          <t>C25MLT</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>217225</t>
+          <t>2729991</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>16/10/2025</t>
+          <t>07/10/2025</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>3500816070</t>
+          <t>3600445359</t>
         </is>
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN DẦU KHÍ THÁI BÌNH DƯƠNG</t>
+          <t>CÔNG TY CỔ PHẦN THƯƠNG MẠI LONG THÀNH</t>
         </is>
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>Số 104 Trần Phú, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 286, Đường Lê Duẩn, Ấp Văn Hải, Xã Long Thành, Tỉnh Đồng Nai</t>
         </is>
       </c>
       <c r="I12" s="7" t="inlineStr">
         <is>
-          <t>3502501171</t>
+          <t>3502267355</t>
         </is>
       </c>
       <c r="J12" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI PHÁT ĐẠT VŨNG TÀU</t>
+          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
         </is>
       </c>
       <c r="K12" s="6"/>
       <c r="L12" s="13" t="n">
-        <v>912778.0</v>
+        <v>925926.0</v>
       </c>
       <c r="M12" s="13" t="n">
-        <v>73022.0</v>
+        <v>74074.0</v>
       </c>
       <c r="N12" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O12" s="13" t="n">
-        <v>985800.0</v>
+        <v>1000000.0</v>
       </c>
       <c r="P12" s="6" t="inlineStr">
         <is>
@@ -751,56 +751,56 @@
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>C25MXD</t>
+          <t>C25MLT</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>220448</t>
+          <t>2768014</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>20/10/2025</t>
+          <t>11/10/2025</t>
         </is>
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
-          <t>3500816070</t>
+          <t>3600445359</t>
         </is>
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN DẦU KHÍ THÁI BÌNH DƯƠNG</t>
+          <t>CÔNG TY CỔ PHẦN THƯƠNG MẠI LONG THÀNH</t>
         </is>
       </c>
       <c r="H13" s="6" t="inlineStr">
         <is>
-          <t>Số 104 Trần Phú, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 286, Đường Lê Duẩn, Ấp Văn Hải, Xã Long Thành, Tỉnh Đồng Nai</t>
         </is>
       </c>
       <c r="I13" s="7" t="inlineStr">
         <is>
-          <t>3502501171</t>
+          <t>3502267355</t>
         </is>
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI PHÁT ĐẠT VŨNG TÀU</t>
+          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
         </is>
       </c>
       <c r="K13" s="6"/>
       <c r="L13" s="13" t="n">
-        <v>2728889.0</v>
+        <v>879630.0</v>
       </c>
       <c r="M13" s="13" t="n">
-        <v>218311.0</v>
+        <v>70370.0</v>
       </c>
       <c r="N13" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O13" s="13" t="n">
-        <v>2947200.0</v>
+        <v>950000.0</v>
       </c>
       <c r="P13" s="6" t="inlineStr">
         <is>
@@ -824,56 +824,56 @@
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>C25MXD</t>
+          <t>C25MLT</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>221185</t>
+          <t>2801622</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>21/10/2025</t>
+          <t>14/10/2025</t>
         </is>
       </c>
       <c r="F14" s="7" t="inlineStr">
         <is>
-          <t>3500816070</t>
+          <t>3600445359</t>
         </is>
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN DẦU KHÍ THÁI BÌNH DƯƠNG</t>
+          <t>CÔNG TY CỔ PHẦN THƯƠNG MẠI LONG THÀNH</t>
         </is>
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
-          <t>Số 104 Trần Phú, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 286, Đường Lê Duẩn, Ấp Văn Hải, Xã Long Thành, Tỉnh Đồng Nai</t>
         </is>
       </c>
       <c r="I14" s="7" t="inlineStr">
         <is>
-          <t>3502501171</t>
+          <t>3502267355</t>
         </is>
       </c>
       <c r="J14" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI PHÁT ĐẠT VŨNG TÀU</t>
+          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
         </is>
       </c>
       <c r="K14" s="6"/>
       <c r="L14" s="13" t="n">
-        <v>886889.0</v>
+        <v>925926.0</v>
       </c>
       <c r="M14" s="13" t="n">
-        <v>70951.0</v>
+        <v>74074.0</v>
       </c>
       <c r="N14" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O14" s="13" t="n">
-        <v>957840.0</v>
+        <v>1000000.0</v>
       </c>
       <c r="P14" s="6" t="inlineStr">
         <is>
@@ -897,56 +897,56 @@
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>C25MTL</t>
+          <t>C25MLT</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>4708</t>
+          <t>2829496</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
-          <t>03/10/2025</t>
+          <t>17/10/2025</t>
         </is>
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
-          <t>3502236646</t>
+          <t>3600445359</t>
         </is>
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ VẬN TẢI TIẾN LỢI</t>
+          <t>CÔNG TY CỔ PHẦN THƯƠNG MẠI LONG THÀNH</t>
         </is>
       </c>
       <c r="H15" s="6" t="inlineStr">
         <is>
-          <t>Số 20, tổ 1 , ấp Lò Vôi, Xã Long Hải, Thành Phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 286, Đường Lê Duẩn, Ấp Văn Hải, Xã Long Thành, Tỉnh Đồng Nai</t>
         </is>
       </c>
       <c r="I15" s="7" t="inlineStr">
         <is>
-          <t>3502501171</t>
+          <t>3502267355</t>
         </is>
       </c>
       <c r="J15" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI PHÁT ĐẠT VŨNG TÀU</t>
+          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
         </is>
       </c>
       <c r="K15" s="6"/>
       <c r="L15" s="13" t="n">
-        <v>2.555E7</v>
+        <v>925926.0</v>
       </c>
       <c r="M15" s="13" t="n">
-        <v>2044000.0</v>
+        <v>74074.0</v>
       </c>
       <c r="N15" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O15" s="13" t="n">
-        <v>2.7594E7</v>
+        <v>1000000.0</v>
       </c>
       <c r="P15" s="6" t="inlineStr">
         <is>
@@ -954,6 +954,1028 @@
         </is>
       </c>
       <c r="Q15" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="n">
+        <v>10.0</v>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>C25MLT</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>2848178</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>19/10/2025</t>
+        </is>
+      </c>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>3600445359</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN THƯƠNG MẠI LONG THÀNH</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>Số 286, Đường Lê Duẩn, Ấp Văn Hải, Xã Long Thành, Tỉnh Đồng Nai</t>
+        </is>
+      </c>
+      <c r="I16" s="7" t="inlineStr">
+        <is>
+          <t>3502267355</t>
+        </is>
+      </c>
+      <c r="J16" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
+        </is>
+      </c>
+      <c r="K16" s="6"/>
+      <c r="L16" s="13" t="n">
+        <v>898148.0</v>
+      </c>
+      <c r="M16" s="13" t="n">
+        <v>71852.0</v>
+      </c>
+      <c r="N16" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O16" s="13" t="n">
+        <v>970000.0</v>
+      </c>
+      <c r="P16" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q16" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="n">
+        <v>11.0</v>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>C25MLT</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>2876011</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>22/10/2025</t>
+        </is>
+      </c>
+      <c r="F17" s="7" t="inlineStr">
+        <is>
+          <t>3600445359</t>
+        </is>
+      </c>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN THƯƠNG MẠI LONG THÀNH</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>Số 286, Đường Lê Duẩn, Ấp Văn Hải, Xã Long Thành, Tỉnh Đồng Nai</t>
+        </is>
+      </c>
+      <c r="I17" s="7" t="inlineStr">
+        <is>
+          <t>3502267355</t>
+        </is>
+      </c>
+      <c r="J17" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
+        </is>
+      </c>
+      <c r="K17" s="6"/>
+      <c r="L17" s="13" t="n">
+        <v>833333.0</v>
+      </c>
+      <c r="M17" s="13" t="n">
+        <v>66667.0</v>
+      </c>
+      <c r="N17" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O17" s="13" t="n">
+        <v>900000.0</v>
+      </c>
+      <c r="P17" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q17" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="n">
+        <v>12.0</v>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>C25MLT</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>2888579</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>23/10/2025</t>
+        </is>
+      </c>
+      <c r="F18" s="7" t="inlineStr">
+        <is>
+          <t>3600445359</t>
+        </is>
+      </c>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN THƯƠNG MẠI LONG THÀNH</t>
+        </is>
+      </c>
+      <c r="H18" s="6" t="inlineStr">
+        <is>
+          <t>Số 286, Đường Lê Duẩn, Ấp Văn Hải, Xã Long Thành, Tỉnh Đồng Nai</t>
+        </is>
+      </c>
+      <c r="I18" s="7" t="inlineStr">
+        <is>
+          <t>3502267355</t>
+        </is>
+      </c>
+      <c r="J18" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
+        </is>
+      </c>
+      <c r="K18" s="6"/>
+      <c r="L18" s="13" t="n">
+        <v>462963.0</v>
+      </c>
+      <c r="M18" s="13" t="n">
+        <v>37037.0</v>
+      </c>
+      <c r="N18" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O18" s="13" t="n">
+        <v>500000.0</v>
+      </c>
+      <c r="P18" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q18" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="n">
+        <v>13.0</v>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>C25MLT</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>2896815</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>24/10/2025</t>
+        </is>
+      </c>
+      <c r="F19" s="7" t="inlineStr">
+        <is>
+          <t>3600445359</t>
+        </is>
+      </c>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN THƯƠNG MẠI LONG THÀNH</t>
+        </is>
+      </c>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t>Số 286, Đường Lê Duẩn, Ấp Văn Hải, Xã Long Thành, Tỉnh Đồng Nai</t>
+        </is>
+      </c>
+      <c r="I19" s="7" t="inlineStr">
+        <is>
+          <t>3502267355</t>
+        </is>
+      </c>
+      <c r="J19" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
+        </is>
+      </c>
+      <c r="K19" s="6"/>
+      <c r="L19" s="13" t="n">
+        <v>462963.0</v>
+      </c>
+      <c r="M19" s="13" t="n">
+        <v>37037.0</v>
+      </c>
+      <c r="N19" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O19" s="13" t="n">
+        <v>500000.0</v>
+      </c>
+      <c r="P19" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q19" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="n">
+        <v>14.0</v>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>C25MLT</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>2897086</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>24/10/2025</t>
+        </is>
+      </c>
+      <c r="F20" s="7" t="inlineStr">
+        <is>
+          <t>3600445359</t>
+        </is>
+      </c>
+      <c r="G20" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN THƯƠNG MẠI LONG THÀNH</t>
+        </is>
+      </c>
+      <c r="H20" s="6" t="inlineStr">
+        <is>
+          <t>Số 286, Đường Lê Duẩn, Ấp Văn Hải, Xã Long Thành, Tỉnh Đồng Nai</t>
+        </is>
+      </c>
+      <c r="I20" s="7" t="inlineStr">
+        <is>
+          <t>3502267355</t>
+        </is>
+      </c>
+      <c r="J20" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
+        </is>
+      </c>
+      <c r="K20" s="6"/>
+      <c r="L20" s="13" t="n">
+        <v>416667.0</v>
+      </c>
+      <c r="M20" s="13" t="n">
+        <v>33333.0</v>
+      </c>
+      <c r="N20" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O20" s="13" t="n">
+        <v>450000.0</v>
+      </c>
+      <c r="P20" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q20" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="n">
+        <v>15.0</v>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>C25MLT</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>2897119</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>24/10/2025</t>
+        </is>
+      </c>
+      <c r="F21" s="7" t="inlineStr">
+        <is>
+          <t>3600445359</t>
+        </is>
+      </c>
+      <c r="G21" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN THƯƠNG MẠI LONG THÀNH</t>
+        </is>
+      </c>
+      <c r="H21" s="6" t="inlineStr">
+        <is>
+          <t>Số 286, Đường Lê Duẩn, Ấp Văn Hải, Xã Long Thành, Tỉnh Đồng Nai</t>
+        </is>
+      </c>
+      <c r="I21" s="7" t="inlineStr">
+        <is>
+          <t>3502267355</t>
+        </is>
+      </c>
+      <c r="J21" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
+        </is>
+      </c>
+      <c r="K21" s="6"/>
+      <c r="L21" s="13" t="n">
+        <v>416667.0</v>
+      </c>
+      <c r="M21" s="13" t="n">
+        <v>33333.0</v>
+      </c>
+      <c r="N21" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O21" s="13" t="n">
+        <v>450000.0</v>
+      </c>
+      <c r="P21" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q21" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="n">
+        <v>16.0</v>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>C25MLT</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>2908853</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>25/10/2025</t>
+        </is>
+      </c>
+      <c r="F22" s="7" t="inlineStr">
+        <is>
+          <t>3600445359</t>
+        </is>
+      </c>
+      <c r="G22" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN THƯƠNG MẠI LONG THÀNH</t>
+        </is>
+      </c>
+      <c r="H22" s="6" t="inlineStr">
+        <is>
+          <t>Số 286, Đường Lê Duẩn, Ấp Văn Hải, Xã Long Thành, Tỉnh Đồng Nai</t>
+        </is>
+      </c>
+      <c r="I22" s="7" t="inlineStr">
+        <is>
+          <t>3502267355</t>
+        </is>
+      </c>
+      <c r="J22" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
+        </is>
+      </c>
+      <c r="K22" s="6"/>
+      <c r="L22" s="13" t="n">
+        <v>462963.0</v>
+      </c>
+      <c r="M22" s="13" t="n">
+        <v>37037.0</v>
+      </c>
+      <c r="N22" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O22" s="13" t="n">
+        <v>500000.0</v>
+      </c>
+      <c r="P22" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q22" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="n">
+        <v>17.0</v>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>C25MLT</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>2909096</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>25/10/2025</t>
+        </is>
+      </c>
+      <c r="F23" s="7" t="inlineStr">
+        <is>
+          <t>3600445359</t>
+        </is>
+      </c>
+      <c r="G23" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN THƯƠNG MẠI LONG THÀNH</t>
+        </is>
+      </c>
+      <c r="H23" s="6" t="inlineStr">
+        <is>
+          <t>Số 286, Đường Lê Duẩn, Ấp Văn Hải, Xã Long Thành, Tỉnh Đồng Nai</t>
+        </is>
+      </c>
+      <c r="I23" s="7" t="inlineStr">
+        <is>
+          <t>3502267355</t>
+        </is>
+      </c>
+      <c r="J23" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
+        </is>
+      </c>
+      <c r="K23" s="6"/>
+      <c r="L23" s="13" t="n">
+        <v>462963.0</v>
+      </c>
+      <c r="M23" s="13" t="n">
+        <v>37037.0</v>
+      </c>
+      <c r="N23" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O23" s="13" t="n">
+        <v>500000.0</v>
+      </c>
+      <c r="P23" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q23" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="n">
+        <v>18.0</v>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>C25MLT</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>2909862</t>
+        </is>
+      </c>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t>25/10/2025</t>
+        </is>
+      </c>
+      <c r="F24" s="7" t="inlineStr">
+        <is>
+          <t>3600445359</t>
+        </is>
+      </c>
+      <c r="G24" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN THƯƠNG MẠI LONG THÀNH</t>
+        </is>
+      </c>
+      <c r="H24" s="6" t="inlineStr">
+        <is>
+          <t>Số 286, Đường Lê Duẩn, Ấp Văn Hải, Xã Long Thành, Tỉnh Đồng Nai</t>
+        </is>
+      </c>
+      <c r="I24" s="7" t="inlineStr">
+        <is>
+          <t>3502267355</t>
+        </is>
+      </c>
+      <c r="J24" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
+        </is>
+      </c>
+      <c r="K24" s="6"/>
+      <c r="L24" s="13" t="n">
+        <v>898148.0</v>
+      </c>
+      <c r="M24" s="13" t="n">
+        <v>71852.0</v>
+      </c>
+      <c r="N24" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O24" s="13" t="n">
+        <v>970000.0</v>
+      </c>
+      <c r="P24" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q24" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="n">
+        <v>19.0</v>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>C25MLT</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>2926117</t>
+        </is>
+      </c>
+      <c r="E25" s="7" t="inlineStr">
+        <is>
+          <t>27/10/2025</t>
+        </is>
+      </c>
+      <c r="F25" s="7" t="inlineStr">
+        <is>
+          <t>3600445359</t>
+        </is>
+      </c>
+      <c r="G25" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN THƯƠNG MẠI LONG THÀNH</t>
+        </is>
+      </c>
+      <c r="H25" s="6" t="inlineStr">
+        <is>
+          <t>Số 286, Đường Lê Duẩn, Ấp Văn Hải, Xã Long Thành, Tỉnh Đồng Nai</t>
+        </is>
+      </c>
+      <c r="I25" s="7" t="inlineStr">
+        <is>
+          <t>3502267355</t>
+        </is>
+      </c>
+      <c r="J25" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
+        </is>
+      </c>
+      <c r="K25" s="6"/>
+      <c r="L25" s="13" t="n">
+        <v>925926.0</v>
+      </c>
+      <c r="M25" s="13" t="n">
+        <v>74074.0</v>
+      </c>
+      <c r="N25" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O25" s="13" t="n">
+        <v>1000000.0</v>
+      </c>
+      <c r="P25" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q25" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="n">
+        <v>20.0</v>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>C25MLT</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>2933853</t>
+        </is>
+      </c>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t>27/10/2025</t>
+        </is>
+      </c>
+      <c r="F26" s="7" t="inlineStr">
+        <is>
+          <t>3600445359</t>
+        </is>
+      </c>
+      <c r="G26" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN THƯƠNG MẠI LONG THÀNH</t>
+        </is>
+      </c>
+      <c r="H26" s="6" t="inlineStr">
+        <is>
+          <t>Số 286, Đường Lê Duẩn, Ấp Văn Hải, Xã Long Thành, Tỉnh Đồng Nai</t>
+        </is>
+      </c>
+      <c r="I26" s="7" t="inlineStr">
+        <is>
+          <t>3502267355</t>
+        </is>
+      </c>
+      <c r="J26" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
+        </is>
+      </c>
+      <c r="K26" s="6"/>
+      <c r="L26" s="13" t="n">
+        <v>462963.0</v>
+      </c>
+      <c r="M26" s="13" t="n">
+        <v>37037.0</v>
+      </c>
+      <c r="N26" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O26" s="13" t="n">
+        <v>500000.0</v>
+      </c>
+      <c r="P26" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q26" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="n">
+        <v>21.0</v>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>C25MLT</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>2939649</t>
+        </is>
+      </c>
+      <c r="E27" s="7" t="inlineStr">
+        <is>
+          <t>28/10/2025</t>
+        </is>
+      </c>
+      <c r="F27" s="7" t="inlineStr">
+        <is>
+          <t>3600445359</t>
+        </is>
+      </c>
+      <c r="G27" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN THƯƠNG MẠI LONG THÀNH</t>
+        </is>
+      </c>
+      <c r="H27" s="6" t="inlineStr">
+        <is>
+          <t>Số 286, Đường Lê Duẩn, Ấp Văn Hải, Xã Long Thành, Tỉnh Đồng Nai</t>
+        </is>
+      </c>
+      <c r="I27" s="7" t="inlineStr">
+        <is>
+          <t>3502267355</t>
+        </is>
+      </c>
+      <c r="J27" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
+        </is>
+      </c>
+      <c r="K27" s="6"/>
+      <c r="L27" s="13" t="n">
+        <v>893519.0</v>
+      </c>
+      <c r="M27" s="13" t="n">
+        <v>71481.0</v>
+      </c>
+      <c r="N27" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O27" s="13" t="n">
+        <v>965000.0</v>
+      </c>
+      <c r="P27" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q27" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="n">
+        <v>22.0</v>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>C25MLT</t>
+        </is>
+      </c>
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t>2950930</t>
+        </is>
+      </c>
+      <c r="E28" s="7" t="inlineStr">
+        <is>
+          <t>29/10/2025</t>
+        </is>
+      </c>
+      <c r="F28" s="7" t="inlineStr">
+        <is>
+          <t>3600445359</t>
+        </is>
+      </c>
+      <c r="G28" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN THƯƠNG MẠI LONG THÀNH</t>
+        </is>
+      </c>
+      <c r="H28" s="6" t="inlineStr">
+        <is>
+          <t>Số 286, Đường Lê Duẩn, Ấp Văn Hải, Xã Long Thành, Tỉnh Đồng Nai</t>
+        </is>
+      </c>
+      <c r="I28" s="7" t="inlineStr">
+        <is>
+          <t>3502267355</t>
+        </is>
+      </c>
+      <c r="J28" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
+        </is>
+      </c>
+      <c r="K28" s="6"/>
+      <c r="L28" s="13" t="n">
+        <v>925926.0</v>
+      </c>
+      <c r="M28" s="13" t="n">
+        <v>74074.0</v>
+      </c>
+      <c r="N28" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O28" s="13" t="n">
+        <v>1000000.0</v>
+      </c>
+      <c r="P28" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q28" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="n">
+        <v>23.0</v>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>C25MLT</t>
+        </is>
+      </c>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>2968734</t>
+        </is>
+      </c>
+      <c r="E29" s="7" t="inlineStr">
+        <is>
+          <t>31/10/2025</t>
+        </is>
+      </c>
+      <c r="F29" s="7" t="inlineStr">
+        <is>
+          <t>3600445359</t>
+        </is>
+      </c>
+      <c r="G29" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN THƯƠNG MẠI LONG THÀNH</t>
+        </is>
+      </c>
+      <c r="H29" s="6" t="inlineStr">
+        <is>
+          <t>Số 286, Đường Lê Duẩn, Ấp Văn Hải, Xã Long Thành, Tỉnh Đồng Nai</t>
+        </is>
+      </c>
+      <c r="I29" s="7" t="inlineStr">
+        <is>
+          <t>3502267355</t>
+        </is>
+      </c>
+      <c r="J29" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
+        </is>
+      </c>
+      <c r="K29" s="6"/>
+      <c r="L29" s="13" t="n">
+        <v>851852.0</v>
+      </c>
+      <c r="M29" s="13" t="n">
+        <v>68148.0</v>
+      </c>
+      <c r="N29" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O29" s="13" t="n">
+        <v>920000.0</v>
+      </c>
+      <c r="P29" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q29" s="6" t="inlineStr">
         <is>
           <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
         </is>

--- a/Hoadon/HDVao/10/HDDienTuMayTinhTien.xlsx
+++ b/Hoadon/HDVao/10/HDDienTuMayTinhTien.xlsx
@@ -308,61 +308,57 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>C25MLT</t>
+          <t>C25MVC</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>2668512</t>
+          <t>134</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>01/10/2025</t>
+          <t>14/10/2025</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>3600445359</t>
+          <t>026078008681</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN THƯƠNG MẠI LONG THÀNH</t>
+          <t>Hộ Kinh Doanh Trần Văn Cường (Phường 8)</t>
         </is>
       </c>
       <c r="H7" s="6" t="inlineStr">
         <is>
-          <t>Số 286, Đường Lê Duẩn, Ấp Văn Hải, Xã Long Thành, Tỉnh Đồng Nai</t>
+          <t>209 đường Bình Giã, Phường Tam Thắng, Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I7" s="7" t="inlineStr">
         <is>
-          <t>3502267355</t>
+          <t>3502469834</t>
         </is>
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
         </is>
       </c>
       <c r="K7" s="6"/>
-      <c r="L7" s="13" t="n">
-        <v>925926.0</v>
-      </c>
-      <c r="M7" s="13" t="n">
-        <v>74074.0</v>
-      </c>
+      <c r="L7" s="13"/>
+      <c r="M7" s="13"/>
       <c r="N7" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O7" s="13" t="n">
-        <v>1000000.0</v>
+        <v>2.039E7</v>
       </c>
       <c r="P7" s="6" t="inlineStr">
         <is>
@@ -381,61 +377,57 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>C25MLT</t>
+          <t>C25MVC</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>2675119</t>
+          <t>137</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>02/10/2025</t>
+          <t>15/10/2025</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>3600445359</t>
+          <t>026078008681</t>
         </is>
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN THƯƠNG MẠI LONG THÀNH</t>
+          <t>Hộ Kinh Doanh Trần Văn Cường (Phường 8)</t>
         </is>
       </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
-          <t>Số 286, Đường Lê Duẩn, Ấp Văn Hải, Xã Long Thành, Tỉnh Đồng Nai</t>
+          <t>209 đường Bình Giã, Phường Tam Thắng, Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I8" s="7" t="inlineStr">
         <is>
-          <t>3502267355</t>
+          <t>3502469834</t>
         </is>
       </c>
       <c r="J8" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
         </is>
       </c>
       <c r="K8" s="6"/>
-      <c r="L8" s="13" t="n">
-        <v>925926.0</v>
-      </c>
-      <c r="M8" s="13" t="n">
-        <v>74074.0</v>
-      </c>
+      <c r="L8" s="13"/>
+      <c r="M8" s="13"/>
       <c r="N8" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O8" s="13" t="n">
-        <v>1000000.0</v>
+        <v>5982500.0</v>
       </c>
       <c r="P8" s="6" t="inlineStr">
         <is>
@@ -454,61 +446,57 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>C25MLT</t>
+          <t>C25MNM</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>2675817</t>
+          <t>61</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>02/10/2025</t>
+          <t>31/10/2025</t>
         </is>
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>3600445359</t>
+          <t>036165003642</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN THƯƠNG MẠI LONG THÀNH</t>
+          <t>HỘ KINH DOANH NGUYỄN THỊ PHƯỢNG</t>
         </is>
       </c>
       <c r="H9" s="6" t="inlineStr">
         <is>
-          <t>Số 286, Đường Lê Duẩn, Ấp Văn Hải, Xã Long Thành, Tỉnh Đồng Nai</t>
+          <t>Quầy F44-46 Khu Hành Lang B Nhà Lồng Chợ Vũng Tàu, Phường Vũng Tàu, TP Hồ Chí Minh</t>
         </is>
       </c>
       <c r="I9" s="7" t="inlineStr">
         <is>
-          <t>3502267355</t>
+          <t>3502469834</t>
         </is>
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
         </is>
       </c>
       <c r="K9" s="6"/>
-      <c r="L9" s="13" t="n">
-        <v>926017.0</v>
-      </c>
-      <c r="M9" s="13" t="n">
-        <v>74081.0</v>
-      </c>
+      <c r="L9" s="13"/>
+      <c r="M9" s="13"/>
       <c r="N9" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O9" s="13" t="n">
-        <v>1000098.0</v>
+        <v>2090000.0</v>
       </c>
       <c r="P9" s="6" t="inlineStr">
         <is>
@@ -527,61 +515,57 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>C25MLT</t>
+          <t>C25MTL</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>2689066</t>
+          <t>10602</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>03/10/2025</t>
+          <t>04/10/2025</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>3600445359</t>
+          <t>037165003053</t>
         </is>
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN THƯƠNG MẠI LONG THÀNH</t>
+          <t>HỘ KINH DOANH CỬA HÀNG THÀNH LẬP 1</t>
         </is>
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>Số 286, Đường Lê Duẩn, Ấp Văn Hải, Xã Long Thành, Tỉnh Đồng Nai</t>
+          <t>15A Kha Vạn Cân, Phường Tam Thắng, Thành phố Hồ Chí Minh, Việt Nam.</t>
         </is>
       </c>
       <c r="I10" s="7" t="inlineStr">
         <is>
-          <t>3502267355</t>
+          <t>3502469834</t>
         </is>
       </c>
       <c r="J10" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
         </is>
       </c>
       <c r="K10" s="6"/>
-      <c r="L10" s="13" t="n">
-        <v>879630.0</v>
-      </c>
-      <c r="M10" s="13" t="n">
-        <v>70370.0</v>
-      </c>
+      <c r="L10" s="13"/>
+      <c r="M10" s="13"/>
       <c r="N10" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O10" s="13" t="n">
-        <v>950000.0</v>
+        <v>1200000.0</v>
       </c>
       <c r="P10" s="6" t="inlineStr">
         <is>
@@ -600,61 +584,57 @@
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>C25MLT</t>
+          <t>C25MTL</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>2729417</t>
+          <t>10603</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t>07/10/2025</t>
+          <t>04/10/2025</t>
         </is>
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>3600445359</t>
+          <t>037165003053</t>
         </is>
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN THƯƠNG MẠI LONG THÀNH</t>
+          <t>HỘ KINH DOANH CỬA HÀNG THÀNH LẬP 1</t>
         </is>
       </c>
       <c r="H11" s="6" t="inlineStr">
         <is>
-          <t>Số 286, Đường Lê Duẩn, Ấp Văn Hải, Xã Long Thành, Tỉnh Đồng Nai</t>
+          <t>15A Kha Vạn Cân, Phường Tam Thắng, Thành phố Hồ Chí Minh, Việt Nam.</t>
         </is>
       </c>
       <c r="I11" s="7" t="inlineStr">
         <is>
-          <t>3502267355</t>
+          <t>3502469834</t>
         </is>
       </c>
       <c r="J11" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
         </is>
       </c>
       <c r="K11" s="6"/>
-      <c r="L11" s="13" t="n">
-        <v>879630.0</v>
-      </c>
-      <c r="M11" s="13" t="n">
-        <v>70370.0</v>
-      </c>
+      <c r="L11" s="13"/>
+      <c r="M11" s="13"/>
       <c r="N11" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O11" s="13" t="n">
-        <v>950000.0</v>
+        <v>2364000.0</v>
       </c>
       <c r="P11" s="6" t="inlineStr">
         <is>
@@ -673,61 +653,57 @@
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>C25MLT</t>
+          <t>C25MTL</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>2729991</t>
+          <t>10798</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>07/10/2025</t>
+          <t>18/10/2025</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>3600445359</t>
+          <t>037165003053</t>
         </is>
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN THƯƠNG MẠI LONG THÀNH</t>
+          <t>HỘ KINH DOANH CỬA HÀNG THÀNH LẬP 1</t>
         </is>
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>Số 286, Đường Lê Duẩn, Ấp Văn Hải, Xã Long Thành, Tỉnh Đồng Nai</t>
+          <t>15A Kha Vạn Cân, Phường Tam Thắng, Thành phố Hồ Chí Minh, Việt Nam.</t>
         </is>
       </c>
       <c r="I12" s="7" t="inlineStr">
         <is>
-          <t>3502267355</t>
+          <t>3502469834</t>
         </is>
       </c>
       <c r="J12" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
         </is>
       </c>
       <c r="K12" s="6"/>
-      <c r="L12" s="13" t="n">
-        <v>925926.0</v>
-      </c>
-      <c r="M12" s="13" t="n">
-        <v>74074.0</v>
-      </c>
+      <c r="L12" s="13"/>
+      <c r="M12" s="13"/>
       <c r="N12" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O12" s="13" t="n">
-        <v>1000000.0</v>
+        <v>1200000.0</v>
       </c>
       <c r="P12" s="6" t="inlineStr">
         <is>
@@ -746,61 +722,57 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>C25MLT</t>
+          <t>C25MTL</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>2768014</t>
+          <t>10799</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>11/10/2025</t>
+          <t>18/10/2025</t>
         </is>
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
-          <t>3600445359</t>
+          <t>037165003053</t>
         </is>
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN THƯƠNG MẠI LONG THÀNH</t>
+          <t>HỘ KINH DOANH CỬA HÀNG THÀNH LẬP 1</t>
         </is>
       </c>
       <c r="H13" s="6" t="inlineStr">
         <is>
-          <t>Số 286, Đường Lê Duẩn, Ấp Văn Hải, Xã Long Thành, Tỉnh Đồng Nai</t>
+          <t>15A Kha Vạn Cân, Phường Tam Thắng, Thành phố Hồ Chí Minh, Việt Nam.</t>
         </is>
       </c>
       <c r="I13" s="7" t="inlineStr">
         <is>
-          <t>3502267355</t>
+          <t>3502469834</t>
         </is>
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
         </is>
       </c>
       <c r="K13" s="6"/>
-      <c r="L13" s="13" t="n">
-        <v>879630.0</v>
-      </c>
-      <c r="M13" s="13" t="n">
-        <v>70370.0</v>
-      </c>
+      <c r="L13" s="13"/>
+      <c r="M13" s="13"/>
       <c r="N13" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O13" s="13" t="n">
-        <v>950000.0</v>
+        <v>786000.0</v>
       </c>
       <c r="P13" s="6" t="inlineStr">
         <is>
@@ -819,61 +791,57 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>C25MLT</t>
+          <t>C25MYY</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>2801622</t>
+          <t>2367</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>14/10/2025</t>
+          <t>18/10/2025</t>
         </is>
       </c>
       <c r="F14" s="7" t="inlineStr">
         <is>
-          <t>3600445359</t>
+          <t>037184012312</t>
         </is>
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN THƯƠNG MẠI LONG THÀNH</t>
+          <t>HỘ KINH DOANH PHẠM HẢI QUỲNH ANH</t>
         </is>
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
-          <t>Số 286, Đường Lê Duẩn, Ấp Văn Hải, Xã Long Thành, Tỉnh Đồng Nai</t>
+          <t>Số 45B đường Đoàn Thị Điểm, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam.</t>
         </is>
       </c>
       <c r="I14" s="7" t="inlineStr">
         <is>
-          <t>3502267355</t>
+          <t>3502469834</t>
         </is>
       </c>
       <c r="J14" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
         </is>
       </c>
       <c r="K14" s="6"/>
-      <c r="L14" s="13" t="n">
-        <v>925926.0</v>
-      </c>
-      <c r="M14" s="13" t="n">
-        <v>74074.0</v>
-      </c>
+      <c r="L14" s="13"/>
+      <c r="M14" s="13"/>
       <c r="N14" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O14" s="13" t="n">
-        <v>1000000.0</v>
+        <v>4950000.0</v>
       </c>
       <c r="P14" s="6" t="inlineStr">
         <is>
@@ -892,61 +860,57 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>C25MLT</t>
+          <t>C25MTH</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>2829496</t>
+          <t>87</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
-          <t>17/10/2025</t>
+          <t>13/10/2025</t>
         </is>
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
-          <t>3600445359</t>
+          <t>077094004359</t>
         </is>
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN THƯƠNG MẠI LONG THÀNH</t>
+          <t>HỘ KINH DOANH HẢI SẢN TƯ HÀ</t>
         </is>
       </c>
       <c r="H15" s="6" t="inlineStr">
         <is>
-          <t>Số 286, Đường Lê Duẩn, Ấp Văn Hải, Xã Long Thành, Tỉnh Đồng Nai</t>
+          <t>10 Hoàng Hoa Thám, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I15" s="7" t="inlineStr">
         <is>
-          <t>3502267355</t>
+          <t>3502469834</t>
         </is>
       </c>
       <c r="J15" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
         </is>
       </c>
       <c r="K15" s="6"/>
-      <c r="L15" s="13" t="n">
-        <v>925926.0</v>
-      </c>
-      <c r="M15" s="13" t="n">
-        <v>74074.0</v>
-      </c>
+      <c r="L15" s="13"/>
+      <c r="M15" s="13"/>
       <c r="N15" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O15" s="13" t="n">
-        <v>1000000.0</v>
+        <v>4365000.0</v>
       </c>
       <c r="P15" s="6" t="inlineStr">
         <is>
@@ -965,61 +929,57 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>C25MLT</t>
+          <t>C25MND</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>2848178</t>
+          <t>45</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>19/10/2025</t>
+          <t>15/10/2025</t>
         </is>
       </c>
       <c r="F16" s="7" t="inlineStr">
         <is>
-          <t>3600445359</t>
+          <t>095194004728</t>
         </is>
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN THƯƠNG MẠI LONG THÀNH</t>
+          <t>HỘ KINH DOANH NGUYỄN THỊ NGỌC DIỆP</t>
         </is>
       </c>
       <c r="H16" s="6" t="inlineStr">
         <is>
-          <t>Số 286, Đường Lê Duẩn, Ấp Văn Hải, Xã Long Thành, Tỉnh Đồng Nai</t>
+          <t>Lô 92 Khu chợ đêm Quốc lộ 56, Phường Bà Rịa, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I16" s="7" t="inlineStr">
         <is>
-          <t>3502267355</t>
+          <t>3502469834</t>
         </is>
       </c>
       <c r="J16" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
         </is>
       </c>
       <c r="K16" s="6"/>
-      <c r="L16" s="13" t="n">
-        <v>898148.0</v>
-      </c>
-      <c r="M16" s="13" t="n">
-        <v>71852.0</v>
-      </c>
+      <c r="L16" s="13"/>
+      <c r="M16" s="13"/>
       <c r="N16" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O16" s="13" t="n">
-        <v>970000.0</v>
+        <v>3420000.0</v>
       </c>
       <c r="P16" s="6" t="inlineStr">
         <is>
@@ -1038,61 +998,57 @@
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>C25MLT</t>
+          <t>C25MND</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>2876011</t>
+          <t>53</t>
         </is>
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
-          <t>22/10/2025</t>
+          <t>17/10/2025</t>
         </is>
       </c>
       <c r="F17" s="7" t="inlineStr">
         <is>
-          <t>3600445359</t>
+          <t>095194004728</t>
         </is>
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN THƯƠNG MẠI LONG THÀNH</t>
+          <t>HỘ KINH DOANH NGUYỄN THỊ NGỌC DIỆP</t>
         </is>
       </c>
       <c r="H17" s="6" t="inlineStr">
         <is>
-          <t>Số 286, Đường Lê Duẩn, Ấp Văn Hải, Xã Long Thành, Tỉnh Đồng Nai</t>
+          <t>Lô 92 Khu chợ đêm Quốc lộ 56, Phường Bà Rịa, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I17" s="7" t="inlineStr">
         <is>
-          <t>3502267355</t>
+          <t>3502469834</t>
         </is>
       </c>
       <c r="J17" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
         </is>
       </c>
       <c r="K17" s="6"/>
-      <c r="L17" s="13" t="n">
-        <v>833333.0</v>
-      </c>
-      <c r="M17" s="13" t="n">
-        <v>66667.0</v>
-      </c>
+      <c r="L17" s="13"/>
+      <c r="M17" s="13"/>
       <c r="N17" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O17" s="13" t="n">
-        <v>900000.0</v>
+        <v>3060000.0</v>
       </c>
       <c r="P17" s="6" t="inlineStr">
         <is>
@@ -1111,61 +1067,57 @@
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>C25MLT</t>
+          <t>C25MND</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>2888579</t>
+          <t>63</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>23/10/2025</t>
+          <t>26/10/2025</t>
         </is>
       </c>
       <c r="F18" s="7" t="inlineStr">
         <is>
-          <t>3600445359</t>
+          <t>095194004728</t>
         </is>
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN THƯƠNG MẠI LONG THÀNH</t>
+          <t>HỘ KINH DOANH NGUYỄN THỊ NGỌC DIỆP</t>
         </is>
       </c>
       <c r="H18" s="6" t="inlineStr">
         <is>
-          <t>Số 286, Đường Lê Duẩn, Ấp Văn Hải, Xã Long Thành, Tỉnh Đồng Nai</t>
+          <t>Lô 92 Khu chợ đêm Quốc lộ 56, Phường Bà Rịa, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I18" s="7" t="inlineStr">
         <is>
-          <t>3502267355</t>
+          <t>3502469834</t>
         </is>
       </c>
       <c r="J18" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
         </is>
       </c>
       <c r="K18" s="6"/>
-      <c r="L18" s="13" t="n">
-        <v>462963.0</v>
-      </c>
-      <c r="M18" s="13" t="n">
-        <v>37037.0</v>
-      </c>
+      <c r="L18" s="13"/>
+      <c r="M18" s="13"/>
       <c r="N18" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O18" s="13" t="n">
-        <v>500000.0</v>
+        <v>3598000.0</v>
       </c>
       <c r="P18" s="6" t="inlineStr">
         <is>
@@ -1189,56 +1141,56 @@
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>C25MLT</t>
+          <t>C25MYY</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>2896815</t>
+          <t>376</t>
         </is>
       </c>
       <c r="E19" s="7" t="inlineStr">
         <is>
-          <t>24/10/2025</t>
+          <t>30/10/2025</t>
         </is>
       </c>
       <c r="F19" s="7" t="inlineStr">
         <is>
-          <t>3600445359</t>
+          <t>3500513118</t>
         </is>
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN THƯƠNG MẠI LONG THÀNH</t>
+          <t>DOANH NGHIỆP TƯ NHÂN NHÀ MÁY NƯỚC ĐÁ YẾN LINH</t>
         </is>
       </c>
       <c r="H19" s="6" t="inlineStr">
         <is>
-          <t>Số 286, Đường Lê Duẩn, Ấp Văn Hải, Xã Long Thành, Tỉnh Đồng Nai</t>
+          <t>60/14  Phạm Hồng Thái, Phường Tam Thắng, Thành phố Hồ Chí Minh, Việt Nam.</t>
         </is>
       </c>
       <c r="I19" s="7" t="inlineStr">
         <is>
-          <t>3502267355</t>
+          <t>3502469834</t>
         </is>
       </c>
       <c r="J19" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
         </is>
       </c>
       <c r="K19" s="6"/>
       <c r="L19" s="13" t="n">
-        <v>462963.0</v>
+        <v>3707407.0</v>
       </c>
       <c r="M19" s="13" t="n">
-        <v>37037.0</v>
+        <v>296593.0</v>
       </c>
       <c r="N19" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O19" s="13" t="n">
-        <v>500000.0</v>
+        <v>4004000.0</v>
       </c>
       <c r="P19" s="6" t="inlineStr">
         <is>
@@ -1246,736 +1198,6 @@
         </is>
       </c>
       <c r="Q19" s="6" t="inlineStr">
-        <is>
-          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="4" t="n">
-        <v>14.0</v>
-      </c>
-      <c r="B20" s="7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C20" s="6" t="inlineStr">
-        <is>
-          <t>C25MLT</t>
-        </is>
-      </c>
-      <c r="D20" s="7" t="inlineStr">
-        <is>
-          <t>2897086</t>
-        </is>
-      </c>
-      <c r="E20" s="7" t="inlineStr">
-        <is>
-          <t>24/10/2025</t>
-        </is>
-      </c>
-      <c r="F20" s="7" t="inlineStr">
-        <is>
-          <t>3600445359</t>
-        </is>
-      </c>
-      <c r="G20" s="6" t="inlineStr">
-        <is>
-          <t>CÔNG TY CỔ PHẦN THƯƠNG MẠI LONG THÀNH</t>
-        </is>
-      </c>
-      <c r="H20" s="6" t="inlineStr">
-        <is>
-          <t>Số 286, Đường Lê Duẩn, Ấp Văn Hải, Xã Long Thành, Tỉnh Đồng Nai</t>
-        </is>
-      </c>
-      <c r="I20" s="7" t="inlineStr">
-        <is>
-          <t>3502267355</t>
-        </is>
-      </c>
-      <c r="J20" s="6" t="inlineStr">
-        <is>
-          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
-        </is>
-      </c>
-      <c r="K20" s="6"/>
-      <c r="L20" s="13" t="n">
-        <v>416667.0</v>
-      </c>
-      <c r="M20" s="13" t="n">
-        <v>33333.0</v>
-      </c>
-      <c r="N20" s="13" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="O20" s="13" t="n">
-        <v>450000.0</v>
-      </c>
-      <c r="P20" s="6" t="inlineStr">
-        <is>
-          <t>Hóa đơn mới</t>
-        </is>
-      </c>
-      <c r="Q20" s="6" t="inlineStr">
-        <is>
-          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="4" t="n">
-        <v>15.0</v>
-      </c>
-      <c r="B21" s="7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C21" s="6" t="inlineStr">
-        <is>
-          <t>C25MLT</t>
-        </is>
-      </c>
-      <c r="D21" s="7" t="inlineStr">
-        <is>
-          <t>2897119</t>
-        </is>
-      </c>
-      <c r="E21" s="7" t="inlineStr">
-        <is>
-          <t>24/10/2025</t>
-        </is>
-      </c>
-      <c r="F21" s="7" t="inlineStr">
-        <is>
-          <t>3600445359</t>
-        </is>
-      </c>
-      <c r="G21" s="6" t="inlineStr">
-        <is>
-          <t>CÔNG TY CỔ PHẦN THƯƠNG MẠI LONG THÀNH</t>
-        </is>
-      </c>
-      <c r="H21" s="6" t="inlineStr">
-        <is>
-          <t>Số 286, Đường Lê Duẩn, Ấp Văn Hải, Xã Long Thành, Tỉnh Đồng Nai</t>
-        </is>
-      </c>
-      <c r="I21" s="7" t="inlineStr">
-        <is>
-          <t>3502267355</t>
-        </is>
-      </c>
-      <c r="J21" s="6" t="inlineStr">
-        <is>
-          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
-        </is>
-      </c>
-      <c r="K21" s="6"/>
-      <c r="L21" s="13" t="n">
-        <v>416667.0</v>
-      </c>
-      <c r="M21" s="13" t="n">
-        <v>33333.0</v>
-      </c>
-      <c r="N21" s="13" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="O21" s="13" t="n">
-        <v>450000.0</v>
-      </c>
-      <c r="P21" s="6" t="inlineStr">
-        <is>
-          <t>Hóa đơn mới</t>
-        </is>
-      </c>
-      <c r="Q21" s="6" t="inlineStr">
-        <is>
-          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="4" t="n">
-        <v>16.0</v>
-      </c>
-      <c r="B22" s="7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C22" s="6" t="inlineStr">
-        <is>
-          <t>C25MLT</t>
-        </is>
-      </c>
-      <c r="D22" s="7" t="inlineStr">
-        <is>
-          <t>2908853</t>
-        </is>
-      </c>
-      <c r="E22" s="7" t="inlineStr">
-        <is>
-          <t>25/10/2025</t>
-        </is>
-      </c>
-      <c r="F22" s="7" t="inlineStr">
-        <is>
-          <t>3600445359</t>
-        </is>
-      </c>
-      <c r="G22" s="6" t="inlineStr">
-        <is>
-          <t>CÔNG TY CỔ PHẦN THƯƠNG MẠI LONG THÀNH</t>
-        </is>
-      </c>
-      <c r="H22" s="6" t="inlineStr">
-        <is>
-          <t>Số 286, Đường Lê Duẩn, Ấp Văn Hải, Xã Long Thành, Tỉnh Đồng Nai</t>
-        </is>
-      </c>
-      <c r="I22" s="7" t="inlineStr">
-        <is>
-          <t>3502267355</t>
-        </is>
-      </c>
-      <c r="J22" s="6" t="inlineStr">
-        <is>
-          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
-        </is>
-      </c>
-      <c r="K22" s="6"/>
-      <c r="L22" s="13" t="n">
-        <v>462963.0</v>
-      </c>
-      <c r="M22" s="13" t="n">
-        <v>37037.0</v>
-      </c>
-      <c r="N22" s="13" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="O22" s="13" t="n">
-        <v>500000.0</v>
-      </c>
-      <c r="P22" s="6" t="inlineStr">
-        <is>
-          <t>Hóa đơn mới</t>
-        </is>
-      </c>
-      <c r="Q22" s="6" t="inlineStr">
-        <is>
-          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="4" t="n">
-        <v>17.0</v>
-      </c>
-      <c r="B23" s="7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C23" s="6" t="inlineStr">
-        <is>
-          <t>C25MLT</t>
-        </is>
-      </c>
-      <c r="D23" s="7" t="inlineStr">
-        <is>
-          <t>2909096</t>
-        </is>
-      </c>
-      <c r="E23" s="7" t="inlineStr">
-        <is>
-          <t>25/10/2025</t>
-        </is>
-      </c>
-      <c r="F23" s="7" t="inlineStr">
-        <is>
-          <t>3600445359</t>
-        </is>
-      </c>
-      <c r="G23" s="6" t="inlineStr">
-        <is>
-          <t>CÔNG TY CỔ PHẦN THƯƠNG MẠI LONG THÀNH</t>
-        </is>
-      </c>
-      <c r="H23" s="6" t="inlineStr">
-        <is>
-          <t>Số 286, Đường Lê Duẩn, Ấp Văn Hải, Xã Long Thành, Tỉnh Đồng Nai</t>
-        </is>
-      </c>
-      <c r="I23" s="7" t="inlineStr">
-        <is>
-          <t>3502267355</t>
-        </is>
-      </c>
-      <c r="J23" s="6" t="inlineStr">
-        <is>
-          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
-        </is>
-      </c>
-      <c r="K23" s="6"/>
-      <c r="L23" s="13" t="n">
-        <v>462963.0</v>
-      </c>
-      <c r="M23" s="13" t="n">
-        <v>37037.0</v>
-      </c>
-      <c r="N23" s="13" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="O23" s="13" t="n">
-        <v>500000.0</v>
-      </c>
-      <c r="P23" s="6" t="inlineStr">
-        <is>
-          <t>Hóa đơn mới</t>
-        </is>
-      </c>
-      <c r="Q23" s="6" t="inlineStr">
-        <is>
-          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="4" t="n">
-        <v>18.0</v>
-      </c>
-      <c r="B24" s="7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C24" s="6" t="inlineStr">
-        <is>
-          <t>C25MLT</t>
-        </is>
-      </c>
-      <c r="D24" s="7" t="inlineStr">
-        <is>
-          <t>2909862</t>
-        </is>
-      </c>
-      <c r="E24" s="7" t="inlineStr">
-        <is>
-          <t>25/10/2025</t>
-        </is>
-      </c>
-      <c r="F24" s="7" t="inlineStr">
-        <is>
-          <t>3600445359</t>
-        </is>
-      </c>
-      <c r="G24" s="6" t="inlineStr">
-        <is>
-          <t>CÔNG TY CỔ PHẦN THƯƠNG MẠI LONG THÀNH</t>
-        </is>
-      </c>
-      <c r="H24" s="6" t="inlineStr">
-        <is>
-          <t>Số 286, Đường Lê Duẩn, Ấp Văn Hải, Xã Long Thành, Tỉnh Đồng Nai</t>
-        </is>
-      </c>
-      <c r="I24" s="7" t="inlineStr">
-        <is>
-          <t>3502267355</t>
-        </is>
-      </c>
-      <c r="J24" s="6" t="inlineStr">
-        <is>
-          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
-        </is>
-      </c>
-      <c r="K24" s="6"/>
-      <c r="L24" s="13" t="n">
-        <v>898148.0</v>
-      </c>
-      <c r="M24" s="13" t="n">
-        <v>71852.0</v>
-      </c>
-      <c r="N24" s="13" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="O24" s="13" t="n">
-        <v>970000.0</v>
-      </c>
-      <c r="P24" s="6" t="inlineStr">
-        <is>
-          <t>Hóa đơn mới</t>
-        </is>
-      </c>
-      <c r="Q24" s="6" t="inlineStr">
-        <is>
-          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="4" t="n">
-        <v>19.0</v>
-      </c>
-      <c r="B25" s="7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C25" s="6" t="inlineStr">
-        <is>
-          <t>C25MLT</t>
-        </is>
-      </c>
-      <c r="D25" s="7" t="inlineStr">
-        <is>
-          <t>2926117</t>
-        </is>
-      </c>
-      <c r="E25" s="7" t="inlineStr">
-        <is>
-          <t>27/10/2025</t>
-        </is>
-      </c>
-      <c r="F25" s="7" t="inlineStr">
-        <is>
-          <t>3600445359</t>
-        </is>
-      </c>
-      <c r="G25" s="6" t="inlineStr">
-        <is>
-          <t>CÔNG TY CỔ PHẦN THƯƠNG MẠI LONG THÀNH</t>
-        </is>
-      </c>
-      <c r="H25" s="6" t="inlineStr">
-        <is>
-          <t>Số 286, Đường Lê Duẩn, Ấp Văn Hải, Xã Long Thành, Tỉnh Đồng Nai</t>
-        </is>
-      </c>
-      <c r="I25" s="7" t="inlineStr">
-        <is>
-          <t>3502267355</t>
-        </is>
-      </c>
-      <c r="J25" s="6" t="inlineStr">
-        <is>
-          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
-        </is>
-      </c>
-      <c r="K25" s="6"/>
-      <c r="L25" s="13" t="n">
-        <v>925926.0</v>
-      </c>
-      <c r="M25" s="13" t="n">
-        <v>74074.0</v>
-      </c>
-      <c r="N25" s="13" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="O25" s="13" t="n">
-        <v>1000000.0</v>
-      </c>
-      <c r="P25" s="6" t="inlineStr">
-        <is>
-          <t>Hóa đơn mới</t>
-        </is>
-      </c>
-      <c r="Q25" s="6" t="inlineStr">
-        <is>
-          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="4" t="n">
-        <v>20.0</v>
-      </c>
-      <c r="B26" s="7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C26" s="6" t="inlineStr">
-        <is>
-          <t>C25MLT</t>
-        </is>
-      </c>
-      <c r="D26" s="7" t="inlineStr">
-        <is>
-          <t>2933853</t>
-        </is>
-      </c>
-      <c r="E26" s="7" t="inlineStr">
-        <is>
-          <t>27/10/2025</t>
-        </is>
-      </c>
-      <c r="F26" s="7" t="inlineStr">
-        <is>
-          <t>3600445359</t>
-        </is>
-      </c>
-      <c r="G26" s="6" t="inlineStr">
-        <is>
-          <t>CÔNG TY CỔ PHẦN THƯƠNG MẠI LONG THÀNH</t>
-        </is>
-      </c>
-      <c r="H26" s="6" t="inlineStr">
-        <is>
-          <t>Số 286, Đường Lê Duẩn, Ấp Văn Hải, Xã Long Thành, Tỉnh Đồng Nai</t>
-        </is>
-      </c>
-      <c r="I26" s="7" t="inlineStr">
-        <is>
-          <t>3502267355</t>
-        </is>
-      </c>
-      <c r="J26" s="6" t="inlineStr">
-        <is>
-          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
-        </is>
-      </c>
-      <c r="K26" s="6"/>
-      <c r="L26" s="13" t="n">
-        <v>462963.0</v>
-      </c>
-      <c r="M26" s="13" t="n">
-        <v>37037.0</v>
-      </c>
-      <c r="N26" s="13" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="O26" s="13" t="n">
-        <v>500000.0</v>
-      </c>
-      <c r="P26" s="6" t="inlineStr">
-        <is>
-          <t>Hóa đơn mới</t>
-        </is>
-      </c>
-      <c r="Q26" s="6" t="inlineStr">
-        <is>
-          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="4" t="n">
-        <v>21.0</v>
-      </c>
-      <c r="B27" s="7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C27" s="6" t="inlineStr">
-        <is>
-          <t>C25MLT</t>
-        </is>
-      </c>
-      <c r="D27" s="7" t="inlineStr">
-        <is>
-          <t>2939649</t>
-        </is>
-      </c>
-      <c r="E27" s="7" t="inlineStr">
-        <is>
-          <t>28/10/2025</t>
-        </is>
-      </c>
-      <c r="F27" s="7" t="inlineStr">
-        <is>
-          <t>3600445359</t>
-        </is>
-      </c>
-      <c r="G27" s="6" t="inlineStr">
-        <is>
-          <t>CÔNG TY CỔ PHẦN THƯƠNG MẠI LONG THÀNH</t>
-        </is>
-      </c>
-      <c r="H27" s="6" t="inlineStr">
-        <is>
-          <t>Số 286, Đường Lê Duẩn, Ấp Văn Hải, Xã Long Thành, Tỉnh Đồng Nai</t>
-        </is>
-      </c>
-      <c r="I27" s="7" t="inlineStr">
-        <is>
-          <t>3502267355</t>
-        </is>
-      </c>
-      <c r="J27" s="6" t="inlineStr">
-        <is>
-          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
-        </is>
-      </c>
-      <c r="K27" s="6"/>
-      <c r="L27" s="13" t="n">
-        <v>893519.0</v>
-      </c>
-      <c r="M27" s="13" t="n">
-        <v>71481.0</v>
-      </c>
-      <c r="N27" s="13" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="O27" s="13" t="n">
-        <v>965000.0</v>
-      </c>
-      <c r="P27" s="6" t="inlineStr">
-        <is>
-          <t>Hóa đơn mới</t>
-        </is>
-      </c>
-      <c r="Q27" s="6" t="inlineStr">
-        <is>
-          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="4" t="n">
-        <v>22.0</v>
-      </c>
-      <c r="B28" s="7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C28" s="6" t="inlineStr">
-        <is>
-          <t>C25MLT</t>
-        </is>
-      </c>
-      <c r="D28" s="7" t="inlineStr">
-        <is>
-          <t>2950930</t>
-        </is>
-      </c>
-      <c r="E28" s="7" t="inlineStr">
-        <is>
-          <t>29/10/2025</t>
-        </is>
-      </c>
-      <c r="F28" s="7" t="inlineStr">
-        <is>
-          <t>3600445359</t>
-        </is>
-      </c>
-      <c r="G28" s="6" t="inlineStr">
-        <is>
-          <t>CÔNG TY CỔ PHẦN THƯƠNG MẠI LONG THÀNH</t>
-        </is>
-      </c>
-      <c r="H28" s="6" t="inlineStr">
-        <is>
-          <t>Số 286, Đường Lê Duẩn, Ấp Văn Hải, Xã Long Thành, Tỉnh Đồng Nai</t>
-        </is>
-      </c>
-      <c r="I28" s="7" t="inlineStr">
-        <is>
-          <t>3502267355</t>
-        </is>
-      </c>
-      <c r="J28" s="6" t="inlineStr">
-        <is>
-          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
-        </is>
-      </c>
-      <c r="K28" s="6"/>
-      <c r="L28" s="13" t="n">
-        <v>925926.0</v>
-      </c>
-      <c r="M28" s="13" t="n">
-        <v>74074.0</v>
-      </c>
-      <c r="N28" s="13" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="O28" s="13" t="n">
-        <v>1000000.0</v>
-      </c>
-      <c r="P28" s="6" t="inlineStr">
-        <is>
-          <t>Hóa đơn mới</t>
-        </is>
-      </c>
-      <c r="Q28" s="6" t="inlineStr">
-        <is>
-          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="4" t="n">
-        <v>23.0</v>
-      </c>
-      <c r="B29" s="7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C29" s="6" t="inlineStr">
-        <is>
-          <t>C25MLT</t>
-        </is>
-      </c>
-      <c r="D29" s="7" t="inlineStr">
-        <is>
-          <t>2968734</t>
-        </is>
-      </c>
-      <c r="E29" s="7" t="inlineStr">
-        <is>
-          <t>31/10/2025</t>
-        </is>
-      </c>
-      <c r="F29" s="7" t="inlineStr">
-        <is>
-          <t>3600445359</t>
-        </is>
-      </c>
-      <c r="G29" s="6" t="inlineStr">
-        <is>
-          <t>CÔNG TY CỔ PHẦN THƯƠNG MẠI LONG THÀNH</t>
-        </is>
-      </c>
-      <c r="H29" s="6" t="inlineStr">
-        <is>
-          <t>Số 286, Đường Lê Duẩn, Ấp Văn Hải, Xã Long Thành, Tỉnh Đồng Nai</t>
-        </is>
-      </c>
-      <c r="I29" s="7" t="inlineStr">
-        <is>
-          <t>3502267355</t>
-        </is>
-      </c>
-      <c r="J29" s="6" t="inlineStr">
-        <is>
-          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
-        </is>
-      </c>
-      <c r="K29" s="6"/>
-      <c r="L29" s="13" t="n">
-        <v>851852.0</v>
-      </c>
-      <c r="M29" s="13" t="n">
-        <v>68148.0</v>
-      </c>
-      <c r="N29" s="13" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="O29" s="13" t="n">
-        <v>920000.0</v>
-      </c>
-      <c r="P29" s="6" t="inlineStr">
-        <is>
-          <t>Hóa đơn mới</t>
-        </is>
-      </c>
-      <c r="Q29" s="6" t="inlineStr">
         <is>
           <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
         </is>

--- a/Hoadon/HDVao/10/HDDienTuMayTinhTien.xlsx
+++ b/Hoadon/HDVao/10/HDDienTuMayTinhTien.xlsx
@@ -308,57 +308,61 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>C25MVC</t>
+          <t>C25MDX</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>80</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>14/10/2025</t>
+          <t>04/10/2025</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>026078008681</t>
+          <t>0316603413</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>Hộ Kinh Doanh Trần Văn Cường (Phường 8)</t>
+          <t>CÔNG TY TNHH GIẢI PHÁP XÂY DỰNG 247</t>
         </is>
       </c>
       <c r="H7" s="6" t="inlineStr">
         <is>
-          <t>209 đường Bình Giã, Phường Tam Thắng, Hồ Chí Minh, Việt Nam</t>
+          <t>702/5 Lê Văn Khương, Phường Thới An, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I7" s="7" t="inlineStr">
         <is>
-          <t>3502469834</t>
+          <t>3501844024</t>
         </is>
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN ĐÔNG DƯƠNG VŨNG TÀU</t>
         </is>
       </c>
       <c r="K7" s="6"/>
-      <c r="L7" s="13"/>
-      <c r="M7" s="13"/>
+      <c r="L7" s="13" t="n">
+        <v>7.3379628E7</v>
+      </c>
+      <c r="M7" s="13" t="n">
+        <v>5870370.0</v>
+      </c>
       <c r="N7" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O7" s="13" t="n">
-        <v>2.039E7</v>
+        <v>7.9249998E7</v>
       </c>
       <c r="P7" s="6" t="inlineStr">
         <is>
@@ -377,57 +381,61 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>C25MVC</t>
+          <t>C25MPA</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>224</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>15/10/2025</t>
+          <t>11/10/2025</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>026078008681</t>
+          <t>3501547085</t>
         </is>
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>Hộ Kinh Doanh Trần Văn Cường (Phường 8)</t>
+          <t>CÔNG TY TNHH ĐẦU TƯ THƯƠNG MẠI XÂY DỰNG PHƯỚC AN</t>
         </is>
       </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
-          <t>209 đường Bình Giã, Phường Tam Thắng, Hồ Chí Minh, Việt Nam</t>
+          <t>Số 774 đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam.</t>
         </is>
       </c>
       <c r="I8" s="7" t="inlineStr">
         <is>
-          <t>3502469834</t>
+          <t>3501844024</t>
         </is>
       </c>
       <c r="J8" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN ĐÔNG DƯƠNG VŨNG TÀU</t>
         </is>
       </c>
       <c r="K8" s="6"/>
-      <c r="L8" s="13"/>
-      <c r="M8" s="13"/>
+      <c r="L8" s="13" t="n">
+        <v>9619444.0</v>
+      </c>
+      <c r="M8" s="13" t="n">
+        <v>769556.0</v>
+      </c>
       <c r="N8" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O8" s="13" t="n">
-        <v>5982500.0</v>
+        <v>1.0389E7</v>
       </c>
       <c r="P8" s="6" t="inlineStr">
         <is>
@@ -446,57 +454,61 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>C25MNM</t>
+          <t>C25MCC</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>231799</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>31/10/2025</t>
+          <t>03/10/2025</t>
         </is>
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>036165003642</t>
+          <t>3502280613</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>HỘ KINH DOANH NGUYỄN THỊ PHƯỢNG</t>
+          <t>CÔNG TY CỔ PHẦN DỊCH VỤ PHÁT TRIỂN GIAO THÔNG VẬN TẢI VŨNG TÀU</t>
         </is>
       </c>
       <c r="H9" s="6" t="inlineStr">
         <is>
-          <t>Quầy F44-46 Khu Hành Lang B Nhà Lồng Chợ Vũng Tàu, Phường Vũng Tàu, TP Hồ Chí Minh</t>
+          <t>LK10, đường Hàng Điều 1, Khu nhà ở Khang Linh, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I9" s="7" t="inlineStr">
         <is>
-          <t>3502469834</t>
+          <t>3501844024</t>
         </is>
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN ĐÔNG DƯƠNG VŨNG TÀU</t>
         </is>
       </c>
       <c r="K9" s="6"/>
-      <c r="L9" s="13"/>
-      <c r="M9" s="13"/>
+      <c r="L9" s="13" t="n">
+        <v>462963.0</v>
+      </c>
+      <c r="M9" s="13" t="n">
+        <v>37037.0</v>
+      </c>
       <c r="N9" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O9" s="13" t="n">
-        <v>2090000.0</v>
+        <v>500000.0</v>
       </c>
       <c r="P9" s="6" t="inlineStr">
         <is>
@@ -515,57 +527,61 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>C25MTL</t>
+          <t>C25MCC</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>10602</t>
+          <t>235045</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>04/10/2025</t>
+          <t>07/10/2025</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>037165003053</t>
+          <t>3502280613</t>
         </is>
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>HỘ KINH DOANH CỬA HÀNG THÀNH LẬP 1</t>
+          <t>CÔNG TY CỔ PHẦN DỊCH VỤ PHÁT TRIỂN GIAO THÔNG VẬN TẢI VŨNG TÀU</t>
         </is>
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>15A Kha Vạn Cân, Phường Tam Thắng, Thành phố Hồ Chí Minh, Việt Nam.</t>
+          <t>LK10, đường Hàng Điều 1, Khu nhà ở Khang Linh, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I10" s="7" t="inlineStr">
         <is>
-          <t>3502469834</t>
+          <t>3501844024</t>
         </is>
       </c>
       <c r="J10" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN ĐÔNG DƯƠNG VŨNG TÀU</t>
         </is>
       </c>
       <c r="K10" s="6"/>
-      <c r="L10" s="13"/>
-      <c r="M10" s="13"/>
+      <c r="L10" s="13" t="n">
+        <v>462963.0</v>
+      </c>
+      <c r="M10" s="13" t="n">
+        <v>37037.0</v>
+      </c>
       <c r="N10" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O10" s="13" t="n">
-        <v>1200000.0</v>
+        <v>500000.0</v>
       </c>
       <c r="P10" s="6" t="inlineStr">
         <is>
@@ -584,57 +600,61 @@
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>C25MTL</t>
+          <t>C25MCC</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>10603</t>
+          <t>239827</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t>04/10/2025</t>
+          <t>13/10/2025</t>
         </is>
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>037165003053</t>
+          <t>3502280613</t>
         </is>
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>HỘ KINH DOANH CỬA HÀNG THÀNH LẬP 1</t>
+          <t>CÔNG TY CỔ PHẦN DỊCH VỤ PHÁT TRIỂN GIAO THÔNG VẬN TẢI VŨNG TÀU</t>
         </is>
       </c>
       <c r="H11" s="6" t="inlineStr">
         <is>
-          <t>15A Kha Vạn Cân, Phường Tam Thắng, Thành phố Hồ Chí Minh, Việt Nam.</t>
+          <t>LK10, đường Hàng Điều 1, Khu nhà ở Khang Linh, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I11" s="7" t="inlineStr">
         <is>
-          <t>3502469834</t>
+          <t>3501844024</t>
         </is>
       </c>
       <c r="J11" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN ĐÔNG DƯƠNG VŨNG TÀU</t>
         </is>
       </c>
       <c r="K11" s="6"/>
-      <c r="L11" s="13"/>
-      <c r="M11" s="13"/>
+      <c r="L11" s="13" t="n">
+        <v>462963.0</v>
+      </c>
+      <c r="M11" s="13" t="n">
+        <v>37037.0</v>
+      </c>
       <c r="N11" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O11" s="13" t="n">
-        <v>2364000.0</v>
+        <v>500000.0</v>
       </c>
       <c r="P11" s="6" t="inlineStr">
         <is>
@@ -653,57 +673,61 @@
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>C25MTL</t>
+          <t>C25MCC</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>10798</t>
+          <t>242539</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>18/10/2025</t>
+          <t>16/10/2025</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>037165003053</t>
+          <t>3502280613</t>
         </is>
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>HỘ KINH DOANH CỬA HÀNG THÀNH LẬP 1</t>
+          <t>CÔNG TY CỔ PHẦN DỊCH VỤ PHÁT TRIỂN GIAO THÔNG VẬN TẢI VŨNG TÀU</t>
         </is>
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>15A Kha Vạn Cân, Phường Tam Thắng, Thành phố Hồ Chí Minh, Việt Nam.</t>
+          <t>LK10, đường Hàng Điều 1, Khu nhà ở Khang Linh, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I12" s="7" t="inlineStr">
         <is>
-          <t>3502469834</t>
+          <t>3501844024</t>
         </is>
       </c>
       <c r="J12" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN ĐÔNG DƯƠNG VŨNG TÀU</t>
         </is>
       </c>
       <c r="K12" s="6"/>
-      <c r="L12" s="13"/>
-      <c r="M12" s="13"/>
+      <c r="L12" s="13" t="n">
+        <v>462963.0</v>
+      </c>
+      <c r="M12" s="13" t="n">
+        <v>37037.0</v>
+      </c>
       <c r="N12" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O12" s="13" t="n">
-        <v>1200000.0</v>
+        <v>500000.0</v>
       </c>
       <c r="P12" s="6" t="inlineStr">
         <is>
@@ -722,57 +746,61 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>C25MTL</t>
+          <t>C25MCC</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>10799</t>
+          <t>242951</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>18/10/2025</t>
+          <t>17/10/2025</t>
         </is>
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
-          <t>037165003053</t>
+          <t>3502280613</t>
         </is>
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>HỘ KINH DOANH CỬA HÀNG THÀNH LẬP 1</t>
+          <t>CÔNG TY CỔ PHẦN DỊCH VỤ PHÁT TRIỂN GIAO THÔNG VẬN TẢI VŨNG TÀU</t>
         </is>
       </c>
       <c r="H13" s="6" t="inlineStr">
         <is>
-          <t>15A Kha Vạn Cân, Phường Tam Thắng, Thành phố Hồ Chí Minh, Việt Nam.</t>
+          <t>LK10, đường Hàng Điều 1, Khu nhà ở Khang Linh, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I13" s="7" t="inlineStr">
         <is>
-          <t>3502469834</t>
+          <t>3501844024</t>
         </is>
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN ĐÔNG DƯƠNG VŨNG TÀU</t>
         </is>
       </c>
       <c r="K13" s="6"/>
-      <c r="L13" s="13"/>
-      <c r="M13" s="13"/>
+      <c r="L13" s="13" t="n">
+        <v>925926.0</v>
+      </c>
+      <c r="M13" s="13" t="n">
+        <v>74074.0</v>
+      </c>
       <c r="N13" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O13" s="13" t="n">
-        <v>786000.0</v>
+        <v>1000000.0</v>
       </c>
       <c r="P13" s="6" t="inlineStr">
         <is>
@@ -791,57 +819,61 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>C25MYY</t>
+          <t>C25MCC</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>2367</t>
+          <t>245911</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>18/10/2025</t>
+          <t>20/10/2025</t>
         </is>
       </c>
       <c r="F14" s="7" t="inlineStr">
         <is>
-          <t>037184012312</t>
+          <t>3502280613</t>
         </is>
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>HỘ KINH DOANH PHẠM HẢI QUỲNH ANH</t>
+          <t>CÔNG TY CỔ PHẦN DỊCH VỤ PHÁT TRIỂN GIAO THÔNG VẬN TẢI VŨNG TÀU</t>
         </is>
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
-          <t>Số 45B đường Đoàn Thị Điểm, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam.</t>
+          <t>Số 15 đường Sông Hương, Khu nhà ở Khang Linh, Phường Rạch Dừa, Thành Phố Hồ Chí Minh</t>
         </is>
       </c>
       <c r="I14" s="7" t="inlineStr">
         <is>
-          <t>3502469834</t>
+          <t>3501844024</t>
         </is>
       </c>
       <c r="J14" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN ĐÔNG DƯƠNG VŨNG TÀU</t>
         </is>
       </c>
       <c r="K14" s="6"/>
-      <c r="L14" s="13"/>
-      <c r="M14" s="13"/>
+      <c r="L14" s="13" t="n">
+        <v>462963.0</v>
+      </c>
+      <c r="M14" s="13" t="n">
+        <v>37037.0</v>
+      </c>
       <c r="N14" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O14" s="13" t="n">
-        <v>4950000.0</v>
+        <v>500000.0</v>
       </c>
       <c r="P14" s="6" t="inlineStr">
         <is>
@@ -860,57 +892,61 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>C25MTH</t>
+          <t>C25MCC</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>247961</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
-          <t>13/10/2025</t>
+          <t>23/10/2025</t>
         </is>
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
-          <t>077094004359</t>
+          <t>3502280613</t>
         </is>
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>HỘ KINH DOANH HẢI SẢN TƯ HÀ</t>
+          <t>CÔNG TY CỔ PHẦN DỊCH VỤ PHÁT TRIỂN GIAO THÔNG VẬN TẢI VŨNG TÀU</t>
         </is>
       </c>
       <c r="H15" s="6" t="inlineStr">
         <is>
-          <t>10 Hoàng Hoa Thám, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 15 đường Sông Hương, Khu nhà ở Khang Linh, Phường Rạch Dừa, Thành Phố Hồ Chí Minh</t>
         </is>
       </c>
       <c r="I15" s="7" t="inlineStr">
         <is>
-          <t>3502469834</t>
+          <t>3501844024</t>
         </is>
       </c>
       <c r="J15" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN ĐÔNG DƯƠNG VŨNG TÀU</t>
         </is>
       </c>
       <c r="K15" s="6"/>
-      <c r="L15" s="13"/>
-      <c r="M15" s="13"/>
+      <c r="L15" s="13" t="n">
+        <v>925926.0</v>
+      </c>
+      <c r="M15" s="13" t="n">
+        <v>74074.0</v>
+      </c>
       <c r="N15" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O15" s="13" t="n">
-        <v>4365000.0</v>
+        <v>1000000.0</v>
       </c>
       <c r="P15" s="6" t="inlineStr">
         <is>
@@ -929,57 +965,61 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>C25MND</t>
+          <t>C25MCC</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>248595</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>15/10/2025</t>
+          <t>24/10/2025</t>
         </is>
       </c>
       <c r="F16" s="7" t="inlineStr">
         <is>
-          <t>095194004728</t>
+          <t>3502280613</t>
         </is>
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>HỘ KINH DOANH NGUYỄN THỊ NGỌC DIỆP</t>
+          <t>CÔNG TY CỔ PHẦN DỊCH VỤ PHÁT TRIỂN GIAO THÔNG VẬN TẢI VŨNG TÀU</t>
         </is>
       </c>
       <c r="H16" s="6" t="inlineStr">
         <is>
-          <t>Lô 92 Khu chợ đêm Quốc lộ 56, Phường Bà Rịa, Thành Phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 15 đường Sông Hương, Khu nhà ở Khang Linh, Phường Rạch Dừa, Thành Phố Hồ Chí Minh</t>
         </is>
       </c>
       <c r="I16" s="7" t="inlineStr">
         <is>
-          <t>3502469834</t>
+          <t>3501844024</t>
         </is>
       </c>
       <c r="J16" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN ĐÔNG DƯƠNG VŨNG TÀU</t>
         </is>
       </c>
       <c r="K16" s="6"/>
-      <c r="L16" s="13"/>
-      <c r="M16" s="13"/>
+      <c r="L16" s="13" t="n">
+        <v>462963.0</v>
+      </c>
+      <c r="M16" s="13" t="n">
+        <v>37037.0</v>
+      </c>
       <c r="N16" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O16" s="13" t="n">
-        <v>3420000.0</v>
+        <v>500000.0</v>
       </c>
       <c r="P16" s="6" t="inlineStr">
         <is>
@@ -998,57 +1038,61 @@
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>C25MND</t>
+          <t>C25MCC</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>251494</t>
         </is>
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
-          <t>17/10/2025</t>
+          <t>28/10/2025</t>
         </is>
       </c>
       <c r="F17" s="7" t="inlineStr">
         <is>
-          <t>095194004728</t>
+          <t>3502280613</t>
         </is>
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>HỘ KINH DOANH NGUYỄN THỊ NGỌC DIỆP</t>
+          <t>CÔNG TY CỔ PHẦN DỊCH VỤ PHÁT TRIỂN GIAO THÔNG VẬN TẢI VŨNG TÀU</t>
         </is>
       </c>
       <c r="H17" s="6" t="inlineStr">
         <is>
-          <t>Lô 92 Khu chợ đêm Quốc lộ 56, Phường Bà Rịa, Thành Phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 15 đường Sông Hương, Khu nhà ở Khang Linh, Phường Rạch Dừa, Thành Phố Hồ Chí Minh</t>
         </is>
       </c>
       <c r="I17" s="7" t="inlineStr">
         <is>
-          <t>3502469834</t>
+          <t>3501844024</t>
         </is>
       </c>
       <c r="J17" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN ĐÔNG DƯƠNG VŨNG TÀU</t>
         </is>
       </c>
       <c r="K17" s="6"/>
-      <c r="L17" s="13"/>
-      <c r="M17" s="13"/>
+      <c r="L17" s="13" t="n">
+        <v>462963.0</v>
+      </c>
+      <c r="M17" s="13" t="n">
+        <v>37037.0</v>
+      </c>
       <c r="N17" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O17" s="13" t="n">
-        <v>3060000.0</v>
+        <v>500000.0</v>
       </c>
       <c r="P17" s="6" t="inlineStr">
         <is>
@@ -1067,57 +1111,61 @@
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>C25MND</t>
+          <t>C25MCC</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>252995</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>26/10/2025</t>
+          <t>30/10/2025</t>
         </is>
       </c>
       <c r="F18" s="7" t="inlineStr">
         <is>
-          <t>095194004728</t>
+          <t>3502280613</t>
         </is>
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>HỘ KINH DOANH NGUYỄN THỊ NGỌC DIỆP</t>
+          <t>CÔNG TY CỔ PHẦN DỊCH VỤ PHÁT TRIỂN GIAO THÔNG VẬN TẢI VŨNG TÀU</t>
         </is>
       </c>
       <c r="H18" s="6" t="inlineStr">
         <is>
-          <t>Lô 92 Khu chợ đêm Quốc lộ 56, Phường Bà Rịa, Thành Phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 15 đường Sông Hương, Khu nhà ở Khang Linh, Phường Rạch Dừa, Thành Phố Hồ Chí Minh</t>
         </is>
       </c>
       <c r="I18" s="7" t="inlineStr">
         <is>
-          <t>3502469834</t>
+          <t>3501844024</t>
         </is>
       </c>
       <c r="J18" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN ĐÔNG DƯƠNG VŨNG TÀU</t>
         </is>
       </c>
       <c r="K18" s="6"/>
-      <c r="L18" s="13"/>
-      <c r="M18" s="13"/>
+      <c r="L18" s="13" t="n">
+        <v>925926.0</v>
+      </c>
+      <c r="M18" s="13" t="n">
+        <v>74074.0</v>
+      </c>
       <c r="N18" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O18" s="13" t="n">
-        <v>3598000.0</v>
+        <v>1000000.0</v>
       </c>
       <c r="P18" s="6" t="inlineStr">
         <is>
@@ -1141,56 +1189,56 @@
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>C25MYY</t>
+          <t>C25MVN</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>376</t>
+          <t>6120</t>
         </is>
       </c>
       <c r="E19" s="7" t="inlineStr">
         <is>
-          <t>30/10/2025</t>
+          <t>18/10/2025</t>
         </is>
       </c>
       <c r="F19" s="7" t="inlineStr">
         <is>
-          <t>3500513118</t>
+          <t>3702936116</t>
         </is>
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>DOANH NGHIỆP TƯ NHÂN NHÀ MÁY NƯỚC ĐÁ YẾN LINH</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ ẨM THỰC YUM YUM VIỆT NAM</t>
         </is>
       </c>
       <c r="H19" s="6" t="inlineStr">
         <is>
-          <t>60/14  Phạm Hồng Thái, Phường Tam Thắng, Thành phố Hồ Chí Minh, Việt Nam.</t>
+          <t>Số 104 đường Ngô Gia Tự, Phường Thủ Dầu Một , Thành phố Hồ Chí Minh, Việt Nam.</t>
         </is>
       </c>
       <c r="I19" s="7" t="inlineStr">
         <is>
-          <t>3502469834</t>
+          <t>3501844024</t>
         </is>
       </c>
       <c r="J19" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN ĐÔNG DƯƠNG VŨNG TÀU</t>
         </is>
       </c>
       <c r="K19" s="6"/>
       <c r="L19" s="13" t="n">
-        <v>3707407.0</v>
+        <v>2146000.0</v>
       </c>
       <c r="M19" s="13" t="n">
-        <v>296593.0</v>
+        <v>181680.0</v>
       </c>
       <c r="N19" s="13" t="n">
-        <v>0.0</v>
+        <v>110000.0</v>
       </c>
       <c r="O19" s="13" t="n">
-        <v>4004000.0</v>
+        <v>2327680.0</v>
       </c>
       <c r="P19" s="6" t="inlineStr">
         <is>

--- a/Hoadon/HDVao/10/HDDienTuMayTinhTien.xlsx
+++ b/Hoadon/HDVao/10/HDDienTuMayTinhTien.xlsx
@@ -313,12 +313,12 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>C25MDX</t>
+          <t>C25MCH</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>11391</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
@@ -328,41 +328,41 @@
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>0316603413</t>
+          <t>0313005616</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH GIẢI PHÁP XÂY DỰNG 247</t>
+          <t>CÔNG TY CỔ PHẦN SWAT CLEAN HOME</t>
         </is>
       </c>
       <c r="H7" s="6" t="inlineStr">
         <is>
-          <t>702/5 Lê Văn Khương, Phường Thới An, Thành Phố Hồ Chí Minh, Việt Nam</t>
+          <t>Lầu 6, Số 16 Đường Đào Duy Anh, Phường Đức Nhuận, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I7" s="7" t="inlineStr">
         <is>
-          <t>3501844024</t>
+          <t>3502550210</t>
         </is>
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN ĐÔNG DƯƠNG VŨNG TÀU</t>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
         </is>
       </c>
       <c r="K7" s="6"/>
       <c r="L7" s="13" t="n">
-        <v>7.3379628E7</v>
+        <v>4822167.0</v>
       </c>
       <c r="M7" s="13" t="n">
-        <v>5870370.0</v>
+        <v>385773.0</v>
       </c>
       <c r="N7" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O7" s="13" t="n">
-        <v>7.9249998E7</v>
+        <v>5207940.0</v>
       </c>
       <c r="P7" s="6" t="inlineStr">
         <is>
@@ -386,56 +386,56 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>C25MPA</t>
+          <t>C25MCH</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>224</t>
+          <t>12053</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>11/10/2025</t>
+          <t>20/10/2025</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>3501547085</t>
+          <t>0313005616</t>
         </is>
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH ĐẦU TƯ THƯƠNG MẠI XÂY DỰNG PHƯỚC AN</t>
+          <t>CÔNG TY CỔ PHẦN SWAT CLEAN HOME</t>
         </is>
       </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
-          <t>Số 774 đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam.</t>
+          <t>Lầu 6, Số 16 Đường Đào Duy Anh, Phường Đức Nhuận, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I8" s="7" t="inlineStr">
         <is>
-          <t>3501844024</t>
+          <t>3502550210</t>
         </is>
       </c>
       <c r="J8" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN ĐÔNG DƯƠNG VŨNG TÀU</t>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
         </is>
       </c>
       <c r="K8" s="6"/>
       <c r="L8" s="13" t="n">
-        <v>9619444.0</v>
+        <v>4176389.0</v>
       </c>
       <c r="M8" s="13" t="n">
-        <v>769556.0</v>
+        <v>334111.0</v>
       </c>
       <c r="N8" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O8" s="13" t="n">
-        <v>1.0389E7</v>
+        <v>4510500.0</v>
       </c>
       <c r="P8" s="6" t="inlineStr">
         <is>
@@ -459,56 +459,56 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>C25MCC</t>
+          <t>C25MTT</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>231799</t>
+          <t>6472</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>03/10/2025</t>
+          <t>09/10/2025</t>
         </is>
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>3502280613</t>
+          <t>3500405761</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN DỊCH VỤ PHÁT TRIỂN GIAO THÔNG VẬN TẢI VŨNG TÀU</t>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN HỒNG THANH</t>
         </is>
       </c>
       <c r="H9" s="6" t="inlineStr">
         <is>
-          <t>LK10, đường Hàng Điều 1, Khu nhà ở Khang Linh, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 98-100-102-104 Lý Tự Trọng, Phường Vũng Tàu, Thành Phố Hồ Chí Minh Việt Nam</t>
         </is>
       </c>
       <c r="I9" s="7" t="inlineStr">
         <is>
-          <t>3501844024</t>
+          <t>3502550210</t>
         </is>
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN ĐÔNG DƯƠNG VŨNG TÀU</t>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
         </is>
       </c>
       <c r="K9" s="6"/>
       <c r="L9" s="13" t="n">
-        <v>462963.0</v>
+        <v>1.2136364E7</v>
       </c>
       <c r="M9" s="13" t="n">
-        <v>37037.0</v>
+        <v>1213636.0</v>
       </c>
       <c r="N9" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O9" s="13" t="n">
-        <v>500000.0</v>
+        <v>1.335E7</v>
       </c>
       <c r="P9" s="6" t="inlineStr">
         <is>
@@ -532,56 +532,56 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>C25MCC</t>
+          <t>C25MRV</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>235045</t>
+          <t>1229</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>07/10/2025</t>
+          <t>01/10/2025</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>3502280613</t>
+          <t>3500704465</t>
         </is>
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN DỊCH VỤ PHÁT TRIỂN GIAO THÔNG VẬN TẢI VŨNG TÀU</t>
+          <t>CÔNG TY TNHH RỒNG VIỆT</t>
         </is>
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>LK10, đường Hàng Điều 1, Khu nhà ở Khang Linh, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I10" s="7" t="inlineStr">
         <is>
-          <t>3501844024</t>
+          <t>3502550210</t>
         </is>
       </c>
       <c r="J10" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN ĐÔNG DƯƠNG VŨNG TÀU</t>
+          <t xml:space="preserve">CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH </t>
         </is>
       </c>
       <c r="K10" s="6"/>
       <c r="L10" s="13" t="n">
-        <v>462963.0</v>
+        <v>991050.0</v>
       </c>
       <c r="M10" s="13" t="n">
-        <v>37037.0</v>
+        <v>79284.0</v>
       </c>
       <c r="N10" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O10" s="13" t="n">
-        <v>500000.0</v>
+        <v>1070334.0</v>
       </c>
       <c r="P10" s="6" t="inlineStr">
         <is>
@@ -605,56 +605,56 @@
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>C25MCC</t>
+          <t>C25MRV</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>239827</t>
+          <t>1454</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t>13/10/2025</t>
+          <t>02/10/2025</t>
         </is>
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>3502280613</t>
+          <t>3500704465</t>
         </is>
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN DỊCH VỤ PHÁT TRIỂN GIAO THÔNG VẬN TẢI VŨNG TÀU</t>
+          <t>CÔNG TY TNHH RỒNG VIỆT</t>
         </is>
       </c>
       <c r="H11" s="6" t="inlineStr">
         <is>
-          <t>LK10, đường Hàng Điều 1, Khu nhà ở Khang Linh, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I11" s="7" t="inlineStr">
         <is>
-          <t>3501844024</t>
+          <t>3502550210</t>
         </is>
       </c>
       <c r="J11" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN ĐÔNG DƯƠNG VŨNG TÀU</t>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
         </is>
       </c>
       <c r="K11" s="6"/>
       <c r="L11" s="13" t="n">
-        <v>462963.0</v>
+        <v>3694800.0</v>
       </c>
       <c r="M11" s="13" t="n">
-        <v>37037.0</v>
+        <v>295584.0</v>
       </c>
       <c r="N11" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O11" s="13" t="n">
-        <v>500000.0</v>
+        <v>3990384.0</v>
       </c>
       <c r="P11" s="6" t="inlineStr">
         <is>
@@ -678,56 +678,56 @@
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>C25MCC</t>
+          <t>C25MRV</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>242539</t>
+          <t>1455</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>16/10/2025</t>
+          <t>02/10/2025</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>3502280613</t>
+          <t>3500704465</t>
         </is>
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN DỊCH VỤ PHÁT TRIỂN GIAO THÔNG VẬN TẢI VŨNG TÀU</t>
+          <t>CÔNG TY TNHH RỒNG VIỆT</t>
         </is>
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>LK10, đường Hàng Điều 1, Khu nhà ở Khang Linh, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I12" s="7" t="inlineStr">
         <is>
-          <t>3501844024</t>
+          <t>3502550210</t>
         </is>
       </c>
       <c r="J12" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN ĐÔNG DƯƠNG VŨNG TÀU</t>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
         </is>
       </c>
       <c r="K12" s="6"/>
       <c r="L12" s="13" t="n">
-        <v>462963.0</v>
+        <v>1.3032E7</v>
       </c>
       <c r="M12" s="13" t="n">
-        <v>37037.0</v>
+        <v>1042560.0</v>
       </c>
       <c r="N12" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O12" s="13" t="n">
-        <v>500000.0</v>
+        <v>1.407456E7</v>
       </c>
       <c r="P12" s="6" t="inlineStr">
         <is>
@@ -751,56 +751,56 @@
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>C25MCC</t>
+          <t>C25MRV</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>242951</t>
+          <t>1475</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>17/10/2025</t>
+          <t>03/10/2025</t>
         </is>
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
-          <t>3502280613</t>
+          <t>3500704465</t>
         </is>
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN DỊCH VỤ PHÁT TRIỂN GIAO THÔNG VẬN TẢI VŨNG TÀU</t>
+          <t>CÔNG TY TNHH RỒNG VIỆT</t>
         </is>
       </c>
       <c r="H13" s="6" t="inlineStr">
         <is>
-          <t>LK10, đường Hàng Điều 1, Khu nhà ở Khang Linh, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I13" s="7" t="inlineStr">
         <is>
-          <t>3501844024</t>
+          <t>3502550210</t>
         </is>
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN ĐÔNG DƯƠNG VŨNG TÀU</t>
+          <t xml:space="preserve">CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH </t>
         </is>
       </c>
       <c r="K13" s="6"/>
       <c r="L13" s="13" t="n">
-        <v>925926.0</v>
+        <v>2.0277778E7</v>
       </c>
       <c r="M13" s="13" t="n">
-        <v>74074.0</v>
+        <v>1622222.0</v>
       </c>
       <c r="N13" s="13" t="n">
-        <v>0.0</v>
+        <v>1358222.0</v>
       </c>
       <c r="O13" s="13" t="n">
-        <v>1000000.0</v>
+        <v>2.19E7</v>
       </c>
       <c r="P13" s="6" t="inlineStr">
         <is>
@@ -824,56 +824,56 @@
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>C25MCC</t>
+          <t>C25MRV</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>245911</t>
+          <t>1891</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>20/10/2025</t>
+          <t>04/10/2025</t>
         </is>
       </c>
       <c r="F14" s="7" t="inlineStr">
         <is>
-          <t>3502280613</t>
+          <t>3500704465</t>
         </is>
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN DỊCH VỤ PHÁT TRIỂN GIAO THÔNG VẬN TẢI VŨNG TÀU</t>
+          <t>CÔNG TY TNHH RỒNG VIỆT</t>
         </is>
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
-          <t>Số 15 đường Sông Hương, Khu nhà ở Khang Linh, Phường Rạch Dừa, Thành Phố Hồ Chí Minh</t>
+          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I14" s="7" t="inlineStr">
         <is>
-          <t>3501844024</t>
+          <t>3502550210</t>
         </is>
       </c>
       <c r="J14" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN ĐÔNG DƯƠNG VŨNG TÀU</t>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
         </is>
       </c>
       <c r="K14" s="6"/>
       <c r="L14" s="13" t="n">
-        <v>462963.0</v>
+        <v>1151136.0</v>
       </c>
       <c r="M14" s="13" t="n">
-        <v>37037.0</v>
+        <v>92091.0</v>
       </c>
       <c r="N14" s="13" t="n">
-        <v>0.0</v>
+        <v>144864.0</v>
       </c>
       <c r="O14" s="13" t="n">
-        <v>500000.0</v>
+        <v>1243227.0</v>
       </c>
       <c r="P14" s="6" t="inlineStr">
         <is>
@@ -897,60 +897,60 @@
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>C25MCC</t>
+          <t>C25MRV</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>247961</t>
+          <t>2147</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
-          <t>23/10/2025</t>
+          <t>07/10/2025</t>
         </is>
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
-          <t>3502280613</t>
+          <t>3500704465</t>
         </is>
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN DỊCH VỤ PHÁT TRIỂN GIAO THÔNG VẬN TẢI VŨNG TÀU</t>
+          <t>CÔNG TY TNHH RỒNG VIỆT</t>
         </is>
       </c>
       <c r="H15" s="6" t="inlineStr">
         <is>
-          <t>Số 15 đường Sông Hương, Khu nhà ở Khang Linh, Phường Rạch Dừa, Thành Phố Hồ Chí Minh</t>
+          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I15" s="7" t="inlineStr">
         <is>
-          <t>3501844024</t>
+          <t>3502550210</t>
         </is>
       </c>
       <c r="J15" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN ĐÔNG DƯƠNG VŨNG TÀU</t>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
         </is>
       </c>
       <c r="K15" s="6"/>
       <c r="L15" s="13" t="n">
-        <v>925926.0</v>
+        <v>0.0</v>
       </c>
       <c r="M15" s="13" t="n">
-        <v>74074.0</v>
+        <v>0.0</v>
       </c>
       <c r="N15" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O15" s="13" t="n">
-        <v>1000000.0</v>
+        <v>0.0</v>
       </c>
       <c r="P15" s="6" t="inlineStr">
         <is>
-          <t>Hóa đơn mới</t>
+          <t>Hóa đơn điều chỉnh</t>
         </is>
       </c>
       <c r="Q15" s="6" t="inlineStr">
@@ -970,56 +970,56 @@
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>C25MCC</t>
+          <t>C25MRV</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>248595</t>
+          <t>2150</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>24/10/2025</t>
+          <t>07/10/2025</t>
         </is>
       </c>
       <c r="F16" s="7" t="inlineStr">
         <is>
-          <t>3502280613</t>
+          <t>3500704465</t>
         </is>
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN DỊCH VỤ PHÁT TRIỂN GIAO THÔNG VẬN TẢI VŨNG TÀU</t>
+          <t>CÔNG TY TNHH RỒNG VIỆT</t>
         </is>
       </c>
       <c r="H16" s="6" t="inlineStr">
         <is>
-          <t>Số 15 đường Sông Hương, Khu nhà ở Khang Linh, Phường Rạch Dừa, Thành Phố Hồ Chí Minh</t>
+          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I16" s="7" t="inlineStr">
         <is>
-          <t>3501844024</t>
+          <t>3502550210</t>
         </is>
       </c>
       <c r="J16" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN ĐÔNG DƯƠNG VŨNG TÀU</t>
+          <t xml:space="preserve">CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH </t>
         </is>
       </c>
       <c r="K16" s="6"/>
       <c r="L16" s="13" t="n">
-        <v>462963.0</v>
+        <v>2462963.0</v>
       </c>
       <c r="M16" s="13" t="n">
-        <v>37037.0</v>
+        <v>197037.0</v>
       </c>
       <c r="N16" s="13" t="n">
-        <v>0.0</v>
+        <v>363637.0</v>
       </c>
       <c r="O16" s="13" t="n">
-        <v>500000.0</v>
+        <v>2660000.0</v>
       </c>
       <c r="P16" s="6" t="inlineStr">
         <is>
@@ -1043,56 +1043,56 @@
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>C25MCC</t>
+          <t>C25MRV</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>251494</t>
+          <t>2359</t>
         </is>
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
-          <t>28/10/2025</t>
+          <t>07/10/2025</t>
         </is>
       </c>
       <c r="F17" s="7" t="inlineStr">
         <is>
-          <t>3502280613</t>
+          <t>3500704465</t>
         </is>
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN DỊCH VỤ PHÁT TRIỂN GIAO THÔNG VẬN TẢI VŨNG TÀU</t>
+          <t>CÔNG TY TNHH RỒNG VIỆT</t>
         </is>
       </c>
       <c r="H17" s="6" t="inlineStr">
         <is>
-          <t>Số 15 đường Sông Hương, Khu nhà ở Khang Linh, Phường Rạch Dừa, Thành Phố Hồ Chí Minh</t>
+          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I17" s="7" t="inlineStr">
         <is>
-          <t>3501844024</t>
+          <t>3502550210</t>
         </is>
       </c>
       <c r="J17" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN ĐÔNG DƯƠNG VŨNG TÀU</t>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
         </is>
       </c>
       <c r="K17" s="6"/>
       <c r="L17" s="13" t="n">
-        <v>462963.0</v>
+        <v>3048160.0</v>
       </c>
       <c r="M17" s="13" t="n">
-        <v>37037.0</v>
+        <v>243853.0</v>
       </c>
       <c r="N17" s="13" t="n">
-        <v>0.0</v>
+        <v>35040.0</v>
       </c>
       <c r="O17" s="13" t="n">
-        <v>500000.0</v>
+        <v>3292013.0</v>
       </c>
       <c r="P17" s="6" t="inlineStr">
         <is>
@@ -1116,56 +1116,56 @@
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>C25MCC</t>
+          <t>C25MRV</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>252995</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>30/10/2025</t>
+          <t>07/10/2025</t>
         </is>
       </c>
       <c r="F18" s="7" t="inlineStr">
         <is>
-          <t>3502280613</t>
+          <t>3500704465</t>
         </is>
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN DỊCH VỤ PHÁT TRIỂN GIAO THÔNG VẬN TẢI VŨNG TÀU</t>
+          <t>CÔNG TY TNHH RỒNG VIỆT</t>
         </is>
       </c>
       <c r="H18" s="6" t="inlineStr">
         <is>
-          <t>Số 15 đường Sông Hương, Khu nhà ở Khang Linh, Phường Rạch Dừa, Thành Phố Hồ Chí Minh</t>
+          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I18" s="7" t="inlineStr">
         <is>
-          <t>3501844024</t>
+          <t>3502550210</t>
         </is>
       </c>
       <c r="J18" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN ĐÔNG DƯƠNG VŨNG TÀU</t>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
         </is>
       </c>
       <c r="K18" s="6"/>
       <c r="L18" s="13" t="n">
-        <v>925926.0</v>
+        <v>4396560.0</v>
       </c>
       <c r="M18" s="13" t="n">
-        <v>74074.0</v>
+        <v>351725.0</v>
       </c>
       <c r="N18" s="13" t="n">
-        <v>0.0</v>
+        <v>171840.0</v>
       </c>
       <c r="O18" s="13" t="n">
-        <v>1000000.0</v>
+        <v>4748285.0</v>
       </c>
       <c r="P18" s="6" t="inlineStr">
         <is>
@@ -1189,56 +1189,56 @@
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>C25MVN</t>
+          <t>C25MRV</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>6120</t>
+          <t>2810</t>
         </is>
       </c>
       <c r="E19" s="7" t="inlineStr">
         <is>
-          <t>18/10/2025</t>
+          <t>09/10/2025</t>
         </is>
       </c>
       <c r="F19" s="7" t="inlineStr">
         <is>
-          <t>3702936116</t>
+          <t>3500704465</t>
         </is>
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ ẨM THỰC YUM YUM VIỆT NAM</t>
+          <t>CÔNG TY TNHH RỒNG VIỆT</t>
         </is>
       </c>
       <c r="H19" s="6" t="inlineStr">
         <is>
-          <t>Số 104 đường Ngô Gia Tự, Phường Thủ Dầu Một , Thành phố Hồ Chí Minh, Việt Nam.</t>
+          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I19" s="7" t="inlineStr">
         <is>
-          <t>3501844024</t>
+          <t>3502550210</t>
         </is>
       </c>
       <c r="J19" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN ĐÔNG DƯƠNG VŨNG TÀU</t>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
         </is>
       </c>
       <c r="K19" s="6"/>
       <c r="L19" s="13" t="n">
-        <v>2146000.0</v>
+        <v>2226548.0</v>
       </c>
       <c r="M19" s="13" t="n">
-        <v>181680.0</v>
+        <v>178124.0</v>
       </c>
       <c r="N19" s="13" t="n">
-        <v>110000.0</v>
+        <v>194652.0</v>
       </c>
       <c r="O19" s="13" t="n">
-        <v>2327680.0</v>
+        <v>2404672.0</v>
       </c>
       <c r="P19" s="6" t="inlineStr">
         <is>
@@ -1246,6 +1246,3433 @@
         </is>
       </c>
       <c r="Q19" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="n">
+        <v>14.0</v>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>C25MRV</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>3076</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>10/10/2025</t>
+        </is>
+      </c>
+      <c r="F20" s="7" t="inlineStr">
+        <is>
+          <t>3500704465</t>
+        </is>
+      </c>
+      <c r="G20" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH RỒNG VIỆT</t>
+        </is>
+      </c>
+      <c r="H20" s="6" t="inlineStr">
+        <is>
+          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I20" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J20" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K20" s="6"/>
+      <c r="L20" s="13" t="n">
+        <v>3072504.0</v>
+      </c>
+      <c r="M20" s="13" t="n">
+        <v>245800.0</v>
+      </c>
+      <c r="N20" s="13" t="n">
+        <v>54816.0</v>
+      </c>
+      <c r="O20" s="13" t="n">
+        <v>3318304.0</v>
+      </c>
+      <c r="P20" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q20" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="n">
+        <v>15.0</v>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>C25MRV</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>3309</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>11/10/2025</t>
+        </is>
+      </c>
+      <c r="F21" s="7" t="inlineStr">
+        <is>
+          <t>3500704465</t>
+        </is>
+      </c>
+      <c r="G21" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH RỒNG VIỆT</t>
+        </is>
+      </c>
+      <c r="H21" s="6" t="inlineStr">
+        <is>
+          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I21" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J21" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K21" s="6"/>
+      <c r="L21" s="13" t="n">
+        <v>2166260.0</v>
+      </c>
+      <c r="M21" s="13" t="n">
+        <v>173301.0</v>
+      </c>
+      <c r="N21" s="13" t="n">
+        <v>71490.0</v>
+      </c>
+      <c r="O21" s="13" t="n">
+        <v>2339561.0</v>
+      </c>
+      <c r="P21" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q21" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="n">
+        <v>16.0</v>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>C25MRV</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>3743</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>14/10/2025</t>
+        </is>
+      </c>
+      <c r="F22" s="7" t="inlineStr">
+        <is>
+          <t>3500704465</t>
+        </is>
+      </c>
+      <c r="G22" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH RỒNG VIỆT</t>
+        </is>
+      </c>
+      <c r="H22" s="6" t="inlineStr">
+        <is>
+          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I22" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J22" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K22" s="6"/>
+      <c r="L22" s="13" t="n">
+        <v>3215624.0</v>
+      </c>
+      <c r="M22" s="13" t="n">
+        <v>257250.0</v>
+      </c>
+      <c r="N22" s="13" t="n">
+        <v>22176.0</v>
+      </c>
+      <c r="O22" s="13" t="n">
+        <v>3472874.0</v>
+      </c>
+      <c r="P22" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q22" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="n">
+        <v>17.0</v>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>C25MRV</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>3744</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>14/10/2025</t>
+        </is>
+      </c>
+      <c r="F23" s="7" t="inlineStr">
+        <is>
+          <t>3500704465</t>
+        </is>
+      </c>
+      <c r="G23" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH RỒNG VIỆT</t>
+        </is>
+      </c>
+      <c r="H23" s="6" t="inlineStr">
+        <is>
+          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I23" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J23" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K23" s="6"/>
+      <c r="L23" s="13" t="n">
+        <v>928800.0</v>
+      </c>
+      <c r="M23" s="13" t="n">
+        <v>74304.0</v>
+      </c>
+      <c r="N23" s="13" t="n">
+        <v>103200.0</v>
+      </c>
+      <c r="O23" s="13" t="n">
+        <v>1003104.0</v>
+      </c>
+      <c r="P23" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q23" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="n">
+        <v>18.0</v>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>C25MRV</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>3791</t>
+        </is>
+      </c>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t>15/10/2025</t>
+        </is>
+      </c>
+      <c r="F24" s="7" t="inlineStr">
+        <is>
+          <t>3500704465</t>
+        </is>
+      </c>
+      <c r="G24" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH RỒNG VIỆT</t>
+        </is>
+      </c>
+      <c r="H24" s="6" t="inlineStr">
+        <is>
+          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I24" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J24" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH </t>
+        </is>
+      </c>
+      <c r="K24" s="6"/>
+      <c r="L24" s="13" t="n">
+        <v>2.2777778E7</v>
+      </c>
+      <c r="M24" s="13" t="n">
+        <v>1822222.0</v>
+      </c>
+      <c r="N24" s="13" t="n">
+        <v>1846222.0</v>
+      </c>
+      <c r="O24" s="13" t="n">
+        <v>2.46E7</v>
+      </c>
+      <c r="P24" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q24" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="n">
+        <v>19.0</v>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>C25MRV</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>4222</t>
+        </is>
+      </c>
+      <c r="E25" s="7" t="inlineStr">
+        <is>
+          <t>16/10/2025</t>
+        </is>
+      </c>
+      <c r="F25" s="7" t="inlineStr">
+        <is>
+          <t>3500704465</t>
+        </is>
+      </c>
+      <c r="G25" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH RỒNG VIỆT</t>
+        </is>
+      </c>
+      <c r="H25" s="6" t="inlineStr">
+        <is>
+          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I25" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J25" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K25" s="6"/>
+      <c r="L25" s="13" t="n">
+        <v>5595124.0</v>
+      </c>
+      <c r="M25" s="13" t="n">
+        <v>447610.0</v>
+      </c>
+      <c r="N25" s="13" t="n">
+        <v>162876.0</v>
+      </c>
+      <c r="O25" s="13" t="n">
+        <v>6042734.0</v>
+      </c>
+      <c r="P25" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q25" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="n">
+        <v>20.0</v>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>C25MRV</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>4231</t>
+        </is>
+      </c>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t>16/10/2025</t>
+        </is>
+      </c>
+      <c r="F26" s="7" t="inlineStr">
+        <is>
+          <t>3500704465</t>
+        </is>
+      </c>
+      <c r="G26" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH RỒNG VIỆT</t>
+        </is>
+      </c>
+      <c r="H26" s="6" t="inlineStr">
+        <is>
+          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I26" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J26" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K26" s="6"/>
+      <c r="L26" s="13" t="n">
+        <v>2462963.0</v>
+      </c>
+      <c r="M26" s="13" t="n">
+        <v>197037.0</v>
+      </c>
+      <c r="N26" s="13" t="n">
+        <v>363637.0</v>
+      </c>
+      <c r="O26" s="13" t="n">
+        <v>2660000.0</v>
+      </c>
+      <c r="P26" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q26" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="n">
+        <v>21.0</v>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>C25MRV</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>4440</t>
+        </is>
+      </c>
+      <c r="E27" s="7" t="inlineStr">
+        <is>
+          <t>17/10/2025</t>
+        </is>
+      </c>
+      <c r="F27" s="7" t="inlineStr">
+        <is>
+          <t>3500704465</t>
+        </is>
+      </c>
+      <c r="G27" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH RỒNG VIỆT</t>
+        </is>
+      </c>
+      <c r="H27" s="6" t="inlineStr">
+        <is>
+          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I27" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J27" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K27" s="6"/>
+      <c r="L27" s="13" t="n">
+        <v>1617696.0</v>
+      </c>
+      <c r="M27" s="13" t="n">
+        <v>129416.0</v>
+      </c>
+      <c r="N27" s="13" t="n">
+        <v>26304.0</v>
+      </c>
+      <c r="O27" s="13" t="n">
+        <v>1747112.0</v>
+      </c>
+      <c r="P27" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q27" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="n">
+        <v>22.0</v>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>C25MRV</t>
+        </is>
+      </c>
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t>4441</t>
+        </is>
+      </c>
+      <c r="E28" s="7" t="inlineStr">
+        <is>
+          <t>17/10/2025</t>
+        </is>
+      </c>
+      <c r="F28" s="7" t="inlineStr">
+        <is>
+          <t>3500704465</t>
+        </is>
+      </c>
+      <c r="G28" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH RỒNG VIỆT</t>
+        </is>
+      </c>
+      <c r="H28" s="6" t="inlineStr">
+        <is>
+          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I28" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J28" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K28" s="6"/>
+      <c r="L28" s="13" t="n">
+        <v>2518456.0</v>
+      </c>
+      <c r="M28" s="13" t="n">
+        <v>201476.0</v>
+      </c>
+      <c r="N28" s="13" t="n">
+        <v>54984.0</v>
+      </c>
+      <c r="O28" s="13" t="n">
+        <v>2719932.0</v>
+      </c>
+      <c r="P28" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q28" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="n">
+        <v>23.0</v>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>C25MRV</t>
+        </is>
+      </c>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>4691</t>
+        </is>
+      </c>
+      <c r="E29" s="7" t="inlineStr">
+        <is>
+          <t>18/10/2025</t>
+        </is>
+      </c>
+      <c r="F29" s="7" t="inlineStr">
+        <is>
+          <t>3500704465</t>
+        </is>
+      </c>
+      <c r="G29" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH RỒNG VIỆT</t>
+        </is>
+      </c>
+      <c r="H29" s="6" t="inlineStr">
+        <is>
+          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I29" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J29" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K29" s="6"/>
+      <c r="L29" s="13" t="n">
+        <v>1094400.0</v>
+      </c>
+      <c r="M29" s="13" t="n">
+        <v>87552.0</v>
+      </c>
+      <c r="N29" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O29" s="13" t="n">
+        <v>1181952.0</v>
+      </c>
+      <c r="P29" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q29" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="n">
+        <v>24.0</v>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>C25MRV</t>
+        </is>
+      </c>
+      <c r="D30" s="7" t="inlineStr">
+        <is>
+          <t>4692</t>
+        </is>
+      </c>
+      <c r="E30" s="7" t="inlineStr">
+        <is>
+          <t>18/10/2025</t>
+        </is>
+      </c>
+      <c r="F30" s="7" t="inlineStr">
+        <is>
+          <t>3500704465</t>
+        </is>
+      </c>
+      <c r="G30" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH RỒNG VIỆT</t>
+        </is>
+      </c>
+      <c r="H30" s="6" t="inlineStr">
+        <is>
+          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I30" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J30" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K30" s="6"/>
+      <c r="L30" s="13" t="n">
+        <v>2183862.0</v>
+      </c>
+      <c r="M30" s="13" t="n">
+        <v>174709.0</v>
+      </c>
+      <c r="N30" s="13" t="n">
+        <v>11538.0</v>
+      </c>
+      <c r="O30" s="13" t="n">
+        <v>2358571.0</v>
+      </c>
+      <c r="P30" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q30" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="n">
+        <v>25.0</v>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>C25MRV</t>
+        </is>
+      </c>
+      <c r="D31" s="7" t="inlineStr">
+        <is>
+          <t>5180</t>
+        </is>
+      </c>
+      <c r="E31" s="7" t="inlineStr">
+        <is>
+          <t>21/10/2025</t>
+        </is>
+      </c>
+      <c r="F31" s="7" t="inlineStr">
+        <is>
+          <t>3500704465</t>
+        </is>
+      </c>
+      <c r="G31" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH RỒNG VIỆT</t>
+        </is>
+      </c>
+      <c r="H31" s="6" t="inlineStr">
+        <is>
+          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I31" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J31" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K31" s="6"/>
+      <c r="L31" s="13" t="n">
+        <v>4556000.0</v>
+      </c>
+      <c r="M31" s="13" t="n">
+        <v>364480.0</v>
+      </c>
+      <c r="N31" s="13" t="n">
+        <v>42000.0</v>
+      </c>
+      <c r="O31" s="13" t="n">
+        <v>4920480.0</v>
+      </c>
+      <c r="P31" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q31" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="n">
+        <v>26.0</v>
+      </c>
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="inlineStr">
+        <is>
+          <t>C25MRV</t>
+        </is>
+      </c>
+      <c r="D32" s="7" t="inlineStr">
+        <is>
+          <t>5181</t>
+        </is>
+      </c>
+      <c r="E32" s="7" t="inlineStr">
+        <is>
+          <t>21/10/2025</t>
+        </is>
+      </c>
+      <c r="F32" s="7" t="inlineStr">
+        <is>
+          <t>3500704465</t>
+        </is>
+      </c>
+      <c r="G32" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH RỒNG VIỆT</t>
+        </is>
+      </c>
+      <c r="H32" s="6" t="inlineStr">
+        <is>
+          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I32" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J32" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K32" s="6"/>
+      <c r="L32" s="13" t="n">
+        <v>2107752.0</v>
+      </c>
+      <c r="M32" s="13" t="n">
+        <v>168620.0</v>
+      </c>
+      <c r="N32" s="13" t="n">
+        <v>98648.0</v>
+      </c>
+      <c r="O32" s="13" t="n">
+        <v>2276372.0</v>
+      </c>
+      <c r="P32" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q32" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="n">
+        <v>27.0</v>
+      </c>
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>C25MRV</t>
+        </is>
+      </c>
+      <c r="D33" s="7" t="inlineStr">
+        <is>
+          <t>5198</t>
+        </is>
+      </c>
+      <c r="E33" s="7" t="inlineStr">
+        <is>
+          <t>21/10/2025</t>
+        </is>
+      </c>
+      <c r="F33" s="7" t="inlineStr">
+        <is>
+          <t>3500704465</t>
+        </is>
+      </c>
+      <c r="G33" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH RỒNG VIỆT</t>
+        </is>
+      </c>
+      <c r="H33" s="6" t="inlineStr">
+        <is>
+          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I33" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J33" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH </t>
+        </is>
+      </c>
+      <c r="K33" s="6"/>
+      <c r="L33" s="13" t="n">
+        <v>3.4027778E7</v>
+      </c>
+      <c r="M33" s="13" t="n">
+        <v>2722222.0</v>
+      </c>
+      <c r="N33" s="13" t="n">
+        <v>2032222.0</v>
+      </c>
+      <c r="O33" s="13" t="n">
+        <v>3.675E7</v>
+      </c>
+      <c r="P33" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q33" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="n">
+        <v>28.0</v>
+      </c>
+      <c r="B34" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="inlineStr">
+        <is>
+          <t>C25MRV</t>
+        </is>
+      </c>
+      <c r="D34" s="7" t="inlineStr">
+        <is>
+          <t>5257</t>
+        </is>
+      </c>
+      <c r="E34" s="7" t="inlineStr">
+        <is>
+          <t>22/10/2025</t>
+        </is>
+      </c>
+      <c r="F34" s="7" t="inlineStr">
+        <is>
+          <t>3500704465</t>
+        </is>
+      </c>
+      <c r="G34" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH RỒNG VIỆT</t>
+        </is>
+      </c>
+      <c r="H34" s="6" t="inlineStr">
+        <is>
+          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I34" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J34" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K34" s="6"/>
+      <c r="L34" s="13" t="n">
+        <v>2.172E7</v>
+      </c>
+      <c r="M34" s="13" t="n">
+        <v>1737600.0</v>
+      </c>
+      <c r="N34" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O34" s="13" t="n">
+        <v>2.34576E7</v>
+      </c>
+      <c r="P34" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q34" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="n">
+        <v>29.0</v>
+      </c>
+      <c r="B35" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="inlineStr">
+        <is>
+          <t>C25MRV</t>
+        </is>
+      </c>
+      <c r="D35" s="7" t="inlineStr">
+        <is>
+          <t>5829</t>
+        </is>
+      </c>
+      <c r="E35" s="7" t="inlineStr">
+        <is>
+          <t>24/10/2025</t>
+        </is>
+      </c>
+      <c r="F35" s="7" t="inlineStr">
+        <is>
+          <t>3500704465</t>
+        </is>
+      </c>
+      <c r="G35" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH RỒNG VIỆT</t>
+        </is>
+      </c>
+      <c r="H35" s="6" t="inlineStr">
+        <is>
+          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I35" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J35" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K35" s="6"/>
+      <c r="L35" s="13" t="n">
+        <v>1424352.0</v>
+      </c>
+      <c r="M35" s="13" t="n">
+        <v>113948.0</v>
+      </c>
+      <c r="N35" s="13" t="n">
+        <v>31608.0</v>
+      </c>
+      <c r="O35" s="13" t="n">
+        <v>1538300.0</v>
+      </c>
+      <c r="P35" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q35" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="B36" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="inlineStr">
+        <is>
+          <t>C25MRV</t>
+        </is>
+      </c>
+      <c r="D36" s="7" t="inlineStr">
+        <is>
+          <t>6060</t>
+        </is>
+      </c>
+      <c r="E36" s="7" t="inlineStr">
+        <is>
+          <t>25/10/2025</t>
+        </is>
+      </c>
+      <c r="F36" s="7" t="inlineStr">
+        <is>
+          <t>3500704465</t>
+        </is>
+      </c>
+      <c r="G36" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH RỒNG VIỆT</t>
+        </is>
+      </c>
+      <c r="H36" s="6" t="inlineStr">
+        <is>
+          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I36" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J36" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K36" s="6"/>
+      <c r="L36" s="13" t="n">
+        <v>5015229.0</v>
+      </c>
+      <c r="M36" s="13" t="n">
+        <v>401218.0</v>
+      </c>
+      <c r="N36" s="13" t="n">
+        <v>297471.0</v>
+      </c>
+      <c r="O36" s="13" t="n">
+        <v>5416447.0</v>
+      </c>
+      <c r="P36" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q36" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="n">
+        <v>31.0</v>
+      </c>
+      <c r="B37" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="inlineStr">
+        <is>
+          <t>C25MRV</t>
+        </is>
+      </c>
+      <c r="D37" s="7" t="inlineStr">
+        <is>
+          <t>6275</t>
+        </is>
+      </c>
+      <c r="E37" s="7" t="inlineStr">
+        <is>
+          <t>27/10/2025</t>
+        </is>
+      </c>
+      <c r="F37" s="7" t="inlineStr">
+        <is>
+          <t>3500704465</t>
+        </is>
+      </c>
+      <c r="G37" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH RỒNG VIỆT</t>
+        </is>
+      </c>
+      <c r="H37" s="6" t="inlineStr">
+        <is>
+          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I37" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J37" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH </t>
+        </is>
+      </c>
+      <c r="K37" s="6"/>
+      <c r="L37" s="13" t="n">
+        <v>2462963.0</v>
+      </c>
+      <c r="M37" s="13" t="n">
+        <v>197037.0</v>
+      </c>
+      <c r="N37" s="13" t="n">
+        <v>363637.0</v>
+      </c>
+      <c r="O37" s="13" t="n">
+        <v>2660000.0</v>
+      </c>
+      <c r="P37" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q37" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="n">
+        <v>32.0</v>
+      </c>
+      <c r="B38" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C38" s="6" t="inlineStr">
+        <is>
+          <t>C25MRV</t>
+        </is>
+      </c>
+      <c r="D38" s="7" t="inlineStr">
+        <is>
+          <t>6505</t>
+        </is>
+      </c>
+      <c r="E38" s="7" t="inlineStr">
+        <is>
+          <t>28/10/2025</t>
+        </is>
+      </c>
+      <c r="F38" s="7" t="inlineStr">
+        <is>
+          <t>3500704465</t>
+        </is>
+      </c>
+      <c r="G38" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH RỒNG VIỆT</t>
+        </is>
+      </c>
+      <c r="H38" s="6" t="inlineStr">
+        <is>
+          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I38" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J38" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K38" s="6"/>
+      <c r="L38" s="13" t="n">
+        <v>1128000.0</v>
+      </c>
+      <c r="M38" s="13" t="n">
+        <v>90240.0</v>
+      </c>
+      <c r="N38" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O38" s="13" t="n">
+        <v>1218240.0</v>
+      </c>
+      <c r="P38" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q38" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="n">
+        <v>33.0</v>
+      </c>
+      <c r="B39" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="inlineStr">
+        <is>
+          <t>C25MRV</t>
+        </is>
+      </c>
+      <c r="D39" s="7" t="inlineStr">
+        <is>
+          <t>6506</t>
+        </is>
+      </c>
+      <c r="E39" s="7" t="inlineStr">
+        <is>
+          <t>28/10/2025</t>
+        </is>
+      </c>
+      <c r="F39" s="7" t="inlineStr">
+        <is>
+          <t>3500704465</t>
+        </is>
+      </c>
+      <c r="G39" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH RỒNG VIỆT</t>
+        </is>
+      </c>
+      <c r="H39" s="6" t="inlineStr">
+        <is>
+          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I39" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J39" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K39" s="6"/>
+      <c r="L39" s="13" t="n">
+        <v>3372664.0</v>
+      </c>
+      <c r="M39" s="13" t="n">
+        <v>269813.0</v>
+      </c>
+      <c r="N39" s="13" t="n">
+        <v>47856.0</v>
+      </c>
+      <c r="O39" s="13" t="n">
+        <v>3642477.0</v>
+      </c>
+      <c r="P39" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q39" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="n">
+        <v>34.0</v>
+      </c>
+      <c r="B40" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C40" s="6" t="inlineStr">
+        <is>
+          <t>C25MRV</t>
+        </is>
+      </c>
+      <c r="D40" s="7" t="inlineStr">
+        <is>
+          <t>6507</t>
+        </is>
+      </c>
+      <c r="E40" s="7" t="inlineStr">
+        <is>
+          <t>28/10/2025</t>
+        </is>
+      </c>
+      <c r="F40" s="7" t="inlineStr">
+        <is>
+          <t>3500704465</t>
+        </is>
+      </c>
+      <c r="G40" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH RỒNG VIỆT</t>
+        </is>
+      </c>
+      <c r="H40" s="6" t="inlineStr">
+        <is>
+          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I40" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J40" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K40" s="6"/>
+      <c r="L40" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M40" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N40" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O40" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="P40" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q40" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="n">
+        <v>35.0</v>
+      </c>
+      <c r="B41" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C41" s="6" t="inlineStr">
+        <is>
+          <t>C25MRV</t>
+        </is>
+      </c>
+      <c r="D41" s="7" t="inlineStr">
+        <is>
+          <t>6520</t>
+        </is>
+      </c>
+      <c r="E41" s="7" t="inlineStr">
+        <is>
+          <t>28/10/2025</t>
+        </is>
+      </c>
+      <c r="F41" s="7" t="inlineStr">
+        <is>
+          <t>3500704465</t>
+        </is>
+      </c>
+      <c r="G41" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH RỒNG VIỆT</t>
+        </is>
+      </c>
+      <c r="H41" s="6" t="inlineStr">
+        <is>
+          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I41" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J41" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH </t>
+        </is>
+      </c>
+      <c r="K41" s="6"/>
+      <c r="L41" s="13" t="n">
+        <v>2462963.0</v>
+      </c>
+      <c r="M41" s="13" t="n">
+        <v>197037.0</v>
+      </c>
+      <c r="N41" s="13" t="n">
+        <v>363637.0</v>
+      </c>
+      <c r="O41" s="13" t="n">
+        <v>2660000.0</v>
+      </c>
+      <c r="P41" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q41" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="n">
+        <v>36.0</v>
+      </c>
+      <c r="B42" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C42" s="6" t="inlineStr">
+        <is>
+          <t>C25MRV</t>
+        </is>
+      </c>
+      <c r="D42" s="7" t="inlineStr">
+        <is>
+          <t>6968</t>
+        </is>
+      </c>
+      <c r="E42" s="7" t="inlineStr">
+        <is>
+          <t>30/10/2025</t>
+        </is>
+      </c>
+      <c r="F42" s="7" t="inlineStr">
+        <is>
+          <t>3500704465</t>
+        </is>
+      </c>
+      <c r="G42" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH RỒNG VIỆT</t>
+        </is>
+      </c>
+      <c r="H42" s="6" t="inlineStr">
+        <is>
+          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I42" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J42" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K42" s="6"/>
+      <c r="L42" s="13" t="n">
+        <v>2160232.0</v>
+      </c>
+      <c r="M42" s="13" t="n">
+        <v>172819.0</v>
+      </c>
+      <c r="N42" s="13" t="n">
+        <v>37368.0</v>
+      </c>
+      <c r="O42" s="13" t="n">
+        <v>2333051.0</v>
+      </c>
+      <c r="P42" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q42" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="n">
+        <v>37.0</v>
+      </c>
+      <c r="B43" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C43" s="6" t="inlineStr">
+        <is>
+          <t>C25MRV</t>
+        </is>
+      </c>
+      <c r="D43" s="7" t="inlineStr">
+        <is>
+          <t>6969</t>
+        </is>
+      </c>
+      <c r="E43" s="7" t="inlineStr">
+        <is>
+          <t>30/10/2025</t>
+        </is>
+      </c>
+      <c r="F43" s="7" t="inlineStr">
+        <is>
+          <t>3500704465</t>
+        </is>
+      </c>
+      <c r="G43" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH RỒNG VIỆT</t>
+        </is>
+      </c>
+      <c r="H43" s="6" t="inlineStr">
+        <is>
+          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I43" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J43" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K43" s="6"/>
+      <c r="L43" s="13" t="n">
+        <v>862020.0</v>
+      </c>
+      <c r="M43" s="13" t="n">
+        <v>68962.0</v>
+      </c>
+      <c r="N43" s="13" t="n">
+        <v>95780.0</v>
+      </c>
+      <c r="O43" s="13" t="n">
+        <v>930982.0</v>
+      </c>
+      <c r="P43" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q43" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="n">
+        <v>38.0</v>
+      </c>
+      <c r="B44" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C44" s="6" t="inlineStr">
+        <is>
+          <t>C25MRV</t>
+        </is>
+      </c>
+      <c r="D44" s="7" t="inlineStr">
+        <is>
+          <t>7247</t>
+        </is>
+      </c>
+      <c r="E44" s="7" t="inlineStr">
+        <is>
+          <t>31/10/2025</t>
+        </is>
+      </c>
+      <c r="F44" s="7" t="inlineStr">
+        <is>
+          <t>3500704465</t>
+        </is>
+      </c>
+      <c r="G44" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH RỒNG VIỆT</t>
+        </is>
+      </c>
+      <c r="H44" s="6" t="inlineStr">
+        <is>
+          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I44" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J44" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K44" s="6"/>
+      <c r="L44" s="13" t="n">
+        <v>2249506.0</v>
+      </c>
+      <c r="M44" s="13" t="n">
+        <v>179960.0</v>
+      </c>
+      <c r="N44" s="13" t="n">
+        <v>17094.0</v>
+      </c>
+      <c r="O44" s="13" t="n">
+        <v>2429466.0</v>
+      </c>
+      <c r="P44" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q44" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="n">
+        <v>39.0</v>
+      </c>
+      <c r="B45" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C45" s="6" t="inlineStr">
+        <is>
+          <t>C25MRV</t>
+        </is>
+      </c>
+      <c r="D45" s="7" t="inlineStr">
+        <is>
+          <t>7335</t>
+        </is>
+      </c>
+      <c r="E45" s="7" t="inlineStr">
+        <is>
+          <t>31/10/2025</t>
+        </is>
+      </c>
+      <c r="F45" s="7" t="inlineStr">
+        <is>
+          <t>3500704465</t>
+        </is>
+      </c>
+      <c r="G45" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH RỒNG VIỆT</t>
+        </is>
+      </c>
+      <c r="H45" s="6" t="inlineStr">
+        <is>
+          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I45" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J45" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K45" s="6"/>
+      <c r="L45" s="13" t="n">
+        <v>2901600.0</v>
+      </c>
+      <c r="M45" s="13" t="n">
+        <v>232128.0</v>
+      </c>
+      <c r="N45" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O45" s="13" t="n">
+        <v>3133728.0</v>
+      </c>
+      <c r="P45" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q45" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="n">
+        <v>40.0</v>
+      </c>
+      <c r="B46" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C46" s="6" t="inlineStr">
+        <is>
+          <t>C25MBM</t>
+        </is>
+      </c>
+      <c r="D46" s="7" t="inlineStr">
+        <is>
+          <t>11562</t>
+        </is>
+      </c>
+      <c r="E46" s="7" t="inlineStr">
+        <is>
+          <t>08/10/2025</t>
+        </is>
+      </c>
+      <c r="F46" s="7" t="inlineStr">
+        <is>
+          <t>3501013206</t>
+        </is>
+      </c>
+      <c r="G46" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI BẠCH MAI</t>
+        </is>
+      </c>
+      <c r="H46" s="6" t="inlineStr">
+        <is>
+          <t>Số 01A Tô Nguyệt Đình, Phường Long Hương, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I46" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J46" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K46" s="6"/>
+      <c r="L46" s="13" t="n">
+        <v>2269444.0</v>
+      </c>
+      <c r="M46" s="13" t="n">
+        <v>181556.0</v>
+      </c>
+      <c r="N46" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O46" s="13" t="n">
+        <v>2451000.0</v>
+      </c>
+      <c r="P46" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q46" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="n">
+        <v>41.0</v>
+      </c>
+      <c r="B47" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C47" s="6" t="inlineStr">
+        <is>
+          <t>C25MBM</t>
+        </is>
+      </c>
+      <c r="D47" s="7" t="inlineStr">
+        <is>
+          <t>11563</t>
+        </is>
+      </c>
+      <c r="E47" s="7" t="inlineStr">
+        <is>
+          <t>08/10/2025</t>
+        </is>
+      </c>
+      <c r="F47" s="7" t="inlineStr">
+        <is>
+          <t>3501013206</t>
+        </is>
+      </c>
+      <c r="G47" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI BẠCH MAI</t>
+        </is>
+      </c>
+      <c r="H47" s="6" t="inlineStr">
+        <is>
+          <t>Số 01A Tô Nguyệt Đình, Phường Long Hương, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I47" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J47" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K47" s="6"/>
+      <c r="L47" s="13" t="n">
+        <v>1.1462963E7</v>
+      </c>
+      <c r="M47" s="13" t="n">
+        <v>917037.0</v>
+      </c>
+      <c r="N47" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O47" s="13" t="n">
+        <v>1.238E7</v>
+      </c>
+      <c r="P47" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q47" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="n">
+        <v>42.0</v>
+      </c>
+      <c r="B48" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C48" s="6" t="inlineStr">
+        <is>
+          <t>C25MBM</t>
+        </is>
+      </c>
+      <c r="D48" s="7" t="inlineStr">
+        <is>
+          <t>11564</t>
+        </is>
+      </c>
+      <c r="E48" s="7" t="inlineStr">
+        <is>
+          <t>08/10/2025</t>
+        </is>
+      </c>
+      <c r="F48" s="7" t="inlineStr">
+        <is>
+          <t>3501013206</t>
+        </is>
+      </c>
+      <c r="G48" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI BẠCH MAI</t>
+        </is>
+      </c>
+      <c r="H48" s="6" t="inlineStr">
+        <is>
+          <t>Số 01A Tô Nguyệt Đình, Phường Long Hương, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I48" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J48" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K48" s="6"/>
+      <c r="L48" s="13" t="n">
+        <v>9259259.0</v>
+      </c>
+      <c r="M48" s="13" t="n">
+        <v>740741.0</v>
+      </c>
+      <c r="N48" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O48" s="13" t="n">
+        <v>1.0E7</v>
+      </c>
+      <c r="P48" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q48" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="n">
+        <v>43.0</v>
+      </c>
+      <c r="B49" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C49" s="6" t="inlineStr">
+        <is>
+          <t>C25MBM</t>
+        </is>
+      </c>
+      <c r="D49" s="7" t="inlineStr">
+        <is>
+          <t>11565</t>
+        </is>
+      </c>
+      <c r="E49" s="7" t="inlineStr">
+        <is>
+          <t>08/10/2025</t>
+        </is>
+      </c>
+      <c r="F49" s="7" t="inlineStr">
+        <is>
+          <t>3501013206</t>
+        </is>
+      </c>
+      <c r="G49" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI BẠCH MAI</t>
+        </is>
+      </c>
+      <c r="H49" s="6" t="inlineStr">
+        <is>
+          <t>Số 01A Tô Nguyệt Đình, Phường Long Hương, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I49" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J49" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K49" s="6"/>
+      <c r="L49" s="13" t="n">
+        <v>4652779.0</v>
+      </c>
+      <c r="M49" s="13" t="n">
+        <v>372221.0</v>
+      </c>
+      <c r="N49" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O49" s="13" t="n">
+        <v>5025000.0</v>
+      </c>
+      <c r="P49" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q49" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="n">
+        <v>44.0</v>
+      </c>
+      <c r="B50" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C50" s="6" t="inlineStr">
+        <is>
+          <t>C25MBM</t>
+        </is>
+      </c>
+      <c r="D50" s="7" t="inlineStr">
+        <is>
+          <t>16197</t>
+        </is>
+      </c>
+      <c r="E50" s="7" t="inlineStr">
+        <is>
+          <t>31/10/2025</t>
+        </is>
+      </c>
+      <c r="F50" s="7" t="inlineStr">
+        <is>
+          <t>3501013206</t>
+        </is>
+      </c>
+      <c r="G50" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI BẠCH MAI</t>
+        </is>
+      </c>
+      <c r="H50" s="6" t="inlineStr">
+        <is>
+          <t>Số 01A Tô Nguyệt Đình, Phường Long Hương, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I50" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J50" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K50" s="6"/>
+      <c r="L50" s="13" t="n">
+        <v>6984260.0</v>
+      </c>
+      <c r="M50" s="13" t="n">
+        <v>558740.0</v>
+      </c>
+      <c r="N50" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O50" s="13" t="n">
+        <v>7543000.0</v>
+      </c>
+      <c r="P50" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q50" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="n">
+        <v>45.0</v>
+      </c>
+      <c r="B51" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C51" s="6" t="inlineStr">
+        <is>
+          <t>C25MTK</t>
+        </is>
+      </c>
+      <c r="D51" s="7" t="inlineStr">
+        <is>
+          <t>1949</t>
+        </is>
+      </c>
+      <c r="E51" s="7" t="inlineStr">
+        <is>
+          <t>07/10/2025</t>
+        </is>
+      </c>
+      <c r="F51" s="7" t="inlineStr">
+        <is>
+          <t>3502242819</t>
+        </is>
+      </c>
+      <c r="G51" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THOẠI KHANG</t>
+        </is>
+      </c>
+      <c r="H51" s="6" t="inlineStr">
+        <is>
+          <t>36 Trường Chinh, Khu phố Hải An, Xã Long Hải, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I51" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J51" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K51" s="6"/>
+      <c r="L51" s="13" t="n">
+        <v>9851852.0</v>
+      </c>
+      <c r="M51" s="13" t="n">
+        <v>788148.0</v>
+      </c>
+      <c r="N51" s="13"/>
+      <c r="O51" s="13" t="n">
+        <v>1.064E7</v>
+      </c>
+      <c r="P51" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q51" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="n">
+        <v>46.0</v>
+      </c>
+      <c r="B52" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C52" s="6" t="inlineStr">
+        <is>
+          <t>C25MTK</t>
+        </is>
+      </c>
+      <c r="D52" s="7" t="inlineStr">
+        <is>
+          <t>2036</t>
+        </is>
+      </c>
+      <c r="E52" s="7" t="inlineStr">
+        <is>
+          <t>14/10/2025</t>
+        </is>
+      </c>
+      <c r="F52" s="7" t="inlineStr">
+        <is>
+          <t>3502242819</t>
+        </is>
+      </c>
+      <c r="G52" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THOẠI KHANG</t>
+        </is>
+      </c>
+      <c r="H52" s="6" t="inlineStr">
+        <is>
+          <t>36 Trường Chinh, Khu phố Hải An, Xã Long Hải, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I52" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J52" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K52" s="6"/>
+      <c r="L52" s="13" t="n">
+        <v>1.231482E7</v>
+      </c>
+      <c r="M52" s="13" t="n">
+        <v>985186.0</v>
+      </c>
+      <c r="N52" s="13"/>
+      <c r="O52" s="13" t="n">
+        <v>1.3300006E7</v>
+      </c>
+      <c r="P52" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q52" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="n">
+        <v>47.0</v>
+      </c>
+      <c r="B53" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C53" s="6" t="inlineStr">
+        <is>
+          <t>C25MDH</t>
+        </is>
+      </c>
+      <c r="D53" s="7" t="inlineStr">
+        <is>
+          <t>468</t>
+        </is>
+      </c>
+      <c r="E53" s="7" t="inlineStr">
+        <is>
+          <t>09/10/2025</t>
+        </is>
+      </c>
+      <c r="F53" s="7" t="inlineStr">
+        <is>
+          <t>3502399055</t>
+        </is>
+      </c>
+      <c r="G53" s="6" t="inlineStr">
+        <is>
+          <t>Công Ty Trách Nhiệm Hữu Hạn Thực Phẩm Đức Hải</t>
+        </is>
+      </c>
+      <c r="H53" s="6" t="inlineStr">
+        <is>
+          <t>Số 1 Nguyễn Chánh, Phường Bà Rịa, TP Hồ Chí Minh, Việt Nam.</t>
+        </is>
+      </c>
+      <c r="I53" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J53" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K53" s="6"/>
+      <c r="L53" s="13" t="n">
+        <v>2752314.0</v>
+      </c>
+      <c r="M53" s="13" t="n">
+        <v>220186.0</v>
+      </c>
+      <c r="N53" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O53" s="13" t="n">
+        <v>2972500.0</v>
+      </c>
+      <c r="P53" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q53" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="n">
+        <v>48.0</v>
+      </c>
+      <c r="B54" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C54" s="6" t="inlineStr">
+        <is>
+          <t>C25MDH</t>
+        </is>
+      </c>
+      <c r="D54" s="7" t="inlineStr">
+        <is>
+          <t>515</t>
+        </is>
+      </c>
+      <c r="E54" s="7" t="inlineStr">
+        <is>
+          <t>21/10/2025</t>
+        </is>
+      </c>
+      <c r="F54" s="7" t="inlineStr">
+        <is>
+          <t>3502399055</t>
+        </is>
+      </c>
+      <c r="G54" s="6" t="inlineStr">
+        <is>
+          <t>Công Ty Trách Nhiệm Hữu Hạn Thực Phẩm Đức Hải</t>
+        </is>
+      </c>
+      <c r="H54" s="6" t="inlineStr">
+        <is>
+          <t>Số 1 Nguyễn Chánh, Phường Bà Rịa, TP Hồ Chí Minh, Việt Nam.</t>
+        </is>
+      </c>
+      <c r="I54" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J54" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K54" s="6"/>
+      <c r="L54" s="13" t="n">
+        <v>1514352.0</v>
+      </c>
+      <c r="M54" s="13" t="n">
+        <v>121148.0</v>
+      </c>
+      <c r="N54" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O54" s="13" t="n">
+        <v>1635500.0</v>
+      </c>
+      <c r="P54" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q54" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="n">
+        <v>49.0</v>
+      </c>
+      <c r="B55" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C55" s="6" t="inlineStr">
+        <is>
+          <t>C25MDH</t>
+        </is>
+      </c>
+      <c r="D55" s="7" t="inlineStr">
+        <is>
+          <t>530</t>
+        </is>
+      </c>
+      <c r="E55" s="7" t="inlineStr">
+        <is>
+          <t>28/10/2025</t>
+        </is>
+      </c>
+      <c r="F55" s="7" t="inlineStr">
+        <is>
+          <t>3502399055</t>
+        </is>
+      </c>
+      <c r="G55" s="6" t="inlineStr">
+        <is>
+          <t>Công Ty Trách Nhiệm Hữu Hạn Thực Phẩm Đức Hải</t>
+        </is>
+      </c>
+      <c r="H55" s="6" t="inlineStr">
+        <is>
+          <t>Số 1 Nguyễn Chánh, Phường Bà Rịa, TP Hồ Chí Minh, Việt Nam.</t>
+        </is>
+      </c>
+      <c r="I55" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J55" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K55" s="6"/>
+      <c r="L55" s="13" t="n">
+        <v>1287037.0</v>
+      </c>
+      <c r="M55" s="13" t="n">
+        <v>102963.0</v>
+      </c>
+      <c r="N55" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O55" s="13" t="n">
+        <v>1390000.0</v>
+      </c>
+      <c r="P55" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q55" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="n">
+        <v>50.0</v>
+      </c>
+      <c r="B56" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C56" s="6" t="inlineStr">
+        <is>
+          <t>C25MNB</t>
+        </is>
+      </c>
+      <c r="D56" s="7" t="inlineStr">
+        <is>
+          <t>1778</t>
+        </is>
+      </c>
+      <c r="E56" s="7" t="inlineStr">
+        <is>
+          <t>06/10/2025</t>
+        </is>
+      </c>
+      <c r="F56" s="7" t="inlineStr">
+        <is>
+          <t>3502437617</t>
+        </is>
+      </c>
+      <c r="G56" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH NƯỚC GIẢI KHÁT NHUNG BÌNH</t>
+        </is>
+      </c>
+      <c r="H56" s="6" t="inlineStr">
+        <is>
+          <t>152, tổ 5, Khu Phố 2, Phường Tam Long, Thành phố Hồ Chí Minh, Việt Nam.</t>
+        </is>
+      </c>
+      <c r="I56" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J56" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K56" s="6"/>
+      <c r="L56" s="13" t="n">
+        <v>3.46E7</v>
+      </c>
+      <c r="M56" s="13" t="n">
+        <v>2768000.0</v>
+      </c>
+      <c r="N56" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O56" s="13" t="n">
+        <v>3.7368E7</v>
+      </c>
+      <c r="P56" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q56" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="n">
+        <v>51.0</v>
+      </c>
+      <c r="B57" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C57" s="6" t="inlineStr">
+        <is>
+          <t>C25MNB</t>
+        </is>
+      </c>
+      <c r="D57" s="7" t="inlineStr">
+        <is>
+          <t>2591</t>
+        </is>
+      </c>
+      <c r="E57" s="7" t="inlineStr">
+        <is>
+          <t>30/10/2025</t>
+        </is>
+      </c>
+      <c r="F57" s="7" t="inlineStr">
+        <is>
+          <t>3502437617</t>
+        </is>
+      </c>
+      <c r="G57" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH NƯỚC GIẢI KHÁT NHUNG BÌNH</t>
+        </is>
+      </c>
+      <c r="H57" s="6" t="inlineStr">
+        <is>
+          <t>152, tổ 5, Khu Phố 2, Phường Tam Long, Thành phố Hồ Chí Minh, Việt Nam.</t>
+        </is>
+      </c>
+      <c r="I57" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J57" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K57" s="6"/>
+      <c r="L57" s="13" t="n">
+        <v>7.8051852E7</v>
+      </c>
+      <c r="M57" s="13" t="n">
+        <v>6244148.0</v>
+      </c>
+      <c r="N57" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O57" s="13" t="n">
+        <v>8.4296E7</v>
+      </c>
+      <c r="P57" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q57" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="n">
+        <v>52.0</v>
+      </c>
+      <c r="B58" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C58" s="6" t="inlineStr">
+        <is>
+          <t>C25MYY</t>
+        </is>
+      </c>
+      <c r="D58" s="7" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="E58" s="7" t="inlineStr">
+        <is>
+          <t>10/10/2025</t>
+        </is>
+      </c>
+      <c r="F58" s="7" t="inlineStr">
+        <is>
+          <t>3502483525</t>
+        </is>
+      </c>
+      <c r="G58" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI ĐẠI Ý 79</t>
+        </is>
+      </c>
+      <c r="H58" s="6" t="inlineStr">
+        <is>
+          <t>Số 22/18/29 đường Nam Kỳ Khởi Nghĩa, Phường Vũng Tàu, TP Hồ Chí Minh , Việt Nam</t>
+        </is>
+      </c>
+      <c r="I58" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J58" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH </t>
+        </is>
+      </c>
+      <c r="K58" s="6"/>
+      <c r="L58" s="13" t="n">
+        <v>6.962963E7</v>
+      </c>
+      <c r="M58" s="13" t="n">
+        <v>5570370.0</v>
+      </c>
+      <c r="N58" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O58" s="13" t="n">
+        <v>7.52E7</v>
+      </c>
+      <c r="P58" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q58" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="4" t="n">
+        <v>53.0</v>
+      </c>
+      <c r="B59" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C59" s="6" t="inlineStr">
+        <is>
+          <t>C25MNL</t>
+        </is>
+      </c>
+      <c r="D59" s="7" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="E59" s="7" t="inlineStr">
+        <is>
+          <t>10/10/2025</t>
+        </is>
+      </c>
+      <c r="F59" s="7" t="inlineStr">
+        <is>
+          <t>3502547930</t>
+        </is>
+      </c>
+      <c r="G59" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH  PHÁT TRIỂN THƯƠNG MẠI TÂM NGUYÊN LONG</t>
+        </is>
+      </c>
+      <c r="H59" s="6" t="inlineStr">
+        <is>
+          <t>199 Đường 2/9, Phường Tam Thắng, TP Hồ Chí Minh, Việt Nam.</t>
+        </is>
+      </c>
+      <c r="I59" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J59" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K59" s="6"/>
+      <c r="L59" s="13" t="n">
+        <v>8945180.0</v>
+      </c>
+      <c r="M59" s="13" t="n">
+        <v>715614.0</v>
+      </c>
+      <c r="N59" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O59" s="13" t="n">
+        <v>9660794.0</v>
+      </c>
+      <c r="P59" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q59" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="4" t="n">
+        <v>54.0</v>
+      </c>
+      <c r="B60" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C60" s="6" t="inlineStr">
+        <is>
+          <t>C25MNL</t>
+        </is>
+      </c>
+      <c r="D60" s="7" t="inlineStr">
+        <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="E60" s="7" t="inlineStr">
+        <is>
+          <t>10/10/2025</t>
+        </is>
+      </c>
+      <c r="F60" s="7" t="inlineStr">
+        <is>
+          <t>3502547930</t>
+        </is>
+      </c>
+      <c r="G60" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH  PHÁT TRIỂN THƯƠNG MẠI TÂM NGUYÊN LONG</t>
+        </is>
+      </c>
+      <c r="H60" s="6" t="inlineStr">
+        <is>
+          <t>199 Đường 2/9, Phường Tam Thắng, TP Hồ Chí Minh, Việt Nam.</t>
+        </is>
+      </c>
+      <c r="I60" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J60" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K60" s="6"/>
+      <c r="L60" s="13" t="n">
+        <v>5046275.0</v>
+      </c>
+      <c r="M60" s="13" t="n">
+        <v>403702.0</v>
+      </c>
+      <c r="N60" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O60" s="13" t="n">
+        <v>5449977.0</v>
+      </c>
+      <c r="P60" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q60" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="4" t="n">
+        <v>55.0</v>
+      </c>
+      <c r="B61" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C61" s="6" t="inlineStr">
+        <is>
+          <t>C25MNL</t>
+        </is>
+      </c>
+      <c r="D61" s="7" t="inlineStr">
+        <is>
+          <t>133</t>
+        </is>
+      </c>
+      <c r="E61" s="7" t="inlineStr">
+        <is>
+          <t>10/10/2025</t>
+        </is>
+      </c>
+      <c r="F61" s="7" t="inlineStr">
+        <is>
+          <t>3502547930</t>
+        </is>
+      </c>
+      <c r="G61" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH  PHÁT TRIỂN THƯƠNG MẠI TÂM NGUYÊN LONG</t>
+        </is>
+      </c>
+      <c r="H61" s="6" t="inlineStr">
+        <is>
+          <t>199 Đường 2/9, Phường Tam Thắng, TP Hồ Chí Minh, Việt Nam.</t>
+        </is>
+      </c>
+      <c r="I61" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J61" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K61" s="6"/>
+      <c r="L61" s="13" t="n">
+        <v>1.0572222E7</v>
+      </c>
+      <c r="M61" s="13" t="n">
+        <v>845778.0</v>
+      </c>
+      <c r="N61" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O61" s="13" t="n">
+        <v>1.1418E7</v>
+      </c>
+      <c r="P61" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q61" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="4" t="n">
+        <v>56.0</v>
+      </c>
+      <c r="B62" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C62" s="6" t="inlineStr">
+        <is>
+          <t>C25MNL</t>
+        </is>
+      </c>
+      <c r="D62" s="7" t="inlineStr">
+        <is>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="E62" s="7" t="inlineStr">
+        <is>
+          <t>10/10/2025</t>
+        </is>
+      </c>
+      <c r="F62" s="7" t="inlineStr">
+        <is>
+          <t>3502547930</t>
+        </is>
+      </c>
+      <c r="G62" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH  PHÁT TRIỂN THƯƠNG MẠI TÂM NGUYÊN LONG</t>
+        </is>
+      </c>
+      <c r="H62" s="6" t="inlineStr">
+        <is>
+          <t>199 Đường 2/9, Phường Tam Thắng, TP Hồ Chí Minh, Việt Nam.</t>
+        </is>
+      </c>
+      <c r="I62" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J62" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K62" s="6"/>
+      <c r="L62" s="13" t="n">
+        <v>7453700.0</v>
+      </c>
+      <c r="M62" s="13" t="n">
+        <v>596296.0</v>
+      </c>
+      <c r="N62" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O62" s="13" t="n">
+        <v>8049996.0</v>
+      </c>
+      <c r="P62" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q62" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="4" t="n">
+        <v>57.0</v>
+      </c>
+      <c r="B63" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C63" s="6" t="inlineStr">
+        <is>
+          <t>C25MNL</t>
+        </is>
+      </c>
+      <c r="D63" s="7" t="inlineStr">
+        <is>
+          <t>235</t>
+        </is>
+      </c>
+      <c r="E63" s="7" t="inlineStr">
+        <is>
+          <t>15/10/2025</t>
+        </is>
+      </c>
+      <c r="F63" s="7" t="inlineStr">
+        <is>
+          <t>3502547930</t>
+        </is>
+      </c>
+      <c r="G63" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH  PHÁT TRIỂN THƯƠNG MẠI TÂM NGUYÊN LONG</t>
+        </is>
+      </c>
+      <c r="H63" s="6" t="inlineStr">
+        <is>
+          <t>199 Đường 2/9, Phường Tam Thắng, TP Hồ Chí Minh, Việt Nam.</t>
+        </is>
+      </c>
+      <c r="I63" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J63" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K63" s="6"/>
+      <c r="L63" s="13" t="n">
+        <v>1425924.0</v>
+      </c>
+      <c r="M63" s="13" t="n">
+        <v>114074.0</v>
+      </c>
+      <c r="N63" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O63" s="13" t="n">
+        <v>1539998.0</v>
+      </c>
+      <c r="P63" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q63" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="4" t="n">
+        <v>58.0</v>
+      </c>
+      <c r="B64" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C64" s="6" t="inlineStr">
+        <is>
+          <t>C25MNL</t>
+        </is>
+      </c>
+      <c r="D64" s="7" t="inlineStr">
+        <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="E64" s="7" t="inlineStr">
+        <is>
+          <t>15/10/2025</t>
+        </is>
+      </c>
+      <c r="F64" s="7" t="inlineStr">
+        <is>
+          <t>3502547930</t>
+        </is>
+      </c>
+      <c r="G64" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH  PHÁT TRIỂN THƯƠNG MẠI TÂM NGUYÊN LONG</t>
+        </is>
+      </c>
+      <c r="H64" s="6" t="inlineStr">
+        <is>
+          <t>199 Đường 2/9, Phường Tam Thắng, TP Hồ Chí Minh, Việt Nam.</t>
+        </is>
+      </c>
+      <c r="I64" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J64" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K64" s="6"/>
+      <c r="L64" s="13" t="n">
+        <v>1268514.0</v>
+      </c>
+      <c r="M64" s="13" t="n">
+        <v>101481.0</v>
+      </c>
+      <c r="N64" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O64" s="13" t="n">
+        <v>1369995.0</v>
+      </c>
+      <c r="P64" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q64" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="4" t="n">
+        <v>59.0</v>
+      </c>
+      <c r="B65" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C65" s="6" t="inlineStr">
+        <is>
+          <t>C25MNL</t>
+        </is>
+      </c>
+      <c r="D65" s="7" t="inlineStr">
+        <is>
+          <t>456</t>
+        </is>
+      </c>
+      <c r="E65" s="7" t="inlineStr">
+        <is>
+          <t>27/10/2025</t>
+        </is>
+      </c>
+      <c r="F65" s="7" t="inlineStr">
+        <is>
+          <t>3502547930</t>
+        </is>
+      </c>
+      <c r="G65" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH  PHÁT TRIỂN THƯƠNG MẠI TÂM NGUYÊN LONG</t>
+        </is>
+      </c>
+      <c r="H65" s="6" t="inlineStr">
+        <is>
+          <t>199 Đường 2/9, Phường Tam Thắng, TP Hồ Chí Minh, Việt Nam.</t>
+        </is>
+      </c>
+      <c r="I65" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J65" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K65" s="6"/>
+      <c r="L65" s="13" t="n">
+        <v>2490000.0</v>
+      </c>
+      <c r="M65" s="13" t="n">
+        <v>199200.0</v>
+      </c>
+      <c r="N65" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O65" s="13" t="n">
+        <v>2689200.0</v>
+      </c>
+      <c r="P65" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q65" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="4" t="n">
+        <v>60.0</v>
+      </c>
+      <c r="B66" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C66" s="6" t="inlineStr">
+        <is>
+          <t>C25MNL</t>
+        </is>
+      </c>
+      <c r="D66" s="7" t="inlineStr">
+        <is>
+          <t>564</t>
+        </is>
+      </c>
+      <c r="E66" s="7" t="inlineStr">
+        <is>
+          <t>30/10/2025</t>
+        </is>
+      </c>
+      <c r="F66" s="7" t="inlineStr">
+        <is>
+          <t>3502547930</t>
+        </is>
+      </c>
+      <c r="G66" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH  PHÁT TRIỂN THƯƠNG MẠI TÂM NGUYÊN LONG</t>
+        </is>
+      </c>
+      <c r="H66" s="6" t="inlineStr">
+        <is>
+          <t>199 Đường 2/9, Phường Tam Thắng, TP Hồ Chí Minh, Việt Nam.</t>
+        </is>
+      </c>
+      <c r="I66" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J66" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K66" s="6"/>
+      <c r="L66" s="13" t="n">
+        <v>999996.0</v>
+      </c>
+      <c r="M66" s="13" t="n">
+        <v>80000.0</v>
+      </c>
+      <c r="N66" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O66" s="13" t="n">
+        <v>1079996.0</v>
+      </c>
+      <c r="P66" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q66" s="6" t="inlineStr">
         <is>
           <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
         </is>
